--- a/data/收益明细.xlsx
+++ b/data/收益明细.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1872"/>
+  <dimension ref="A1:B1873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01708626586554995</v>
+        <v>0.01708626586554973</v>
       </c>
     </row>
     <row r="5">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01959088856936153</v>
+        <v>-0.01959088856936131</v>
       </c>
     </row>
     <row r="6">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006012079939521353</v>
+        <v>0.006012079939521131</v>
       </c>
     </row>
     <row r="10">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.02482113306987566</v>
+        <v>-0.02482113306987555</v>
       </c>
     </row>
     <row r="11">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0002830345069972928</v>
+        <v>0.0002830345069970708</v>
       </c>
     </row>
     <row r="14">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0001149061768455084</v>
+        <v>-0.0001149061768457305</v>
       </c>
     </row>
     <row r="16">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01429719159433296</v>
+        <v>-0.01429719159433274</v>
       </c>
     </row>
     <row r="17">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01770705818691187</v>
+        <v>0.01770705818691209</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0078953901868557</v>
+        <v>0.007895390186855478</v>
       </c>
     </row>
     <row r="22">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.004813489541999005</v>
+        <v>-0.004813489541999116</v>
       </c>
     </row>
     <row r="23">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01103394141021785</v>
+        <v>-0.01103394141021741</v>
       </c>
     </row>
     <row r="24">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001300529274145479</v>
+        <v>0.001300529274145035</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.01419384410462099</v>
+        <v>-0.01419384410462032</v>
       </c>
     </row>
     <row r="26">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.02093991851095045</v>
+        <v>-0.02093991851095056</v>
       </c>
     </row>
     <row r="27">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.003845426417374509</v>
+        <v>-0.003845426417374731</v>
       </c>
     </row>
     <row r="28">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.02495840999482868</v>
+        <v>-0.02495840999482879</v>
       </c>
     </row>
     <row r="29">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02589360303164323</v>
+        <v>0.02589360303164301</v>
       </c>
     </row>
     <row r="30">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002525375130286278</v>
+        <v>-0.002525375130286056</v>
       </c>
     </row>
     <row r="31">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01973963642471444</v>
+        <v>0.01973963642471466</v>
       </c>
     </row>
     <row r="32">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.004210241006697757</v>
+        <v>0.004210241006697535</v>
       </c>
     </row>
     <row r="33">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001884967431883489</v>
+        <v>-0.001884967431883267</v>
       </c>
     </row>
     <row r="35">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.01742029164600889</v>
+        <v>-0.017420291646009</v>
       </c>
     </row>
     <row r="36">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.01117478896934143</v>
+        <v>-0.01117478896934154</v>
       </c>
     </row>
     <row r="37">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01287970868229604</v>
+        <v>0.01287970868229582</v>
       </c>
     </row>
     <row r="40">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.006841711920057669</v>
+        <v>-0.00684171192005778</v>
       </c>
     </row>
     <row r="46">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.01470890548394133</v>
+        <v>-0.01470890548394099</v>
       </c>
     </row>
     <row r="47">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001516813142787843</v>
+        <v>0.001516813142787399</v>
       </c>
     </row>
     <row r="48">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.007930184982597011</v>
+        <v>0.007930184982597233</v>
       </c>
     </row>
     <row r="50">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.005911720674500298</v>
+        <v>0.005911720674500076</v>
       </c>
     </row>
     <row r="53">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.02053072188950766</v>
+        <v>-0.02053072188950744</v>
       </c>
     </row>
     <row r="54">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.001853243456947928</v>
+        <v>-0.001853243456948039</v>
       </c>
     </row>
     <row r="55">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0005818242947028818</v>
+        <v>-0.0005818242947027708</v>
       </c>
     </row>
     <row r="56">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.001965305837336229</v>
+        <v>-0.00196530583733634</v>
       </c>
     </row>
     <row r="58">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.01025040173899916</v>
+        <v>-0.01025040173899894</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.01423955478730576</v>
+        <v>0.01423955478730599</v>
       </c>
     </row>
     <row r="60">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.006068343100603668</v>
+        <v>0.006068343100603446</v>
       </c>
     </row>
     <row r="61">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.01502882802808303</v>
+        <v>0.01502882802808325</v>
       </c>
     </row>
     <row r="63">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.001618041480692223</v>
+        <v>-0.001618041480692334</v>
       </c>
     </row>
     <row r="64">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.001647578626110757</v>
+        <v>0.001647578626110535</v>
       </c>
     </row>
     <row r="65">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.01572464749582747</v>
+        <v>-0.01572464749582758</v>
       </c>
     </row>
     <row r="66">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.03071406754613126</v>
+        <v>-0.03071406754613137</v>
       </c>
     </row>
     <row r="68">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.004518276709787772</v>
+        <v>0.004518276709787994</v>
       </c>
     </row>
     <row r="70">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.006408761531918383</v>
+        <v>-0.006408761531918605</v>
       </c>
     </row>
     <row r="72">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.01660011531513839</v>
+        <v>-0.01660011531513828</v>
       </c>
     </row>
     <row r="73">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.0249061696280688</v>
+        <v>-0.02490616962806891</v>
       </c>
     </row>
     <row r="74">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.009629834844572027</v>
+        <v>0.009629834844572249</v>
       </c>
     </row>
     <row r="75">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.02379802663933739</v>
+        <v>-0.02379802663933728</v>
       </c>
     </row>
     <row r="76">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.01357255159012682</v>
+        <v>0.0135725515901266</v>
       </c>
     </row>
     <row r="77">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.04032934029329893</v>
+        <v>0.04032934029329938</v>
       </c>
     </row>
     <row r="78">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.01157491216086093</v>
+        <v>-0.01157491216086082</v>
       </c>
     </row>
     <row r="79">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0008419080480059904</v>
+        <v>0.0008419080480055463</v>
       </c>
     </row>
     <row r="80">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.001611284363969734</v>
+        <v>-0.001611284363969401</v>
       </c>
     </row>
     <row r="81">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.01353832413503731</v>
+        <v>0.01353832413503708</v>
       </c>
     </row>
     <row r="82">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.01171909526792114</v>
+        <v>-0.01171909526792125</v>
       </c>
     </row>
     <row r="83">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.01554090893306825</v>
+        <v>0.01554090893306848</v>
       </c>
     </row>
     <row r="84">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.003073483587245462</v>
+        <v>0.00307348358724524</v>
       </c>
     </row>
     <row r="86">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.005650763803636827</v>
+        <v>-0.005650763803636938</v>
       </c>
     </row>
     <row r="95">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.01833484279885322</v>
+        <v>0.01833484279885345</v>
       </c>
     </row>
     <row r="96">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.007403482524558358</v>
+        <v>0.00740348252455858</v>
       </c>
     </row>
     <row r="98">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.03628247986016753</v>
+        <v>-0.03628247986016764</v>
       </c>
     </row>
     <row r="99">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.006787204901907318</v>
+        <v>0.00678720490190754</v>
       </c>
     </row>
     <row r="100">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.003650438829745362</v>
+        <v>0.00365043882974514</v>
       </c>
     </row>
     <row r="101">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.04487543075745493</v>
+        <v>-0.04487543075745515</v>
       </c>
     </row>
     <row r="102">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.008359590506336945</v>
+        <v>0.008359590506337611</v>
       </c>
     </row>
     <row r="103">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.003506676924671437</v>
+        <v>0.003506676924670993</v>
       </c>
     </row>
     <row r="104">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.01717319003679019</v>
+        <v>0.01717319003679041</v>
       </c>
     </row>
     <row r="105">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.02143879218847411</v>
+        <v>-0.02143879218847422</v>
       </c>
     </row>
     <row r="106">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.01768189764393502</v>
+        <v>0.01768189764393524</v>
       </c>
     </row>
     <row r="107">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.02806041603567366</v>
+        <v>0.02806041603567344</v>
       </c>
     </row>
     <row r="108">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.01988985853059544</v>
+        <v>-0.01988985853059533</v>
       </c>
     </row>
     <row r="111">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.001760312165028477</v>
+        <v>0.001760312165028255</v>
       </c>
     </row>
     <row r="112">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.01104303779937976</v>
+        <v>-0.01104303779937965</v>
       </c>
     </row>
     <row r="113">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.006605522591641488</v>
+        <v>0.00660552259164171</v>
       </c>
     </row>
     <row r="116">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.003283574459499894</v>
+        <v>0.003283574459499672</v>
       </c>
     </row>
     <row r="119">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.009524529778775492</v>
+        <v>-0.00952452977877527</v>
       </c>
     </row>
     <row r="120">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.006632720948458459</v>
+        <v>0.006632720948458237</v>
       </c>
     </row>
     <row r="121">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.006285131891105689</v>
+        <v>-0.006285131891105911</v>
       </c>
     </row>
     <row r="124">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.01315178967089392</v>
+        <v>0.01315178967089436</v>
       </c>
     </row>
     <row r="125">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.02128995667108347</v>
+        <v>-0.02128995667108358</v>
       </c>
     </row>
     <row r="126">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.003513601841357961</v>
+        <v>-0.00351360184135785</v>
       </c>
     </row>
     <row r="127">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.009084748374499019</v>
+        <v>-0.00908474837449913</v>
       </c>
     </row>
     <row r="128">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.002058478204177039</v>
+        <v>0.002058478204177261</v>
       </c>
     </row>
     <row r="129">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0005666444986545116</v>
+        <v>0.0005666444986547337</v>
       </c>
     </row>
     <row r="132">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.00423882413680865</v>
+        <v>-0.004238824136808539</v>
       </c>
     </row>
     <row r="134">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-0.003723496416957572</v>
+        <v>-0.003723496416957683</v>
       </c>
     </row>
     <row r="136">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.0001652283752828776</v>
+        <v>0.0001652283752830996</v>
       </c>
     </row>
     <row r="138">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.01331679645708272</v>
+        <v>-0.01331679645708295</v>
       </c>
     </row>
     <row r="139">
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.002803517459478488</v>
+        <v>0.002803517459478266</v>
       </c>
     </row>
     <row r="141">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-0.007230494200146764</v>
+        <v>-0.007230494200146653</v>
       </c>
     </row>
     <row r="142">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.003361413291861792</v>
+        <v>0.003361413291862014</v>
       </c>
     </row>
     <row r="143">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.01271455330696947</v>
+        <v>-0.01271455330696958</v>
       </c>
     </row>
     <row r="146">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.01002425580893418</v>
+        <v>-0.01002425580893407</v>
       </c>
     </row>
     <row r="147">
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-0.01082163193005903</v>
+        <v>-0.01082163193005925</v>
       </c>
     </row>
     <row r="148">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.00883011675863099</v>
+        <v>-0.008830116758630879</v>
       </c>
     </row>
     <row r="149">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.02485377751131201</v>
+        <v>0.02485377751131224</v>
       </c>
     </row>
     <row r="150">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.009965127047785183</v>
+        <v>0.009965127047784961</v>
       </c>
     </row>
     <row r="152">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.00235316735197566</v>
+        <v>0.002353167351975438</v>
       </c>
     </row>
     <row r="157">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.01816743827592338</v>
+        <v>0.01816743827592315</v>
       </c>
     </row>
     <row r="160">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.04038116384874435</v>
+        <v>0.04038116384874457</v>
       </c>
     </row>
     <row r="161">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.001572250187622526</v>
+        <v>0.001572250187622748</v>
       </c>
     </row>
     <row r="162">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-0.001188945965756916</v>
+        <v>-0.001188945965757138</v>
       </c>
     </row>
     <row r="163">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.02268840531965233</v>
+        <v>0.02268840531965211</v>
       </c>
     </row>
     <row r="167">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.01385774179379662</v>
+        <v>0.01385774179379728</v>
       </c>
     </row>
     <row r="168">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.01292715848901804</v>
+        <v>0.01292715848901782</v>
       </c>
     </row>
     <row r="169">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.03897267939271387</v>
+        <v>0.03897267939271365</v>
       </c>
     </row>
     <row r="171">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.01576083647396964</v>
+        <v>0.01576083647396942</v>
       </c>
     </row>
     <row r="172">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-0.01287047771256233</v>
+        <v>-0.01287047771256211</v>
       </c>
     </row>
     <row r="173">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-0.02010864563764037</v>
+        <v>-0.02010864563764014</v>
       </c>
     </row>
     <row r="174">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.02280085917189423</v>
+        <v>0.02280085917189401</v>
       </c>
     </row>
     <row r="175">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.02206458867388972</v>
+        <v>0.02206458867388994</v>
       </c>
     </row>
     <row r="176">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-0.00152068652328996</v>
+        <v>-0.001520686523290182</v>
       </c>
     </row>
     <row r="178">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.008013929700946942</v>
+        <v>0.008013929700947386</v>
       </c>
     </row>
     <row r="179">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-0.009968224254928715</v>
+        <v>-0.009968224254929048</v>
       </c>
     </row>
     <row r="184">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0215164476616978</v>
+        <v>0.02151644766169825</v>
       </c>
     </row>
     <row r="185">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.03632438240299574</v>
+        <v>0.03632438240299551</v>
       </c>
     </row>
     <row r="186">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.002428842704102374</v>
+        <v>0.002428842704102596</v>
       </c>
     </row>
     <row r="187">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.01232785125458702</v>
+        <v>0.0123278512545868</v>
       </c>
     </row>
     <row r="189">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-0.005911016976345995</v>
+        <v>-0.005911016976345773</v>
       </c>
     </row>
     <row r="198">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-0.01554208955406366</v>
+        <v>-0.015542089554064</v>
       </c>
     </row>
     <row r="201">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>-0.0313753863883981</v>
+        <v>-0.03137538638839776</v>
       </c>
     </row>
     <row r="203">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-0.007432472344896524</v>
+        <v>-0.007432472344896857</v>
       </c>
     </row>
     <row r="204">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-0.01586853705332902</v>
+        <v>-0.0158685370533288</v>
       </c>
     </row>
     <row r="205">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-0.06260735064051903</v>
+        <v>-0.06260735064051925</v>
       </c>
     </row>
     <row r="207">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-0.01849371293912749</v>
+        <v>-0.01849371293912727</v>
       </c>
     </row>
     <row r="209">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-0.01352349645923523</v>
+        <v>-0.01352349645923501</v>
       </c>
     </row>
     <row r="210">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.02978462115459624</v>
+        <v>0.02978462115459601</v>
       </c>
     </row>
     <row r="211">
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-0.007820309839754236</v>
+        <v>-0.007820309839754014</v>
       </c>
     </row>
     <row r="212">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-0.009297749213471818</v>
+        <v>-0.009297749213471929</v>
       </c>
     </row>
     <row r="213">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-0.03583974939327272</v>
+        <v>-0.03583974939327284</v>
       </c>
     </row>
     <row r="216">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-0.02524592988485841</v>
+        <v>-0.0252459298848583</v>
       </c>
     </row>
     <row r="217">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.02345581791036389</v>
+        <v>0.02345581791036411</v>
       </c>
     </row>
     <row r="218">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-0.02549538223839132</v>
+        <v>-0.02549538223839154</v>
       </c>
     </row>
     <row r="220">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.007676112411729497</v>
+        <v>0.007676112411729052</v>
       </c>
     </row>
     <row r="226">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>-0.01203276405873188</v>
+        <v>-0.01203276405873133</v>
       </c>
     </row>
     <row r="227">
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>-0.0165615839164106</v>
+        <v>-0.01656158391641072</v>
       </c>
     </row>
     <row r="228">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.004457846351092476</v>
+        <v>0.004457846351092254</v>
       </c>
     </row>
     <row r="229">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-0.01888008452601797</v>
+        <v>-0.01888008452601775</v>
       </c>
     </row>
     <row r="230">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.03093200369612181</v>
+        <v>0.03093200369612159</v>
       </c>
     </row>
     <row r="232">
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>-0.01350592962578268</v>
+        <v>-0.01350592962578245</v>
       </c>
     </row>
     <row r="233">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-0.02230753052044865</v>
+        <v>-0.02230753052044887</v>
       </c>
     </row>
     <row r="235">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.001288611809081797</v>
+        <v>0.001288611809082019</v>
       </c>
     </row>
     <row r="236">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>-0.006103397318362624</v>
+        <v>-0.006103397318362513</v>
       </c>
     </row>
     <row r="237">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.01551701882355472</v>
+        <v>0.01551701882355494</v>
       </c>
     </row>
     <row r="238">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.008182175199940245</v>
+        <v>0.008182175199939579</v>
       </c>
     </row>
     <row r="239">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>-0.00107758256190793</v>
+        <v>-0.001077582561907708</v>
       </c>
     </row>
     <row r="241">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>-0.01332218641913374</v>
+        <v>-0.01332218641913352</v>
       </c>
     </row>
     <row r="242">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>-0.001484734728148029</v>
+        <v>-0.001484734728148251</v>
       </c>
     </row>
     <row r="243">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>-0.01022144958477367</v>
+        <v>-0.01022144958477345</v>
       </c>
     </row>
     <row r="245">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.00765432241265751</v>
+        <v>0.007654322412657732</v>
       </c>
     </row>
     <row r="247">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.003156926335925236</v>
+        <v>0.00315692633592457</v>
       </c>
     </row>
     <row r="249">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.009953939649229193</v>
+        <v>0.009953939649229637</v>
       </c>
     </row>
     <row r="250">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>-0.02475288513342833</v>
+        <v>-0.02475288513342844</v>
       </c>
     </row>
     <row r="251">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>-0.003399587844266638</v>
+        <v>-0.003399587844266416</v>
       </c>
     </row>
     <row r="253">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>-0.002933628876201189</v>
+        <v>-0.0029336288762013</v>
       </c>
     </row>
     <row r="254">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.008188714848466283</v>
+        <v>0.008188714848466727</v>
       </c>
     </row>
     <row r="255">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.01320413981256374</v>
+        <v>0.01320413981256352</v>
       </c>
     </row>
     <row r="256">
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.009926371010728685</v>
+        <v>0.009926371010728907</v>
       </c>
     </row>
     <row r="257">
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>-0.0004500109206555525</v>
+        <v>-0.0004500109206558855</v>
       </c>
     </row>
     <row r="258">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>-0.02019517082525735</v>
+        <v>-0.02019517082525712</v>
       </c>
     </row>
     <row r="259">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.001379341962310043</v>
+        <v>0.001379341962310265</v>
       </c>
     </row>
     <row r="260">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>-0.02430784936589159</v>
+        <v>-0.02430784936589203</v>
       </c>
     </row>
     <row r="261">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.01545389369577177</v>
+        <v>0.01545389369577199</v>
       </c>
     </row>
     <row r="262">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>-0.001001787967991996</v>
+        <v>-0.001001787967992551</v>
       </c>
     </row>
     <row r="265">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.004257320113309815</v>
+        <v>0.004257320113310259</v>
       </c>
     </row>
     <row r="266">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>-0.006195873821834619</v>
+        <v>-0.006195873821834286</v>
       </c>
     </row>
     <row r="268">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>-0.003875213419964441</v>
+        <v>-0.003875213419964552</v>
       </c>
     </row>
     <row r="269">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>-0.01081617222596687</v>
+        <v>-0.01081617222596698</v>
       </c>
     </row>
     <row r="270">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.008929135062472726</v>
+        <v>0.008929135062472948</v>
       </c>
     </row>
     <row r="274">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>-0.01036636592066764</v>
+        <v>-0.01036636592066742</v>
       </c>
     </row>
     <row r="275">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.01676361839134954</v>
+        <v>0.01676361839134932</v>
       </c>
     </row>
     <row r="276">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.008449611388157141</v>
+        <v>0.008449611388157363</v>
       </c>
     </row>
     <row r="278">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.004073087573717604</v>
+        <v>0.004073087573717382</v>
       </c>
     </row>
     <row r="279">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.02683243182111172</v>
+        <v>0.02683243182111195</v>
       </c>
     </row>
     <row r="281">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>-0.00290058493460188</v>
+        <v>-0.002900584934601991</v>
       </c>
     </row>
     <row r="282">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>-0.003094739345946174</v>
+        <v>-0.003094739345946063</v>
       </c>
     </row>
     <row r="284">
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>-0.009092287423267731</v>
+        <v>-0.009092287423267953</v>
       </c>
     </row>
     <row r="285">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>-0.01181005384569711</v>
+        <v>-0.011810053845697</v>
       </c>
     </row>
     <row r="286">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.01340457728856936</v>
+        <v>0.01340457728856892</v>
       </c>
     </row>
     <row r="287">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.01288796472531262</v>
+        <v>0.01288796472531306</v>
       </c>
     </row>
     <row r="288">
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>-6.889337240911786e-05</v>
+        <v>-6.88933724093399e-05</v>
       </c>
     </row>
     <row r="289">
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>-0.02111459339307442</v>
+        <v>-0.02111459339307453</v>
       </c>
     </row>
     <row r="290">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.02973578085217921</v>
+        <v>0.02973578085217965</v>
       </c>
     </row>
     <row r="291">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.004660551463087304</v>
+        <v>0.004660551463086859</v>
       </c>
     </row>
     <row r="292">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.001914057068349795</v>
+        <v>0.001914057068349573</v>
       </c>
     </row>
     <row r="295">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.02006307618460035</v>
+        <v>0.02006307618460013</v>
       </c>
     </row>
     <row r="296">
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.006155233025517903</v>
+        <v>0.006155233025518347</v>
       </c>
     </row>
     <row r="297">
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>-0.005523292544501235</v>
+        <v>-0.005523292544501124</v>
       </c>
     </row>
     <row r="298">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.006675465865011443</v>
+        <v>0.006675465865011221</v>
       </c>
     </row>
     <row r="300">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>-0.005541326993856455</v>
+        <v>-0.005541326993856566</v>
       </c>
     </row>
     <row r="304">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>-0.006010935248334515</v>
+        <v>-0.006010935248334182</v>
       </c>
     </row>
     <row r="305">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>-0.001352161496891102</v>
+        <v>-0.00135216149689088</v>
       </c>
     </row>
     <row r="306">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>-0.02334943685624735</v>
+        <v>-0.02334943685624791</v>
       </c>
     </row>
     <row r="307">
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>-0.02106560754035391</v>
+        <v>-0.02106560754035347</v>
       </c>
     </row>
     <row r="308">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.01403802759265393</v>
+        <v>0.01403802759265371</v>
       </c>
     </row>
     <row r="309">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>-0.02020860387000667</v>
+        <v>-0.02020860387000689</v>
       </c>
     </row>
     <row r="310">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.007368109109177956</v>
+        <v>0.007368109109177734</v>
       </c>
     </row>
     <row r="312">
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.01088365655079326</v>
+        <v>0.01088365655079371</v>
       </c>
     </row>
     <row r="315">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>-0.001533424229726688</v>
+        <v>-0.001533424229727021</v>
       </c>
     </row>
     <row r="317">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>-0.01734685492222121</v>
+        <v>-0.01734685492222143</v>
       </c>
     </row>
     <row r="319">
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>-0.006510350869090353</v>
+        <v>-0.00651035086909002</v>
       </c>
     </row>
     <row r="320">
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.007038878014478778</v>
+        <v>0.007038878014479</v>
       </c>
     </row>
     <row r="321">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>-0.00548654105218993</v>
+        <v>-0.005486541052190042</v>
       </c>
     </row>
     <row r="322">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>-0.001705044302586667</v>
+        <v>-0.001705044302587222</v>
       </c>
     </row>
     <row r="324">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.008334179621441118</v>
+        <v>0.00833417962144134</v>
       </c>
     </row>
     <row r="325">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>-0.006854435087049526</v>
+        <v>-0.006854435087049748</v>
       </c>
     </row>
     <row r="328">
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.001745935703510115</v>
+        <v>0.001745935703510559</v>
       </c>
     </row>
     <row r="330">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>-0.00126315786118425</v>
+        <v>-0.001263157861184361</v>
       </c>
     </row>
     <row r="331">
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>-0.02448851298871968</v>
+        <v>-0.0244885129887199</v>
       </c>
     </row>
     <row r="335">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.008275082204899142</v>
+        <v>0.008275082204899364</v>
       </c>
     </row>
     <row r="336">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>-0.005173421113665588</v>
+        <v>-0.005173421113665366</v>
       </c>
     </row>
     <row r="337">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>-0.01014791819777405</v>
+        <v>-0.01014791819777427</v>
       </c>
     </row>
     <row r="339">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.006374669706664449</v>
+        <v>0.006374669706664671</v>
       </c>
     </row>
     <row r="340">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>-0.01135995920824207</v>
+        <v>-0.01135995920824184</v>
       </c>
     </row>
     <row r="342">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>-0.008379181153891913</v>
+        <v>-0.008379181153892246</v>
       </c>
     </row>
     <row r="343">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>-0.00278215635030743</v>
+        <v>-0.002782156350307652</v>
       </c>
     </row>
     <row r="345">
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>-0.005892717468528486</v>
+        <v>-0.005892717468528264</v>
       </c>
     </row>
     <row r="346">
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>-0.009184960887139715</v>
+        <v>-0.009184960887139493</v>
       </c>
     </row>
     <row r="348">
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.006618208574647122</v>
+        <v>0.0066182085746469</v>
       </c>
     </row>
     <row r="353">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.002989378497769479</v>
+        <v>0.002989378497769257</v>
       </c>
     </row>
     <row r="355">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.002151945837539859</v>
+        <v>0.002151945837540303</v>
       </c>
     </row>
     <row r="356">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>-0.006191151837085629</v>
+        <v>-0.006191151837085851</v>
       </c>
     </row>
     <row r="357">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>-0.001880755448676275</v>
+        <v>-0.001880755448676164</v>
       </c>
     </row>
     <row r="358">
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.01220440453958616</v>
+        <v>0.01220440453958593</v>
       </c>
     </row>
     <row r="359">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.02701511919701183</v>
+        <v>0.02701511919701205</v>
       </c>
     </row>
     <row r="360">
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.007534422072914992</v>
+        <v>0.007534422072915214</v>
       </c>
     </row>
     <row r="361">
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.006522330516067543</v>
+        <v>0.006522330516067099</v>
       </c>
     </row>
     <row r="362">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.005299692600070571</v>
+        <v>0.005299692600070349</v>
       </c>
     </row>
     <row r="363">
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>-0.005655717661048887</v>
+        <v>-0.005655717661048665</v>
       </c>
     </row>
     <row r="364">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.01286389659004628</v>
+        <v>0.01286389659004605</v>
       </c>
     </row>
     <row r="366">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>-0.0001029041837982136</v>
+        <v>-0.0001029041837979916</v>
       </c>
     </row>
     <row r="367">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>-0.005860139699447098</v>
+        <v>-0.005860139699446876</v>
       </c>
     </row>
     <row r="369">
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.01828277426452396</v>
+        <v>0.01828277426452418</v>
       </c>
     </row>
     <row r="370">
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>-0.00222917989677085</v>
+        <v>-0.002229179896771405</v>
       </c>
     </row>
     <row r="371">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.01708533903898779</v>
+        <v>0.01708533903898801</v>
       </c>
     </row>
     <row r="372">
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.009095777484984024</v>
+        <v>0.009095777484983802</v>
       </c>
     </row>
     <row r="374">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.01549004655012998</v>
+        <v>0.0154900465501302</v>
       </c>
     </row>
     <row r="375">
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>-0.02053844666690197</v>
+        <v>-0.02053844666690219</v>
       </c>
     </row>
     <row r="376">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.003342652224972431</v>
+        <v>0.003342652224972209</v>
       </c>
     </row>
     <row r="378">
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.006889260034549372</v>
+        <v>0.006889260034549594</v>
       </c>
     </row>
     <row r="379">
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>-0.00207632855954698</v>
+        <v>-0.002076328559547203</v>
       </c>
     </row>
     <row r="382">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>-0.0148171175695142</v>
+        <v>-0.01481711756951409</v>
       </c>
     </row>
     <row r="385">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>-0.03308939982960224</v>
+        <v>-0.03308939982960213</v>
       </c>
     </row>
     <row r="387">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>-0.09131435188878045</v>
+        <v>-0.09131435188878068</v>
       </c>
     </row>
     <row r="388">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.03027144756167832</v>
+        <v>0.03027144756167854</v>
       </c>
     </row>
     <row r="390">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.01812735598908266</v>
+        <v>0.01812735598908222</v>
       </c>
     </row>
     <row r="391">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004965689461809752</v>
+        <v>0.004965689461809975</v>
       </c>
     </row>
     <row r="392">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>-0.009827756990878123</v>
+        <v>-0.009827756990878567</v>
       </c>
     </row>
     <row r="394">
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.009797605121105724</v>
+        <v>0.009797605121106168</v>
       </c>
     </row>
     <row r="395">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.000921279451444823</v>
+        <v>0.0009212794514450451</v>
       </c>
     </row>
     <row r="397">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.02258720738345477</v>
+        <v>0.02258720738345454</v>
       </c>
     </row>
     <row r="398">
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.01100928367499665</v>
+        <v>0.01100928367499643</v>
       </c>
     </row>
     <row r="401">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.005314801954093396</v>
+        <v>0.005314801954093618</v>
       </c>
     </row>
     <row r="402">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.008436786564158805</v>
+        <v>0.008436786564158583</v>
       </c>
     </row>
     <row r="403">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.009106102770877866</v>
+        <v>0.00910610277087831</v>
       </c>
     </row>
     <row r="406">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>-0.04896627391785835</v>
+        <v>-0.04896627391785846</v>
       </c>
     </row>
     <row r="407">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.01216304385588285</v>
+        <v>0.01216304385588307</v>
       </c>
     </row>
     <row r="409">
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.01936679716532352</v>
+        <v>0.01936679716532286</v>
       </c>
     </row>
     <row r="410">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.01224126726095709</v>
+        <v>0.01224126726095731</v>
       </c>
     </row>
     <row r="411">
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.003113205722677481</v>
+        <v>0.003113205722677259</v>
       </c>
     </row>
     <row r="412">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.01060550488299228</v>
+        <v>0.01060550488299206</v>
       </c>
     </row>
     <row r="414">
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>-0.003636900847467484</v>
+        <v>-0.003636900847466928</v>
       </c>
     </row>
     <row r="415">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>-0.02557605268971019</v>
+        <v>-0.02557605268971042</v>
       </c>
     </row>
     <row r="416">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.01490065915636429</v>
+        <v>0.01490065915636452</v>
       </c>
     </row>
     <row r="422">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>-0.03458288890524697</v>
+        <v>-0.03458288890524741</v>
       </c>
     </row>
     <row r="423">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.0247500090051096</v>
+        <v>0.02475000900510982</v>
       </c>
     </row>
     <row r="424">
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.001231795358022536</v>
+        <v>0.001231795358022314</v>
       </c>
     </row>
     <row r="434">
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.0007396833555963767</v>
+        <v>0.0007396833555961546</v>
       </c>
     </row>
     <row r="435">
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>-0.02181224228192313</v>
+        <v>-0.02181224228192291</v>
       </c>
     </row>
     <row r="436">
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.01987431504523718</v>
+        <v>0.0198743150452374</v>
       </c>
     </row>
     <row r="438">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>-0.00965666350158112</v>
+        <v>-0.009656663501581453</v>
       </c>
     </row>
     <row r="439">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.02167770844210803</v>
+        <v>0.02167770844210826</v>
       </c>
     </row>
     <row r="442">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>-0.0004944293018719348</v>
+        <v>-0.0004944293018717127</v>
       </c>
     </row>
     <row r="445">
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>-0.01443028294755178</v>
+        <v>-0.014430282947552</v>
       </c>
     </row>
     <row r="447">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>-0.02248491331951785</v>
+        <v>-0.02248491331951796</v>
       </c>
     </row>
     <row r="448">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>-0.002313182865839591</v>
+        <v>-0.002313182865839147</v>
       </c>
     </row>
     <row r="452">
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.01495471734998066</v>
+        <v>0.01495471734998044</v>
       </c>
     </row>
     <row r="453">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>-0.007643306224190183</v>
+        <v>-0.007643306224189961</v>
       </c>
     </row>
     <row r="457">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.005232954186441097</v>
+        <v>0.005232954186440875</v>
       </c>
     </row>
     <row r="459">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.01210303384659395</v>
+        <v>0.01210303384659417</v>
       </c>
     </row>
     <row r="460">
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>-0.006382489127909174</v>
+        <v>-0.006382489127909396</v>
       </c>
     </row>
     <row r="462">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>-0.02412169320349056</v>
+        <v>-0.02412169320349034</v>
       </c>
     </row>
     <row r="463">
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.01565253831301971</v>
+        <v>0.01565253831301994</v>
       </c>
     </row>
     <row r="465">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.007979889419207353</v>
+        <v>0.007979889419207131</v>
       </c>
     </row>
     <row r="468">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.02863390981250191</v>
+        <v>0.02863390981250169</v>
       </c>
     </row>
     <row r="469">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>-0.008933623130661039</v>
+        <v>-0.00893362313066115</v>
       </c>
     </row>
     <row r="473">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.001938198312464889</v>
+        <v>0.001938198312464667</v>
       </c>
     </row>
     <row r="475">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>-0.001060223337485566</v>
+        <v>-0.001060223337485233</v>
       </c>
     </row>
     <row r="476">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>-0.009176808538233772</v>
+        <v>-0.009176808538233883</v>
       </c>
     </row>
     <row r="477">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>-0.000527251892635805</v>
+        <v>-0.0005272518926355829</v>
       </c>
     </row>
     <row r="478">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>-0.006246128305674947</v>
+        <v>-0.00624612830567528</v>
       </c>
     </row>
     <row r="479">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.0181114266708251</v>
+        <v>0.01811142667082533</v>
       </c>
     </row>
     <row r="480">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>-0.002878368490650263</v>
+        <v>-0.002878368490650041</v>
       </c>
     </row>
     <row r="482">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>-0.004314204397194321</v>
+        <v>-0.004314204397194432</v>
       </c>
     </row>
     <row r="484">
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.004097487506269371</v>
+        <v>0.004097487506269148</v>
       </c>
     </row>
     <row r="485">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>-0.005492885407306192</v>
+        <v>-0.005492885407306081</v>
       </c>
     </row>
     <row r="486">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>-0.002644135485008525</v>
+        <v>-0.002644135485008303</v>
       </c>
     </row>
     <row r="487">
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.02355079610812716</v>
+        <v>0.02355079610812694</v>
       </c>
     </row>
     <row r="488">
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.003832492134195453</v>
+        <v>0.003832492134195675</v>
       </c>
     </row>
     <row r="489">
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.009493299217094853</v>
+        <v>0.009493299217094631</v>
       </c>
     </row>
     <row r="490">
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.03627970318303686</v>
+        <v>0.03627970318303619</v>
       </c>
     </row>
     <row r="492">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.01238882179471346</v>
+        <v>0.0123888217947139</v>
       </c>
     </row>
     <row r="493">
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.02671823379014016</v>
+        <v>0.02671823379014038</v>
       </c>
     </row>
     <row r="494">
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.02822860587138276</v>
+        <v>0.02822860587138254</v>
       </c>
     </row>
     <row r="495">
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>-0.01452789259209708</v>
+        <v>-0.01452789259209697</v>
       </c>
     </row>
     <row r="496">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>-0.006480168006391729</v>
+        <v>-0.00648016800639184</v>
       </c>
     </row>
     <row r="498">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.04951011788526216</v>
+        <v>0.04951011788526172</v>
       </c>
     </row>
     <row r="502">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.004428684443200437</v>
+        <v>0.004428684443200659</v>
       </c>
     </row>
     <row r="504">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>-0.00993831214526042</v>
+        <v>-0.009938312145260197</v>
       </c>
     </row>
     <row r="505">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>-0.05254779292324019</v>
+        <v>-0.05254779292323997</v>
       </c>
     </row>
     <row r="506">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.0082135100752041</v>
+        <v>0.008213510075204322</v>
       </c>
     </row>
     <row r="507">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.0174150348126958</v>
+        <v>0.01741503481269557</v>
       </c>
     </row>
     <row r="508">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.02144877567392878</v>
+        <v>0.02144877567392856</v>
       </c>
     </row>
     <row r="511">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.01669654611587434</v>
+        <v>0.01669654611587457</v>
       </c>
     </row>
     <row r="512">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>-0.01365933840607803</v>
+        <v>-0.01365933840607825</v>
       </c>
     </row>
     <row r="513">
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>-0.0007676065274665467</v>
+        <v>-0.0007676065274664357</v>
       </c>
     </row>
     <row r="515">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>-0.008077353307121893</v>
+        <v>-0.008077353307122004</v>
       </c>
     </row>
     <row r="516">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>-0.01298705135180234</v>
+        <v>-0.01298705135180256</v>
       </c>
     </row>
     <row r="519">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.0176868019864922</v>
+        <v>0.01768680198649264</v>
       </c>
     </row>
     <row r="520">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.00349281184076311</v>
+        <v>0.003492811840762666</v>
       </c>
     </row>
     <row r="521">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.01334792954430086</v>
+        <v>0.01334792954430131</v>
       </c>
     </row>
     <row r="522">
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.009977765461579136</v>
+        <v>0.009977765461578914</v>
       </c>
     </row>
     <row r="523">
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.01505094551183039</v>
+        <v>0.01505094551183062</v>
       </c>
     </row>
     <row r="527">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>-0.004859516642830242</v>
+        <v>-0.004859516642830353</v>
       </c>
     </row>
     <row r="528">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>-0.02080957825508156</v>
+        <v>-0.02080957825508167</v>
       </c>
     </row>
     <row r="529">
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.006390635458470184</v>
+        <v>0.006390635458470406</v>
       </c>
     </row>
     <row r="530">
@@ -5710,7 +5710,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.01193936872076451</v>
+        <v>0.01193936872076473</v>
       </c>
     </row>
     <row r="531">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.0127941369921909</v>
+        <v>0.01279413699219067</v>
       </c>
     </row>
     <row r="532">
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.01069030169980678</v>
+        <v>0.01069030169980634</v>
       </c>
     </row>
     <row r="534">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>-0.008472748391228135</v>
+        <v>-0.008472748391228024</v>
       </c>
     </row>
     <row r="535">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>4.485387649677541e-05</v>
+        <v>4.48538764972195e-05</v>
       </c>
     </row>
     <row r="536">
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>-0.01669079095289872</v>
+        <v>-0.01669079095289905</v>
       </c>
     </row>
     <row r="537">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.01299031431713016</v>
+        <v>0.0129903143171306</v>
       </c>
     </row>
     <row r="538">
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>-0.0388609181974986</v>
+        <v>-0.03886091819749882</v>
       </c>
     </row>
     <row r="539">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>-0.03221633779963784</v>
+        <v>-0.03221633779963806</v>
       </c>
     </row>
     <row r="540">
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.01926604724649184</v>
+        <v>0.01926604724649206</v>
       </c>
     </row>
     <row r="541">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.001091302496142976</v>
+        <v>0.001091302496143198</v>
       </c>
     </row>
     <row r="543">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.004322185428705883</v>
+        <v>0.00432218542870566</v>
       </c>
     </row>
     <row r="544">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.01591589085979717</v>
+        <v>0.01591589085979739</v>
       </c>
     </row>
     <row r="546">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>-0.0003754175504779855</v>
+        <v>-0.0003754175504778745</v>
       </c>
     </row>
     <row r="547">
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.003771375930206045</v>
+        <v>0.003771375930205378</v>
       </c>
     </row>
     <row r="549">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>-0.02525034700361473</v>
+        <v>-0.0252503470036145</v>
       </c>
     </row>
     <row r="550">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.001042128581224322</v>
+        <v>0.001042128581224544</v>
       </c>
     </row>
     <row r="553">
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.004020104940423819</v>
+        <v>0.004020104940423375</v>
       </c>
     </row>
     <row r="557">
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.00217096259888705</v>
+        <v>0.002170962598887494</v>
       </c>
     </row>
     <row r="558">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>-0.003846846795515391</v>
+        <v>-0.003846846795515724</v>
       </c>
     </row>
     <row r="559">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>-0.005353784530419459</v>
+        <v>-0.005353784530419237</v>
       </c>
     </row>
     <row r="560">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.007911651255398278</v>
+        <v>0.0079116512553985</v>
       </c>
     </row>
     <row r="562">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>-0.01094737891536257</v>
+        <v>-0.01094737891536279</v>
       </c>
     </row>
     <row r="563">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>-0.01533761727138294</v>
+        <v>-0.01533761727138283</v>
       </c>
     </row>
     <row r="565">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>-0.005322524029989673</v>
+        <v>-0.005322524029989895</v>
       </c>
     </row>
     <row r="566">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>-0.0004264987484207117</v>
+        <v>-0.0004264987484208227</v>
       </c>
     </row>
     <row r="567">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>-0.003608328315347853</v>
+        <v>-0.003608328315347742</v>
       </c>
     </row>
     <row r="569">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>-0.02512374053322242</v>
+        <v>-0.02512374053322231</v>
       </c>
     </row>
     <row r="570">
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.01523522535080168</v>
+        <v>0.01523522535080146</v>
       </c>
     </row>
     <row r="571">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.01749409490975418</v>
+        <v>0.01749409490975395</v>
       </c>
     </row>
     <row r="572">
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.003928039914497639</v>
+        <v>0.003928039914497861</v>
       </c>
     </row>
     <row r="573">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.02348473907331283</v>
+        <v>0.02348473907331305</v>
       </c>
     </row>
     <row r="574">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>-0.002252944814642444</v>
+        <v>-0.002252944814642666</v>
       </c>
     </row>
     <row r="575">
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.006484031754623087</v>
+        <v>0.006484031754623309</v>
       </c>
     </row>
     <row r="577">
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.001906925307007867</v>
+        <v>0.001906925307007645</v>
       </c>
     </row>
     <row r="578">
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>-0.001860940325803195</v>
+        <v>-0.001860940325803084</v>
       </c>
     </row>
     <row r="580">
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>-0.007664461443462223</v>
+        <v>-0.007664461443462334</v>
       </c>
     </row>
     <row r="582">
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.01363591550751697</v>
+        <v>0.01363591550751719</v>
       </c>
     </row>
     <row r="586">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>-0.001748455951844363</v>
+        <v>-0.001748455951844252</v>
       </c>
     </row>
     <row r="587">
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>-0.01288210213264129</v>
+        <v>-0.0128821021326414</v>
       </c>
     </row>
     <row r="588">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>-0.007302565802489225</v>
+        <v>-0.007302565802489114</v>
       </c>
     </row>
     <row r="589">
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>-0.01190257762578995</v>
+        <v>-0.01190257762579017</v>
       </c>
     </row>
     <row r="591">
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.01627392312625164</v>
+        <v>0.01627392312625187</v>
       </c>
     </row>
     <row r="592">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>-0.01023982910577237</v>
+        <v>-0.01023982910577248</v>
       </c>
     </row>
     <row r="593">
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.01320752459737107</v>
+        <v>0.01320752459737085</v>
       </c>
     </row>
     <row r="595">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.004671046458246453</v>
+        <v>0.004671046458246675</v>
       </c>
     </row>
     <row r="597">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>-0.0001487296738686972</v>
+        <v>-0.0001487296738684751</v>
       </c>
     </row>
     <row r="603">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.01709738385458337</v>
+        <v>0.01709738385458359</v>
       </c>
     </row>
     <row r="606">
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>-0.006132430570840119</v>
+        <v>-0.00613243057084023</v>
       </c>
     </row>
     <row r="607">
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.001374504912855956</v>
+        <v>0.001374504912855734</v>
       </c>
     </row>
     <row r="608">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>-0.02202788261839084</v>
+        <v>-0.02202788261839095</v>
       </c>
     </row>
     <row r="609">
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.01070874258165078</v>
+        <v>0.01070874258165055</v>
       </c>
     </row>
     <row r="610">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>-0.01069384225381087</v>
+        <v>-0.01069384225381076</v>
       </c>
     </row>
     <row r="611">
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>-0.01558542855035561</v>
+        <v>-0.01558542855035572</v>
       </c>
     </row>
     <row r="612">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.01704227045176898</v>
+        <v>0.0170422704517692</v>
       </c>
     </row>
     <row r="613">
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.0223152430196174</v>
+        <v>0.02231524301961718</v>
       </c>
     </row>
     <row r="614">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.008696904879559986</v>
+        <v>0.008696904879560208</v>
       </c>
     </row>
     <row r="615">
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>-0.01504511376612505</v>
+        <v>-0.01504511376612516</v>
       </c>
     </row>
     <row r="617">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>-0.02768781188503822</v>
+        <v>-0.02768781188503844</v>
       </c>
     </row>
     <row r="618">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.001143720783812308</v>
+        <v>0.001143720783812752</v>
       </c>
     </row>
     <row r="619">
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>-0.02093058578157614</v>
+        <v>-0.02093058578157636</v>
       </c>
     </row>
     <row r="620">
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.01046370205155212</v>
+        <v>0.01046370205155189</v>
       </c>
     </row>
     <row r="621">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>-0.0117851285762739</v>
+        <v>-0.01178512857627345</v>
       </c>
     </row>
     <row r="622">
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>-0.0008709690837781503</v>
+        <v>-0.0008709690837782613</v>
       </c>
     </row>
     <row r="623">
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.001884927107094647</v>
+        <v>0.001884927107094425</v>
       </c>
     </row>
     <row r="627">
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>-0.01110773892570938</v>
+        <v>-0.01110773892570893</v>
       </c>
     </row>
     <row r="629">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>-0.013461704175873</v>
+        <v>-0.01346170417587333</v>
       </c>
     </row>
     <row r="630">
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>-0.005319523740433652</v>
+        <v>-0.005319523740433429</v>
       </c>
     </row>
     <row r="634">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.01375680540203361</v>
+        <v>0.01375680540203317</v>
       </c>
     </row>
     <row r="635">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>-0.009106928572388595</v>
+        <v>-0.009106928572388373</v>
       </c>
     </row>
     <row r="637">
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>-0.0299987116999787</v>
+        <v>-0.02999871169997892</v>
       </c>
     </row>
     <row r="638">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.003410405499099767</v>
+        <v>0.003410405499100211</v>
       </c>
     </row>
     <row r="639">
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.01948695608842499</v>
+        <v>0.01948695608842477</v>
       </c>
     </row>
     <row r="641">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.005811059899313742</v>
+        <v>0.00581105989931352</v>
       </c>
     </row>
     <row r="642">
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.0174891103120125</v>
+        <v>0.01748911031201272</v>
       </c>
     </row>
     <row r="643">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.000616191405026667</v>
+        <v>0.0006161914050268891</v>
       </c>
     </row>
     <row r="645">
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>-0.000713681209164152</v>
+        <v>-0.000713681209164263</v>
       </c>
     </row>
     <row r="649">
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.0268675881673992</v>
+        <v>0.02686758816739943</v>
       </c>
     </row>
     <row r="650">
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>-0.002623394149102176</v>
+        <v>-0.002623394149102398</v>
       </c>
     </row>
     <row r="651">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>-0.008463543386215688</v>
+        <v>-0.008463543386216021</v>
       </c>
     </row>
     <row r="653">
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>-0.006162735151731158</v>
+        <v>-0.006162735151731491</v>
       </c>
     </row>
     <row r="655">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>-0.02030760893394623</v>
+        <v>-0.02030760893394612</v>
       </c>
     </row>
     <row r="656">
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>-0.01282302577462269</v>
+        <v>-0.01282302577462235</v>
       </c>
     </row>
     <row r="657">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>-0.001187048072705976</v>
+        <v>-0.001187048072706087</v>
       </c>
     </row>
     <row r="659">
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.001636267172866468</v>
+        <v>0.00163626717286669</v>
       </c>
     </row>
     <row r="664">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.02691745233958365</v>
+        <v>0.02691745233958343</v>
       </c>
     </row>
     <row r="665">
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>-0.004261654684648897</v>
+        <v>-0.004261654684648786</v>
       </c>
     </row>
     <row r="666">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>-0.01706796062126315</v>
+        <v>-0.01706796062126337</v>
       </c>
     </row>
     <row r="667">
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.008864366042871996</v>
+        <v>0.008864366042872218</v>
       </c>
     </row>
     <row r="669">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.001700064093659082</v>
+        <v>0.001700064093659304</v>
       </c>
     </row>
     <row r="671">
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>-0.0002074040852053649</v>
+        <v>-0.000207404085205698</v>
       </c>
     </row>
     <row r="673">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.003243550064908174</v>
+        <v>0.003243550064908396</v>
       </c>
     </row>
     <row r="674">
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>-0.001729672943315719</v>
+        <v>-0.001729672943315941</v>
       </c>
     </row>
     <row r="678">
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>-0.01645923237218783</v>
+        <v>-0.01645923237218772</v>
       </c>
     </row>
     <row r="679">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.002800352759107172</v>
+        <v>0.002800352759107394</v>
       </c>
     </row>
     <row r="680">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>-0.00219384686474966</v>
+        <v>-0.002193846864749882</v>
       </c>
     </row>
     <row r="682">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.01428114335994302</v>
+        <v>0.01428114335994324</v>
       </c>
     </row>
     <row r="683">
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.02239186085432077</v>
+        <v>0.02239186085432054</v>
       </c>
     </row>
     <row r="684">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>-0.001793955407853987</v>
+        <v>-0.001793955407853876</v>
       </c>
     </row>
     <row r="686">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>-0.008673348495482625</v>
+        <v>-0.008673348495482736</v>
       </c>
     </row>
     <row r="688">
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>-0.005787848824408193</v>
+        <v>-0.005787848824408082</v>
       </c>
     </row>
     <row r="689">
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>-0.004497409192048774</v>
+        <v>-0.004497409192048551</v>
       </c>
     </row>
     <row r="690">
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>-0.01284993193291439</v>
+        <v>-0.0128499319329145</v>
       </c>
     </row>
     <row r="693">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.01412636014713042</v>
+        <v>0.0141263601471302</v>
       </c>
     </row>
     <row r="694">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>-0.0102380435509648</v>
+        <v>-0.01023804355096469</v>
       </c>
     </row>
     <row r="695">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>-0.007638768501796789</v>
+        <v>-0.007638768501796678</v>
       </c>
     </row>
     <row r="701">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.001278553122013637</v>
+        <v>0.001278553122013415</v>
       </c>
     </row>
     <row r="702">
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.001799493698123156</v>
+        <v>0.001799493698123378</v>
       </c>
     </row>
     <row r="703">
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.001041340164624316</v>
+        <v>0.001041340164624094</v>
       </c>
     </row>
     <row r="704">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.0001384351425268715</v>
+        <v>0.0001384351425266495</v>
       </c>
     </row>
     <row r="705">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.005557164339933474</v>
+        <v>0.005557164339933696</v>
       </c>
     </row>
     <row r="706">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>-0.003373726460938586</v>
+        <v>-0.003373726460938697</v>
       </c>
     </row>
     <row r="707">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>-0.00223333803908321</v>
+        <v>-0.002233338039083099</v>
       </c>
     </row>
     <row r="709">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.001478340715997506</v>
+        <v>0.00147834071599795</v>
       </c>
     </row>
     <row r="712">
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>-0.004834084516303183</v>
+        <v>-0.004834084516303294</v>
       </c>
     </row>
     <row r="713">
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.001678295853116962</v>
+        <v>0.00167829585311674</v>
       </c>
     </row>
     <row r="714">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.0004622694345122191</v>
+        <v>0.0004622694345124412</v>
       </c>
     </row>
     <row r="715">
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>-0.009971085621614306</v>
+        <v>-0.009971085621614528</v>
       </c>
     </row>
     <row r="717">
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>-0.0006463753444283515</v>
+        <v>-0.0006463753444280185</v>
       </c>
     </row>
     <row r="718">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.007283761315447279</v>
+        <v>0.007283761315447057</v>
       </c>
     </row>
     <row r="719">
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>-0.008616784170997649</v>
+        <v>-0.008616784170997205</v>
       </c>
     </row>
     <row r="720">
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>-0.01501337566738059</v>
+        <v>-0.0150133756673807</v>
       </c>
     </row>
     <row r="721">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.006439802175853826</v>
+        <v>0.006439802175853382</v>
       </c>
     </row>
     <row r="724">
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.005157354066361641</v>
+        <v>0.005157354066362085</v>
       </c>
     </row>
     <row r="725">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>-0.001691837374784622</v>
+        <v>-0.001691837374784733</v>
       </c>
     </row>
     <row r="727">
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.001251630013585192</v>
+        <v>0.001251630013585414</v>
       </c>
     </row>
     <row r="729">
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.007776677403925403</v>
+        <v>0.007776677403925625</v>
       </c>
     </row>
     <row r="730">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>-0.003938692061451143</v>
+        <v>-0.003938692061451254</v>
       </c>
     </row>
     <row r="731">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>-0.004588615118149786</v>
+        <v>-0.004588615118149897</v>
       </c>
     </row>
     <row r="734">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>-0.003365710899696395</v>
+        <v>-0.003365710899696173</v>
       </c>
     </row>
     <row r="736">
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.00561445844033992</v>
+        <v>0.005614458440339698</v>
       </c>
     </row>
     <row r="737">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.009293784976991626</v>
+        <v>0.009293784976991848</v>
       </c>
     </row>
     <row r="741">
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.002496586118192479</v>
+        <v>0.002496586118192257</v>
       </c>
     </row>
     <row r="742">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>-0.002217952630472309</v>
+        <v>-0.002217952630472197</v>
       </c>
     </row>
     <row r="743">
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>-0.001997225757885079</v>
+        <v>-0.00199722575788519</v>
       </c>
     </row>
     <row r="744">
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.002356835600085372</v>
+        <v>0.002356835600085594</v>
       </c>
     </row>
     <row r="745">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>-0.01808644610890786</v>
+        <v>-0.01808644610890808</v>
       </c>
     </row>
     <row r="746">
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.008650292367807344</v>
+        <v>0.008650292367807122</v>
       </c>
     </row>
     <row r="748">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>-0.01238889369916718</v>
+        <v>-0.01238889369916696</v>
       </c>
     </row>
     <row r="749">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>-0.02004753048270991</v>
+        <v>-0.0200475304827098</v>
       </c>
     </row>
     <row r="751">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>-0.008179916370430473</v>
+        <v>-0.008179916370430584</v>
       </c>
     </row>
     <row r="752">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>-0.008291937939607696</v>
+        <v>-0.008291937939607918</v>
       </c>
     </row>
     <row r="758">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>-0.007575863886706391</v>
+        <v>-0.007575863886706169</v>
       </c>
     </row>
     <row r="759">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.01511910335777378</v>
+        <v>0.015119103357774</v>
       </c>
     </row>
     <row r="760">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.011292204689614</v>
+        <v>0.01129220468961378</v>
       </c>
     </row>
     <row r="761">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.004851290265875496</v>
+        <v>0.004851290265875274</v>
       </c>
     </row>
     <row r="763">
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>-0.0258374187287842</v>
+        <v>-0.02583741872878409</v>
       </c>
     </row>
     <row r="766">
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.001219238059372074</v>
+        <v>0.001219238059372296</v>
       </c>
     </row>
     <row r="769">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.0121654725945668</v>
+        <v>0.01216547259456702</v>
       </c>
     </row>
     <row r="771">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.01265069415996178</v>
+        <v>0.01265069415996156</v>
       </c>
     </row>
     <row r="772">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>-0.002009341238782492</v>
+        <v>-0.002009341238782381</v>
       </c>
     </row>
     <row r="773">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>-0.009169161822561112</v>
+        <v>-0.00916916182256089</v>
       </c>
     </row>
     <row r="774">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.004653099476971345</v>
+        <v>0.004653099476971123</v>
       </c>
     </row>
     <row r="779">
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.002908471172346605</v>
+        <v>0.002908471172346383</v>
       </c>
     </row>
     <row r="783">
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.00306411264095674</v>
+        <v>0.003064112640956962</v>
       </c>
     </row>
     <row r="784">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>-0.006876264618988159</v>
+        <v>-0.00687626461898827</v>
       </c>
     </row>
     <row r="788">
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>-0.004371128133827118</v>
+        <v>-0.004371128133827229</v>
       </c>
     </row>
     <row r="789">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>-0.02962037269060314</v>
+        <v>-0.02962037269060303</v>
       </c>
     </row>
     <row r="792">
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>-0.01795844489313636</v>
+        <v>-0.01795844489313625</v>
       </c>
     </row>
     <row r="793">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>-0.02583203567799441</v>
+        <v>-0.02583203567799452</v>
       </c>
     </row>
     <row r="795">
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.02092119190038755</v>
+        <v>0.02092119190038777</v>
       </c>
     </row>
     <row r="796">
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.01925279482107878</v>
+        <v>0.019252794821079</v>
       </c>
     </row>
     <row r="797">
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>-0.004636184424598455</v>
+        <v>-0.004636184424598566</v>
       </c>
     </row>
     <row r="798">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>-0.01802431996932663</v>
+        <v>-0.01802431996932674</v>
       </c>
     </row>
     <row r="799">
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>-0.01215807615023734</v>
+        <v>-0.01215807615023745</v>
       </c>
     </row>
     <row r="802">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>-0.0133540234172852</v>
+        <v>-0.01335402341728531</v>
       </c>
     </row>
     <row r="807">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>-0.006068360018442798</v>
+        <v>-0.006068360018442465</v>
       </c>
     </row>
     <row r="808">
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>-0.01867016110677344</v>
+        <v>-0.01867016110677333</v>
       </c>
     </row>
     <row r="810">
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>-0.01807505154975864</v>
+        <v>-0.01807505154975886</v>
       </c>
     </row>
     <row r="811">
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.01807335822384504</v>
+        <v>0.01807335822384482</v>
       </c>
     </row>
     <row r="812">
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.01281619668621081</v>
+        <v>0.01281619668621103</v>
       </c>
     </row>
     <row r="813">
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.002738229549205773</v>
+        <v>0.002738229549205551</v>
       </c>
     </row>
     <row r="814">
@@ -8550,7 +8550,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.002539037622713014</v>
+        <v>0.002539037622713236</v>
       </c>
     </row>
     <row r="815">
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>-0.01171874014931118</v>
+        <v>-0.01171874014931107</v>
       </c>
     </row>
     <row r="824">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.01436321736450141</v>
+        <v>0.01436321736450119</v>
       </c>
     </row>
     <row r="825">
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>-0.008404541488628126</v>
+        <v>-0.008404541488628348</v>
       </c>
     </row>
     <row r="826">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.005728896102225267</v>
+        <v>0.005728896102225933</v>
       </c>
     </row>
     <row r="827">
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>-0.0005655845203756948</v>
+        <v>-0.0005655845203760279</v>
       </c>
     </row>
     <row r="828">
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>-0.004898818952927875</v>
+        <v>-0.004898818952928097</v>
       </c>
     </row>
     <row r="830">
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.006171723872627766</v>
+        <v>0.006171723872627544</v>
       </c>
     </row>
     <row r="831">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.004345547872978139</v>
+        <v>0.004345547872978583</v>
       </c>
     </row>
     <row r="832">
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>-0.01791946162837665</v>
+        <v>-0.01791946162837688</v>
       </c>
     </row>
     <row r="836">
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>-0.001097866954190896</v>
+        <v>-0.001097866954190785</v>
       </c>
     </row>
     <row r="837">
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>-0.02969843724133736</v>
+        <v>-0.02969843724133747</v>
       </c>
     </row>
     <row r="838">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>-0.002936994804152548</v>
+        <v>-0.002936994804152326</v>
       </c>
     </row>
     <row r="839">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.00709916033068958</v>
+        <v>0.007099160330689358</v>
       </c>
     </row>
     <row r="840">
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.00730898123533863</v>
+        <v>0.007308981235338852</v>
       </c>
     </row>
     <row r="842">
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.00250768881841279</v>
+        <v>0.002507688818412568</v>
       </c>
     </row>
     <row r="843">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>-0.009032861983044427</v>
+        <v>-0.009032861983044538</v>
       </c>
     </row>
     <row r="845">
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.003939646246366557</v>
+        <v>0.003939646246366779</v>
       </c>
     </row>
     <row r="846">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>-0.005961273014209678</v>
+        <v>-0.0059612730142099</v>
       </c>
     </row>
     <row r="847">
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>-0.009721085996666656</v>
+        <v>-0.009721085996666545</v>
       </c>
     </row>
     <row r="848">
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>-0.0183999383002571</v>
+        <v>-0.01839993830025699</v>
       </c>
     </row>
     <row r="852">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.01774275347314802</v>
+        <v>0.01774275347314846</v>
       </c>
     </row>
     <row r="853">
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.0225317236015441</v>
+        <v>0.02253172360154365</v>
       </c>
     </row>
     <row r="854">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.001903142640189426</v>
+        <v>0.001903142640189648</v>
       </c>
     </row>
     <row r="855">
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>-0.02427235157468333</v>
+        <v>-0.02427235157468344</v>
       </c>
     </row>
     <row r="859">
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.00667560526956823</v>
+        <v>0.006675605269568452</v>
       </c>
     </row>
     <row r="860">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>-0.02041433200672971</v>
+        <v>-0.0204143320067296</v>
       </c>
     </row>
     <row r="861">
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>-8.407791363873596e-05</v>
+        <v>-8.407791363862493e-05</v>
       </c>
     </row>
     <row r="863">
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.02006744836312491</v>
+        <v>0.02006744836312468</v>
       </c>
     </row>
     <row r="864">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>-0.001978164576057706</v>
+        <v>-0.001978164576057595</v>
       </c>
     </row>
     <row r="865">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>-0.001256135137375547</v>
+        <v>-0.001256135137375436</v>
       </c>
     </row>
     <row r="866">
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.02207696058347031</v>
+        <v>0.02207696058347053</v>
       </c>
     </row>
     <row r="867">
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>-0.02419158135423183</v>
+        <v>-0.02419158135423216</v>
       </c>
     </row>
     <row r="868">
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>-0.03085535503197578</v>
+        <v>-0.03085535503197601</v>
       </c>
     </row>
     <row r="870">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>-0.01185892682263157</v>
+        <v>-0.01185892682263123</v>
       </c>
     </row>
     <row r="872">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>-0.0528743060367578</v>
+        <v>-0.05287430603675802</v>
       </c>
     </row>
     <row r="873">
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.009028997517175785</v>
+        <v>0.009028997517176229</v>
       </c>
     </row>
     <row r="874">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>-0.0267646488334301</v>
+        <v>-0.02676464883343044</v>
       </c>
     </row>
     <row r="875">
@@ -9190,7 +9190,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.01475118668415432</v>
+        <v>0.01475118668415409</v>
       </c>
     </row>
     <row r="879">
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>-0.002546475484619726</v>
+        <v>-0.002546475484619615</v>
       </c>
     </row>
     <row r="880">
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>-0.02687770664946465</v>
+        <v>-0.02687770664946454</v>
       </c>
     </row>
     <row r="881">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.002871707314528349</v>
+        <v>0.002871707314528127</v>
       </c>
     </row>
     <row r="882">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.002491936752931023</v>
+        <v>0.002491936752930801</v>
       </c>
     </row>
     <row r="883">
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.0131129859977368</v>
+        <v>0.01311298599773725</v>
       </c>
     </row>
     <row r="887">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>-0.01574620650592595</v>
+        <v>-0.01574620650592606</v>
       </c>
     </row>
     <row r="888">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.01587468231271205</v>
+        <v>0.01587468231271227</v>
       </c>
     </row>
     <row r="891">
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.008161032176681626</v>
+        <v>0.008161032176681848</v>
       </c>
     </row>
     <row r="892">
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.006381166397700921</v>
+        <v>0.006381166397700699</v>
       </c>
     </row>
     <row r="893">
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>-0.007617557027504995</v>
+        <v>-0.007617557027505106</v>
       </c>
     </row>
     <row r="895">
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>-0.005248251859024</v>
+        <v>-0.005248251859024111</v>
       </c>
     </row>
     <row r="897">
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>-0.02473090744930528</v>
+        <v>-0.02473090744930506</v>
       </c>
     </row>
     <row r="898">
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>-0.009382867163117536</v>
+        <v>-0.009382867163117647</v>
       </c>
     </row>
     <row r="899">
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.01452034972315719</v>
+        <v>0.01452034972315697</v>
       </c>
     </row>
     <row r="900">
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>-0.04536117353824243</v>
+        <v>-0.04536117353824209</v>
       </c>
     </row>
     <row r="903">
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.02078951518438843</v>
+        <v>0.02078951518438821</v>
       </c>
     </row>
     <row r="904">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.01195971654985395</v>
+        <v>0.01195971654985373</v>
       </c>
     </row>
     <row r="905">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.01003299571925576</v>
+        <v>0.01003299571925598</v>
       </c>
     </row>
     <row r="906">
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>-0.008609047926023017</v>
+        <v>-0.008609047926023128</v>
       </c>
     </row>
     <row r="908">
@@ -9530,7 +9530,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>-0.003512367374536085</v>
+        <v>-0.003512367374535974</v>
       </c>
     </row>
     <row r="913">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.01283923671550879</v>
+        <v>0.01283923671550857</v>
       </c>
     </row>
     <row r="915">
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>-0.007180387489377216</v>
+        <v>-0.007180387489376883</v>
       </c>
     </row>
     <row r="916">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.01348506982872055</v>
+        <v>0.01348506982872011</v>
       </c>
     </row>
     <row r="917">
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>-0.01614598427896952</v>
+        <v>-0.01614598427896963</v>
       </c>
     </row>
     <row r="920">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>-0.015840995042679</v>
+        <v>-0.01584099504267866</v>
       </c>
     </row>
     <row r="922">
@@ -9630,7 +9630,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.007289724862951763</v>
+        <v>0.007289724862951541</v>
       </c>
     </row>
     <row r="923">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>-0.003787806878785105</v>
+        <v>-0.003787806878785216</v>
       </c>
     </row>
     <row r="927">
@@ -9680,7 +9680,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>-0.03074337549969519</v>
+        <v>-0.03074337549969508</v>
       </c>
     </row>
     <row r="928">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>-0.02324862960191743</v>
+        <v>-0.02324862960191731</v>
       </c>
     </row>
     <row r="931">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.02785003639245942</v>
+        <v>0.0278500363924592</v>
       </c>
     </row>
     <row r="932">
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.02439593822905972</v>
+        <v>0.02439593822905994</v>
       </c>
     </row>
     <row r="937">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>-0.009250610430399098</v>
+        <v>-0.009250610430399209</v>
       </c>
     </row>
     <row r="939">
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.01210777571085631</v>
+        <v>0.01210777571085608</v>
       </c>
     </row>
     <row r="940">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.0004441928617495705</v>
+        <v>0.0004441928617497926</v>
       </c>
     </row>
     <row r="941">
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>-0.005738518626669409</v>
+        <v>-0.005738518626669742</v>
       </c>
     </row>
     <row r="943">
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.008592703618164554</v>
+        <v>0.008592703618164776</v>
       </c>
     </row>
     <row r="944">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.0001745891805255972</v>
+        <v>0.0001745891805253752</v>
       </c>
     </row>
     <row r="945">
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.009873618828450947</v>
+        <v>0.009873618828451169</v>
       </c>
     </row>
     <row r="946">
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.02074903899339464</v>
+        <v>0.02074903899339442</v>
       </c>
     </row>
     <row r="947">
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>-0.05224396074816096</v>
+        <v>-0.05224396074816073</v>
       </c>
     </row>
     <row r="948">
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.02348694933766216</v>
+        <v>0.02348694933766238</v>
       </c>
     </row>
     <row r="949">
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>-0.006450835012680067</v>
+        <v>-0.006450835012679845</v>
       </c>
     </row>
     <row r="957">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>-0.005468739357935792</v>
+        <v>-0.005468739357936014</v>
       </c>
     </row>
     <row r="958">
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.003773654668152382</v>
+        <v>0.003773654668152604</v>
       </c>
     </row>
     <row r="961">
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.009063197570568171</v>
+        <v>0.009063197570567949</v>
       </c>
     </row>
     <row r="964">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.002906742145760033</v>
+        <v>0.002906742145760699</v>
       </c>
     </row>
     <row r="967">
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>-0.01278610669300329</v>
+        <v>-0.01278610669300373</v>
       </c>
     </row>
     <row r="968">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>-0.02183379252242756</v>
+        <v>-0.02183379252242745</v>
       </c>
     </row>
     <row r="973">
@@ -10140,7 +10140,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>-0.002232229131368668</v>
+        <v>-0.002232229131369001</v>
       </c>
     </row>
     <row r="974">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>-0.0006225305559334204</v>
+        <v>-0.0006225305559331984</v>
       </c>
     </row>
     <row r="975">
@@ -10160,7 +10160,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.009187022831969482</v>
+        <v>0.00918702283196926</v>
       </c>
     </row>
     <row r="976">
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>-0.002596754297616855</v>
+        <v>-0.002596754297616743</v>
       </c>
     </row>
     <row r="977">
@@ -10180,7 +10180,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>-0.01479631283169502</v>
+        <v>-0.01479631283169491</v>
       </c>
     </row>
     <row r="978">
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.009762321520557116</v>
+        <v>0.009762321520557338</v>
       </c>
     </row>
     <row r="979">
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>-0.003336029333235513</v>
+        <v>-0.003336029333235624</v>
       </c>
     </row>
     <row r="980">
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>-0.01013931298710924</v>
+        <v>-0.01013931298710946</v>
       </c>
     </row>
     <row r="981">
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>-0.01033523934873337</v>
+        <v>-0.01033523934873315</v>
       </c>
     </row>
     <row r="982">
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>-0.0036542717169602</v>
+        <v>-0.003654271716959978</v>
       </c>
     </row>
     <row r="985">
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.02698576578698986</v>
+        <v>0.02698576578698964</v>
       </c>
     </row>
     <row r="986">
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>-0.01160389346474755</v>
+        <v>-0.01160389346474744</v>
       </c>
     </row>
     <row r="989">
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>-0.007616814754117129</v>
+        <v>-0.007616814754117462</v>
       </c>
     </row>
     <row r="991">
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.005893542318945011</v>
+        <v>0.005893542318945233</v>
       </c>
     </row>
     <row r="992">
@@ -10330,7 +10330,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.002679644344423471</v>
+        <v>0.002679644344423249</v>
       </c>
     </row>
     <row r="993">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>-0.00227283775159326</v>
+        <v>-0.002272837751593149</v>
       </c>
     </row>
     <row r="995">
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>-0.03577576283525974</v>
+        <v>-0.03577576283525963</v>
       </c>
     </row>
     <row r="997">
@@ -10380,7 +10380,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>-0.009313003888210991</v>
+        <v>-0.009313003888211102</v>
       </c>
     </row>
     <row r="998">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.01616773732429877</v>
+        <v>0.01616773732429855</v>
       </c>
     </row>
     <row r="1001">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.01649921637084928</v>
+        <v>0.0164992163708495</v>
       </c>
     </row>
     <row r="1002">
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.0160973127483226</v>
+        <v>0.01609731274832282</v>
       </c>
     </row>
     <row r="1003">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>-0.008720930572255092</v>
+        <v>-0.008720930572255314</v>
       </c>
     </row>
     <row r="1005">
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.003768565792003242</v>
+        <v>0.003768565792003464</v>
       </c>
     </row>
     <row r="1006">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.01325321685440484</v>
+        <v>0.01325321685440461</v>
       </c>
     </row>
     <row r="1007">
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>-0.006748188578202474</v>
+        <v>-0.006748188578202252</v>
       </c>
     </row>
     <row r="1008">
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>-0.01018023403800961</v>
+        <v>-0.01018023403800983</v>
       </c>
     </row>
     <row r="1010">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.008049484721175171</v>
+        <v>0.008049484721174949</v>
       </c>
     </row>
     <row r="1011">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.01592332223870074</v>
+        <v>0.01592332223870119</v>
       </c>
     </row>
     <row r="1012">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>-0.01926570719130194</v>
+        <v>-0.01926570719130216</v>
       </c>
     </row>
     <row r="1013">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>-0.003180039434085624</v>
+        <v>-0.003180039434085402</v>
       </c>
     </row>
     <row r="1014">
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.007635541687579295</v>
+        <v>0.007635541687578851</v>
       </c>
     </row>
     <row r="1015">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.009074221255804371</v>
+        <v>0.009074221255804593</v>
       </c>
     </row>
     <row r="1016">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>-0.01042932187807877</v>
+        <v>-0.01042932187807899</v>
       </c>
     </row>
     <row r="1017">
@@ -10590,7 +10590,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.007016031264255984</v>
+        <v>0.007016031264256206</v>
       </c>
     </row>
     <row r="1019">
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>-0.001569921247416173</v>
+        <v>-0.001569921247416395</v>
       </c>
     </row>
     <row r="1020">
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.007113886388666613</v>
+        <v>0.007113886388666835</v>
       </c>
     </row>
     <row r="1021">
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>-0.01550002662593475</v>
+        <v>-0.01550002662593453</v>
       </c>
     </row>
     <row r="1030">
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.008313027443095811</v>
+        <v>0.008313027443095589</v>
       </c>
     </row>
     <row r="1032">
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>-0.002777189986378992</v>
+        <v>-0.002777189986378659</v>
       </c>
     </row>
     <row r="1033">
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>-0.01658249273285239</v>
+        <v>-0.01658249273285262</v>
       </c>
     </row>
     <row r="1034">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>-0.01044878661851334</v>
+        <v>-0.01044878661851323</v>
       </c>
     </row>
     <row r="1035">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.03290266078301607</v>
+        <v>0.03290266078301585</v>
       </c>
     </row>
     <row r="1042">
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.0193826718183896</v>
+        <v>0.01938267181838915</v>
       </c>
     </row>
     <row r="1044">
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.02365679043802982</v>
+        <v>0.02365679043803048</v>
       </c>
     </row>
     <row r="1045">
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.002429051960828543</v>
+        <v>0.002429051960828321</v>
       </c>
     </row>
     <row r="1046">
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>-0.002170950630672852</v>
+        <v>-0.00217095063067263</v>
       </c>
     </row>
     <row r="1048">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>-0.002401417587939325</v>
+        <v>-0.002401417587939769</v>
       </c>
     </row>
     <row r="1049">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>-0.01334137027498505</v>
+        <v>-0.01334137027498472</v>
       </c>
     </row>
     <row r="1051">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.02745808023947638</v>
+        <v>0.02745808023947593</v>
       </c>
     </row>
     <row r="1052">
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>-0.004396291537364205</v>
+        <v>-0.004396291537364094</v>
       </c>
     </row>
     <row r="1053">
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.02710080464807763</v>
+        <v>0.02710080464807785</v>
       </c>
     </row>
     <row r="1056">
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.01371031064314976</v>
+        <v>0.01371031064314954</v>
       </c>
     </row>
     <row r="1057">
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.01447623717756286</v>
+        <v>0.01447623717756308</v>
       </c>
     </row>
     <row r="1059">
@@ -11040,7 +11040,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.002582242337049401</v>
+        <v>0.002582242337049623</v>
       </c>
     </row>
     <row r="1064">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.0001978009999252794</v>
+        <v>0.0001978009999250574</v>
       </c>
     </row>
     <row r="1065">
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>-0.007985798919503795</v>
+        <v>-0.007985798919504017</v>
       </c>
     </row>
     <row r="1067">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>-0.01942554006675412</v>
+        <v>-0.01942554006675368</v>
       </c>
     </row>
     <row r="1071">
@@ -11120,7 +11120,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>-0.007317974766920976</v>
+        <v>-0.007317974766921531</v>
       </c>
     </row>
     <row r="1072">
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>-0.008653895420259738</v>
+        <v>-0.008653895420259294</v>
       </c>
     </row>
     <row r="1074">
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>-0.001970124550798702</v>
+        <v>-0.00197012455079848</v>
       </c>
     </row>
     <row r="1075">
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.01686443716937003</v>
+        <v>0.01686443716936981</v>
       </c>
     </row>
     <row r="1076">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.003170386643204015</v>
+        <v>0.003170386643203793</v>
       </c>
     </row>
     <row r="1077">
@@ -11180,7 +11180,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.01163798284475992</v>
+        <v>0.01163798284476014</v>
       </c>
     </row>
     <row r="1078">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.0139170459132929</v>
+        <v>0.01391704591329268</v>
       </c>
     </row>
     <row r="1079">
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.0008551475142153375</v>
+        <v>0.0008551475142155596</v>
       </c>
     </row>
     <row r="1082">
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>-0.003533328305863725</v>
+        <v>-0.003533328305863948</v>
       </c>
     </row>
     <row r="1083">
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.002529683784929793</v>
+        <v>0.002529683784930015</v>
       </c>
     </row>
     <row r="1085">
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>-0.001032965158952015</v>
+        <v>-0.001032965158951793</v>
       </c>
     </row>
     <row r="1088">
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>-0.01468150187955197</v>
+        <v>-0.01468150187955219</v>
       </c>
     </row>
     <row r="1089">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.01283156005325359</v>
+        <v>0.01283156005325381</v>
       </c>
     </row>
     <row r="1091">
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>-0.008730432033194568</v>
+        <v>-0.00873043203319479</v>
       </c>
     </row>
     <row r="1092">
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>-0.01373945636964857</v>
+        <v>-0.01373945636964846</v>
       </c>
     </row>
     <row r="1094">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>-0.01251152387576315</v>
+        <v>-0.01251152387576293</v>
       </c>
     </row>
     <row r="1097">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>-0.006574370112642169</v>
+        <v>-0.006574370112642058</v>
       </c>
     </row>
     <row r="1098">
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.006809366944742656</v>
+        <v>0.006809366944742212</v>
       </c>
     </row>
     <row r="1099">
@@ -11420,7 +11420,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.01089441711403216</v>
+        <v>0.01089441711403238</v>
       </c>
     </row>
     <row r="1102">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.001590331943461587</v>
+        <v>0.001590331943461809</v>
       </c>
     </row>
     <row r="1104">
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.002661212489138309</v>
+        <v>0.002661212489138087</v>
       </c>
     </row>
     <row r="1105">
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.001064878622267118</v>
+        <v>0.00106487862226734</v>
       </c>
     </row>
     <row r="1106">
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>0.002485182301342093</v>
+        <v>0.002485182301341871</v>
       </c>
     </row>
     <row r="1108">
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>-0.0008406560288554132</v>
+        <v>-0.0008406560288556353</v>
       </c>
     </row>
     <row r="1109">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>-0.00996827470713646</v>
+        <v>-0.009968274707136238</v>
       </c>
     </row>
     <row r="1110">
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>0.001029138406536179</v>
+        <v>0.001029138406535957</v>
       </c>
     </row>
     <row r="1112">
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>0.01075084921676273</v>
+        <v>0.01075084921676317</v>
       </c>
     </row>
     <row r="1113">
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.02479351554263043</v>
+        <v>0.02479351554263021</v>
       </c>
     </row>
     <row r="1114">
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>0.006132342922674061</v>
+        <v>0.006132342922673839</v>
       </c>
     </row>
     <row r="1117">
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.004463416465650738</v>
+        <v>0.00446341646565096</v>
       </c>
     </row>
     <row r="1118">
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.0132957174344086</v>
+        <v>0.01329571743440883</v>
       </c>
     </row>
     <row r="1124">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>0.003471946295962036</v>
+        <v>0.003471946295961814</v>
       </c>
     </row>
     <row r="1125">
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>-0.003251827210925207</v>
+        <v>-0.003251827210925318</v>
       </c>
     </row>
     <row r="1133">
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>0.007155059054588575</v>
+        <v>0.007155059054589241</v>
       </c>
     </row>
     <row r="1135">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>-0.00129833778899402</v>
+        <v>-0.001298337788994131</v>
       </c>
     </row>
     <row r="1137">
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>0.003635445179374974</v>
+        <v>0.003635445179375196</v>
       </c>
     </row>
     <row r="1139">
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>-0.02215157709837268</v>
+        <v>-0.02215157709837312</v>
       </c>
     </row>
     <row r="1140">
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>0.0156449369856968</v>
+        <v>0.01564493698569702</v>
       </c>
     </row>
     <row r="1141">
@@ -11830,7 +11830,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>-0.01621944189213786</v>
+        <v>-0.01621944189213764</v>
       </c>
     </row>
     <row r="1143">
@@ -11840,7 +11840,7 @@
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>0.004813116139540163</v>
+        <v>0.004813116139539941</v>
       </c>
     </row>
     <row r="1144">
@@ -11870,7 +11870,7 @@
         </is>
       </c>
       <c r="B1146" t="n">
-        <v>-0.01639520812226813</v>
+        <v>-0.01639520812226791</v>
       </c>
     </row>
     <row r="1147">
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>0.01493066881486649</v>
+        <v>0.01493066881486627</v>
       </c>
     </row>
     <row r="1148">
@@ -11900,7 +11900,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>0.02692721334073211</v>
+        <v>0.02692721334073189</v>
       </c>
     </row>
     <row r="1150">
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>-0.00638276161675877</v>
+        <v>-0.006382761616758659</v>
       </c>
     </row>
     <row r="1152">
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>-0.003941316579944454</v>
+        <v>-0.003941316579944232</v>
       </c>
     </row>
     <row r="1153">
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>0.01130903820118001</v>
+        <v>0.01130903820117979</v>
       </c>
     </row>
     <row r="1154">
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>-0.02426953109935848</v>
+        <v>-0.0242695310993587</v>
       </c>
     </row>
     <row r="1155">
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>-0.007084652982432216</v>
+        <v>-0.007084652982431994</v>
       </c>
     </row>
     <row r="1156">
@@ -11970,7 +11970,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>-0.0113599339599616</v>
+        <v>-0.01135993395996127</v>
       </c>
     </row>
     <row r="1157">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>0.01091823985512885</v>
+        <v>0.01091823985512819</v>
       </c>
     </row>
     <row r="1158">
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>0.009424615194588482</v>
+        <v>0.009424615194588259</v>
       </c>
     </row>
     <row r="1159">
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>-0.01410855724595728</v>
+        <v>-0.01410855724595705</v>
       </c>
     </row>
     <row r="1160">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>-0.01645137341079661</v>
+        <v>-0.01645137341079639</v>
       </c>
     </row>
     <row r="1163">
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>-0.002214190622527923</v>
+        <v>-0.002214190622528145</v>
       </c>
     </row>
     <row r="1164">
@@ -12080,7 +12080,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>-0.002807021897575313</v>
+        <v>-0.002807021897575757</v>
       </c>
     </row>
     <row r="1168">
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>0.0002924664760584061</v>
+        <v>0.0002924664760588502</v>
       </c>
     </row>
     <row r="1169">
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>-0.03773790998610349</v>
+        <v>-0.03773790998610327</v>
       </c>
     </row>
     <row r="1172">
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>-0.03382134807378634</v>
+        <v>-0.03382134807378645</v>
       </c>
     </row>
     <row r="1174">
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>-0.001014003564860366</v>
+        <v>-0.001014003564860144</v>
       </c>
     </row>
     <row r="1176">
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>0.0342499948837256</v>
+        <v>0.03424999488372538</v>
       </c>
     </row>
     <row r="1177">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>0.009573352655583678</v>
+        <v>0.0095733526555839</v>
       </c>
     </row>
     <row r="1178">
@@ -12200,7 +12200,7 @@
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>0.02090134157089141</v>
+        <v>0.02090134157089096</v>
       </c>
     </row>
     <row r="1180">
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>-0.02424283933234717</v>
+        <v>-0.02424283933234672</v>
       </c>
     </row>
     <row r="1181">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>0.008380706573581254</v>
+        <v>0.008380706573581032</v>
       </c>
     </row>
     <row r="1182">
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>-0.01125125306769059</v>
+        <v>-0.01125125306769037</v>
       </c>
     </row>
     <row r="1184">
@@ -12250,7 +12250,7 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>0.01206354093523987</v>
+        <v>0.01206354093523965</v>
       </c>
     </row>
     <row r="1185">
@@ -12320,7 +12320,7 @@
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>0.007249958626888597</v>
+        <v>0.007249958626888819</v>
       </c>
     </row>
     <row r="1192">
@@ -12330,7 +12330,7 @@
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>0.00175509614035696</v>
+        <v>0.001755096140356738</v>
       </c>
     </row>
     <row r="1193">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>-0.008866235407161582</v>
+        <v>-0.00886623540716136</v>
       </c>
     </row>
     <row r="1195">
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>0.005827947192266869</v>
+        <v>0.005827947192266647</v>
       </c>
     </row>
     <row r="1196">
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>0.0009722448043001375</v>
+        <v>0.0009722448043003595</v>
       </c>
     </row>
     <row r="1197">
@@ -12380,7 +12380,7 @@
         </is>
       </c>
       <c r="B1197" t="n">
-        <v>0.01406591753180231</v>
+        <v>0.01406591753180186</v>
       </c>
     </row>
     <row r="1198">
@@ -12390,7 +12390,7 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>-0.0004356370445006696</v>
+        <v>-0.0004356370445005586</v>
       </c>
     </row>
     <row r="1199">
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>0.00790010449480949</v>
+        <v>0.007900104494809268</v>
       </c>
     </row>
     <row r="1200">
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>-0.02855618552534611</v>
+        <v>-0.02855618552534589</v>
       </c>
     </row>
     <row r="1201">
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="B1201" t="n">
-        <v>0.003826411940607066</v>
+        <v>0.003826411940607288</v>
       </c>
     </row>
     <row r="1202">
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="B1204" t="n">
-        <v>0.004397165248582136</v>
+        <v>0.004397165248582358</v>
       </c>
     </row>
     <row r="1205">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="B1205" t="n">
-        <v>0.01258477309344874</v>
+        <v>0.01258477309344852</v>
       </c>
     </row>
     <row r="1206">
@@ -12480,7 +12480,7 @@
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>-0.006475023406140035</v>
+        <v>-0.006475023406140257</v>
       </c>
     </row>
     <row r="1208">
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>0.01115562520194868</v>
+        <v>0.0111556252019489</v>
       </c>
     </row>
     <row r="1209">
@@ -12500,7 +12500,7 @@
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>0.0007441065345603626</v>
+        <v>0.0007441065345601405</v>
       </c>
     </row>
     <row r="1210">
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>-0.001614555508234972</v>
+        <v>-0.00161455550823475</v>
       </c>
     </row>
     <row r="1211">
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B1212" t="n">
-        <v>-0.02676461411327202</v>
+        <v>-0.02676461411327224</v>
       </c>
     </row>
     <row r="1213">
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>0.02761529311920641</v>
+        <v>0.02761529311920663</v>
       </c>
     </row>
     <row r="1214">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>0.01562053719362</v>
+        <v>0.01562053719362022</v>
       </c>
     </row>
     <row r="1216">
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>0.01438787600000224</v>
+        <v>0.0143878760000018</v>
       </c>
     </row>
     <row r="1217">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>0.003388352163433028</v>
+        <v>0.00338835216343325</v>
       </c>
     </row>
     <row r="1219">
@@ -12600,7 +12600,7 @@
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>-0.004887538168462879</v>
+        <v>-0.004887538168463101</v>
       </c>
     </row>
     <row r="1220">
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>-0.000575697811410647</v>
+        <v>-0.000575697811410425</v>
       </c>
     </row>
     <row r="1221">
@@ -12630,7 +12630,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>-0.0006144229793900724</v>
+        <v>-0.0006144229793902944</v>
       </c>
     </row>
     <row r="1223">
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>0.01288513344958941</v>
+        <v>0.01288513344958964</v>
       </c>
     </row>
     <row r="1224">
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>-0.003713523724295009</v>
+        <v>-0.003713523724295342</v>
       </c>
     </row>
     <row r="1225">
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>0.009037734687209031</v>
+        <v>0.009037734687209253</v>
       </c>
     </row>
     <row r="1226">
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>-0.002934551551948439</v>
+        <v>-0.00293455155194855</v>
       </c>
     </row>
     <row r="1227">
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="B1227" t="n">
-        <v>0.001281120210017805</v>
+        <v>0.001281120210018249</v>
       </c>
     </row>
     <row r="1228">
@@ -12690,7 +12690,7 @@
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>0.003678496091783945</v>
+        <v>0.003678496091783723</v>
       </c>
     </row>
     <row r="1229">
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>-0.01718553996961392</v>
+        <v>-0.01718553996961369</v>
       </c>
     </row>
     <row r="1231">
@@ -12730,7 +12730,7 @@
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>-0.001265598298209381</v>
+        <v>-0.001265598298209603</v>
       </c>
     </row>
     <row r="1233">
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>0.01004728775074049</v>
+        <v>0.01004728775074071</v>
       </c>
     </row>
     <row r="1234">
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>0.003337183657649234</v>
+        <v>0.003337183657648568</v>
       </c>
     </row>
     <row r="1237">
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>0.001035445920764433</v>
+        <v>0.001035445920764877</v>
       </c>
     </row>
     <row r="1238">
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>-0.006060841025893882</v>
+        <v>-0.006060841025893771</v>
       </c>
     </row>
     <row r="1239">
@@ -12800,7 +12800,7 @@
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>-0.007807938764420652</v>
+        <v>-0.007807938764420763</v>
       </c>
     </row>
     <row r="1240">
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>-0.00856986352139455</v>
+        <v>-0.008569863521394772</v>
       </c>
     </row>
     <row r="1241">
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>-0.005913908129421941</v>
+        <v>-0.005913908129421719</v>
       </c>
     </row>
     <row r="1242">
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>-0.0148687268763732</v>
+        <v>-0.01486872687637297</v>
       </c>
     </row>
     <row r="1245">
@@ -12880,7 +12880,7 @@
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>0.002431303661456274</v>
+        <v>0.002431303661456052</v>
       </c>
     </row>
     <row r="1248">
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>-0.003687107598763117</v>
+        <v>-0.003687107598762895</v>
       </c>
     </row>
     <row r="1249">
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>-0.008545212717551487</v>
+        <v>-0.008545212717551709</v>
       </c>
     </row>
     <row r="1250">
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>0.0210296024490999</v>
+        <v>0.02102960244910035</v>
       </c>
     </row>
     <row r="1251">
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>0.001416083513104072</v>
+        <v>0.001416083513103628</v>
       </c>
     </row>
     <row r="1252">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>-0.009933317999790581</v>
+        <v>-0.009933317999790248</v>
       </c>
     </row>
     <row r="1253">
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>-0.0001153766708044124</v>
+        <v>-0.0001153766708046344</v>
       </c>
     </row>
     <row r="1254">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>-0.00888067028540207</v>
+        <v>-0.008880670285401959</v>
       </c>
     </row>
     <row r="1256">
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>-0.02320558054645838</v>
+        <v>-0.0232055805464586</v>
       </c>
     </row>
     <row r="1257">
@@ -12990,7 +12990,7 @@
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>0.03925026505610218</v>
+        <v>0.03925026505610241</v>
       </c>
     </row>
     <row r="1259">
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>0.01149084295381608</v>
+        <v>0.01149084295381586</v>
       </c>
     </row>
     <row r="1260">
@@ -13020,7 +13020,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>0.003584620577915532</v>
+        <v>0.00358462057791531</v>
       </c>
     </row>
     <row r="1262">
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>0.01271317662088678</v>
+        <v>0.012713176620887</v>
       </c>
     </row>
     <row r="1263">
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>0.003509231816038794</v>
+        <v>0.003509231816038572</v>
       </c>
     </row>
     <row r="1265">
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>0.000880763589701683</v>
+        <v>0.000880763589701905</v>
       </c>
     </row>
     <row r="1268">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>-0.004473820029848197</v>
+        <v>-0.004473820029848419</v>
       </c>
     </row>
     <row r="1269">
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>0.0003759903482252192</v>
+        <v>0.0003759903482249971</v>
       </c>
     </row>
     <row r="1272">
@@ -13130,7 +13130,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>0.006711500491789701</v>
+        <v>0.006711500491790146</v>
       </c>
     </row>
     <row r="1273">
@@ -13160,7 +13160,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>-0.012480431763911</v>
+        <v>-0.01248043176391123</v>
       </c>
     </row>
     <row r="1276">
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>0.01257045717820637</v>
+        <v>0.01257045717820682</v>
       </c>
     </row>
     <row r="1277">
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>0.004350892783121729</v>
+        <v>0.004350892783121951</v>
       </c>
     </row>
     <row r="1281">
@@ -13220,7 +13220,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>-0.02081171127619441</v>
+        <v>-0.02081171127619463</v>
       </c>
     </row>
     <row r="1282">
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>0.00267150415617734</v>
+        <v>0.002671504156177118</v>
       </c>
     </row>
     <row r="1284">
@@ -13250,7 +13250,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>0.008764262056524252</v>
+        <v>0.008764262056524474</v>
       </c>
     </row>
     <row r="1285">
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>-0.003907012714317037</v>
+        <v>-0.003907012714316815</v>
       </c>
     </row>
     <row r="1287">
@@ -13290,7 +13290,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>-0.01222493945594971</v>
+        <v>-0.01222493945594993</v>
       </c>
     </row>
     <row r="1289">
@@ -13300,7 +13300,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>-0.01818179788212337</v>
+        <v>-0.0181817978821236</v>
       </c>
     </row>
     <row r="1290">
@@ -13320,7 +13320,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>-0.02462303712567271</v>
+        <v>-0.0246230371256726</v>
       </c>
     </row>
     <row r="1292">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>0.03303143928735763</v>
+        <v>0.03303143928735786</v>
       </c>
     </row>
     <row r="1293">
@@ -13340,7 +13340,7 @@
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>0.02309150347723654</v>
+        <v>0.02309150347723632</v>
       </c>
     </row>
     <row r="1294">
@@ -13350,7 +13350,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>0.004252151122708492</v>
+        <v>0.004252151122708936</v>
       </c>
     </row>
     <row r="1295">
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>0.0147805449236047</v>
+        <v>0.01478054492360403</v>
       </c>
     </row>
     <row r="1296">
@@ -13370,7 +13370,7 @@
         </is>
       </c>
       <c r="B1296" t="n">
-        <v>0.004813630221792042</v>
+        <v>0.004813630221792264</v>
       </c>
     </row>
     <row r="1297">
@@ -13380,7 +13380,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>-0.001930876090826872</v>
+        <v>-0.001930876090826761</v>
       </c>
     </row>
     <row r="1298">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>0.01170853824020912</v>
+        <v>0.0117085382402089</v>
       </c>
     </row>
     <row r="1301">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>0.01107774715226717</v>
+        <v>0.01107774715226761</v>
       </c>
     </row>
     <row r="1302">
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>0.009678606706172044</v>
+        <v>0.0096786067061716</v>
       </c>
     </row>
     <row r="1303">
@@ -13450,7 +13450,7 @@
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>-0.003762180781537783</v>
+        <v>-0.003762180781537561</v>
       </c>
     </row>
     <row r="1305">
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>0.004161192416284765</v>
+        <v>0.004161192416284543</v>
       </c>
     </row>
     <row r="1306">
@@ -13480,7 +13480,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>-0.0004902150543658612</v>
+        <v>-0.0004902150543663053</v>
       </c>
     </row>
     <row r="1308">
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>0.01335196167070252</v>
+        <v>0.01335196167070318</v>
       </c>
     </row>
     <row r="1309">
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>-0.007480463170962626</v>
+        <v>-0.007480463170962848</v>
       </c>
     </row>
     <row r="1310">
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>0.008012052348120857</v>
+        <v>0.008012052348120635</v>
       </c>
     </row>
     <row r="1311">
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>0.009222879504945602</v>
+        <v>0.009222879504946047</v>
       </c>
     </row>
     <row r="1312">
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>0.008697832859458243</v>
+        <v>0.008697832859458021</v>
       </c>
     </row>
     <row r="1315">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>-0.002062717621641341</v>
+        <v>-0.002062717621640897</v>
       </c>
     </row>
     <row r="1317">
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>0.01398800043484094</v>
+        <v>0.0139880004348405</v>
       </c>
     </row>
     <row r="1318">
@@ -13590,7 +13590,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>-0.003901482429946146</v>
+        <v>-0.003901482429945813</v>
       </c>
     </row>
     <row r="1319">
@@ -13600,7 +13600,7 @@
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>-0.01029743294311003</v>
+        <v>-0.01029743294311047</v>
       </c>
     </row>
     <row r="1320">
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>-0.003832206216542455</v>
+        <v>-0.003832206216542011</v>
       </c>
     </row>
     <row r="1321">
@@ -13630,7 +13630,7 @@
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>-0.01695050097809636</v>
+        <v>-0.01695050097809658</v>
       </c>
     </row>
     <row r="1323">
@@ -13650,7 +13650,7 @@
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>-0.01073000053663442</v>
+        <v>-0.01073000053663464</v>
       </c>
     </row>
     <row r="1325">
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>-0.0200196000102727</v>
+        <v>-0.02001960001027225</v>
       </c>
     </row>
     <row r="1326">
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>0.01046216428301294</v>
+        <v>0.01046216428301272</v>
       </c>
     </row>
     <row r="1327">
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>0.004320259857556463</v>
+        <v>0.004320259857556685</v>
       </c>
     </row>
     <row r="1328">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>-0.0003877422885959492</v>
+        <v>-0.0003877422885957271</v>
       </c>
     </row>
     <row r="1329">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>-0.004734613309186897</v>
+        <v>-0.004734613309187119</v>
       </c>
     </row>
     <row r="1331">
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>-0.01116200997214845</v>
+        <v>-0.01116200997214856</v>
       </c>
     </row>
     <row r="1332">
@@ -13730,7 +13730,7 @@
         </is>
       </c>
       <c r="B1332" t="n">
-        <v>0.009033147768030769</v>
+        <v>0.009033147768031213</v>
       </c>
     </row>
     <row r="1333">
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="B1333" t="n">
-        <v>0.00279746870291131</v>
+        <v>0.002797468702911088</v>
       </c>
     </row>
     <row r="1334">
@@ -13760,7 +13760,7 @@
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>-0.01277412936422517</v>
+        <v>-0.01277412936422473</v>
       </c>
     </row>
     <row r="1336">
@@ -13770,7 +13770,7 @@
         </is>
       </c>
       <c r="B1336" t="n">
-        <v>-0.01369011862275682</v>
+        <v>-0.01369011862275726</v>
       </c>
     </row>
     <row r="1337">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="B1340" t="n">
-        <v>0.01760663834637732</v>
+        <v>0.01760663834637755</v>
       </c>
     </row>
     <row r="1341">
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>0.01960053137902062</v>
+        <v>0.01960053137902018</v>
       </c>
     </row>
     <row r="1342">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>0.006712826606764866</v>
+        <v>0.006712826606765088</v>
       </c>
     </row>
     <row r="1343">
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>-0.004704219566368462</v>
+        <v>-0.004704219566368573</v>
       </c>
     </row>
     <row r="1344">
@@ -13850,7 +13850,7 @@
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>-0.02338575500616946</v>
+        <v>-0.02338575500616891</v>
       </c>
     </row>
     <row r="1345">
@@ -13860,7 +13860,7 @@
         </is>
       </c>
       <c r="B1345" t="n">
-        <v>-0.01835432894084166</v>
+        <v>-0.0183543289408421</v>
       </c>
     </row>
     <row r="1346">
@@ -13870,7 +13870,7 @@
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>0.01262582946823376</v>
+        <v>0.01262582946823354</v>
       </c>
     </row>
     <row r="1347">
@@ -13880,7 +13880,7 @@
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>-0.01053153886180525</v>
+        <v>-0.01053153886180491</v>
       </c>
     </row>
     <row r="1348">
@@ -13890,7 +13890,7 @@
         </is>
       </c>
       <c r="B1348" t="n">
-        <v>0.01351861495535234</v>
+        <v>0.01351861495535212</v>
       </c>
     </row>
     <row r="1349">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>-0.01200946454131324</v>
+        <v>-0.01200946454131335</v>
       </c>
     </row>
     <row r="1354">
@@ -13950,7 +13950,7 @@
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>0.002514680374813283</v>
+        <v>0.002514680374813505</v>
       </c>
     </row>
     <row r="1355">
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>-0.05810723940700102</v>
+        <v>-0.05810723940700113</v>
       </c>
     </row>
     <row r="1356">
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>-0.006555159414422862</v>
+        <v>-0.006555159414422751</v>
       </c>
     </row>
     <row r="1358">
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>-0.03967265244533436</v>
+        <v>-0.03967265244533402</v>
       </c>
     </row>
     <row r="1361">
@@ -14020,7 +14020,7 @@
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>-0.03820198234398209</v>
+        <v>-0.0382019823439822</v>
       </c>
     </row>
     <row r="1362">
@@ -14030,7 +14030,7 @@
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>-0.05303003370573955</v>
+        <v>-0.05303003370574</v>
       </c>
     </row>
     <row r="1363">
@@ -14040,7 +14040,7 @@
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>-0.02336054233143792</v>
+        <v>-0.02336054233143747</v>
       </c>
     </row>
     <row r="1364">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>-0.05089259130777335</v>
+        <v>-0.05089259130777357</v>
       </c>
     </row>
     <row r="1365">
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="B1378" t="n">
-        <v>0.05203670336433563</v>
+        <v>0.05203670336433586</v>
       </c>
     </row>
     <row r="1379">
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="B1383" t="n">
-        <v>0.004855096519615909</v>
+        <v>0.004855096519615687</v>
       </c>
     </row>
     <row r="1384">
@@ -14250,7 +14250,7 @@
         </is>
       </c>
       <c r="B1384" t="n">
-        <v>0.02632182410353101</v>
+        <v>0.02632182410353079</v>
       </c>
     </row>
     <row r="1385">
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>0.0226712605361139</v>
+        <v>0.02267126053611412</v>
       </c>
     </row>
     <row r="1386">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>-0.005959807548667428</v>
+        <v>-0.005959807548667539</v>
       </c>
     </row>
     <row r="1389">
@@ -14300,7 +14300,7 @@
         </is>
       </c>
       <c r="B1389" t="n">
-        <v>0.02299659611495875</v>
+        <v>0.02299659611495897</v>
       </c>
     </row>
     <row r="1390">
@@ -14330,7 +14330,7 @@
         </is>
       </c>
       <c r="B1392" t="n">
-        <v>0.01241804702426963</v>
+        <v>0.01241804702426941</v>
       </c>
     </row>
     <row r="1393">
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>0.006950048820966614</v>
+        <v>0.006950048820966837</v>
       </c>
     </row>
     <row r="1396">
@@ -14370,7 +14370,7 @@
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>-0.02910627207066174</v>
+        <v>-0.02910627207066185</v>
       </c>
     </row>
     <row r="1397">
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>0.02006979762826244</v>
+        <v>0.02006979762826266</v>
       </c>
     </row>
     <row r="1398">
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>0.02102553010064256</v>
+        <v>0.02102553010064279</v>
       </c>
     </row>
     <row r="1400">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>0.009770218799781016</v>
+        <v>0.009770218799780794</v>
       </c>
     </row>
     <row r="1401">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>0.004029046316505358</v>
+        <v>0.004029046316505136</v>
       </c>
     </row>
     <row r="1402">
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>-0.01537738586530557</v>
+        <v>-0.01537738586530546</v>
       </c>
     </row>
     <row r="1405">
@@ -14460,7 +14460,7 @@
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>-0.008884883680810418</v>
+        <v>-0.008884883680810529</v>
       </c>
     </row>
     <row r="1406">
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>0.006838149120933279</v>
+        <v>0.006838149120933501</v>
       </c>
     </row>
     <row r="1407">
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1407" t="n">
-        <v>-0.05463894666076674</v>
+        <v>-0.05463894666076696</v>
       </c>
     </row>
     <row r="1408">
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="B1408" t="n">
-        <v>-0.06061014692001487</v>
+        <v>-0.06061014692001476</v>
       </c>
     </row>
     <row r="1409">
@@ -14520,7 +14520,7 @@
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>0.00508751915626493</v>
+        <v>0.005087519156264708</v>
       </c>
     </row>
     <row r="1412">
@@ -14580,7 +14580,7 @@
         </is>
       </c>
       <c r="B1417" t="n">
-        <v>0.02932534904618955</v>
+        <v>0.02932534904618977</v>
       </c>
     </row>
     <row r="1418">
@@ -14600,7 +14600,7 @@
         </is>
       </c>
       <c r="B1419" t="n">
-        <v>0.03917282254077437</v>
+        <v>0.03917282254077414</v>
       </c>
     </row>
     <row r="1420">
@@ -14680,7 +14680,7 @@
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>-0.008661273600503061</v>
+        <v>-0.008661273600503172</v>
       </c>
     </row>
     <row r="1428">
@@ -14690,7 +14690,7 @@
         </is>
       </c>
       <c r="B1428" t="n">
-        <v>0.00116294214593049</v>
+        <v>0.001162942145930268</v>
       </c>
     </row>
     <row r="1429">
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>0.01218757053062181</v>
+        <v>0.01218757053062203</v>
       </c>
     </row>
     <row r="1430">
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="B1430" t="n">
-        <v>-0.009107931592605256</v>
+        <v>-0.009107931592605145</v>
       </c>
     </row>
     <row r="1431">
@@ -14720,7 +14720,7 @@
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>-0.002277196998621278</v>
+        <v>-0.002277196998621944</v>
       </c>
     </row>
     <row r="1432">
@@ -14730,7 +14730,7 @@
         </is>
       </c>
       <c r="B1432" t="n">
-        <v>-0.02183079196920468</v>
+        <v>-0.02183079196920412</v>
       </c>
     </row>
     <row r="1433">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>-0.009366340555972741</v>
+        <v>-0.009366340555973185</v>
       </c>
     </row>
     <row r="1434">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>0.01649582674977279</v>
+        <v>0.01649582674977323</v>
       </c>
     </row>
     <row r="1435">
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>-0.006728787795414859</v>
+        <v>-0.006728787795415081</v>
       </c>
     </row>
     <row r="1436">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>-0.005723034689423256</v>
+        <v>-0.005723034689423034</v>
       </c>
     </row>
     <row r="1439">
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>-0.00716876827963675</v>
+        <v>-0.007168768279636972</v>
       </c>
     </row>
     <row r="1441">
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="B1441" t="n">
-        <v>-0.02953980755226515</v>
+        <v>-0.02953980755226504</v>
       </c>
     </row>
     <row r="1442">
@@ -14840,7 +14840,7 @@
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>0.0277871407829311</v>
+        <v>0.02778714078293087</v>
       </c>
     </row>
     <row r="1444">
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>0.01534889182051269</v>
+        <v>0.01534889182051247</v>
       </c>
     </row>
     <row r="1446">
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>-0.007813373448104621</v>
+        <v>-0.007813373448104399</v>
       </c>
     </row>
     <row r="1447">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>-0.004884440252956312</v>
+        <v>-0.004884440252956423</v>
       </c>
     </row>
     <row r="1451">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>-0.0231029674583092</v>
+        <v>-0.02310296745830887</v>
       </c>
     </row>
     <row r="1452">
@@ -14930,7 +14930,7 @@
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>0.001616336086857961</v>
+        <v>0.001616336086857739</v>
       </c>
     </row>
     <row r="1453">
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>-0.04344583127430746</v>
+        <v>-0.04344583127430734</v>
       </c>
     </row>
     <row r="1454">
@@ -14960,7 +14960,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>0.02646410957223555</v>
+        <v>0.02646410957223577</v>
       </c>
     </row>
     <row r="1456">
@@ -14970,7 +14970,7 @@
         </is>
       </c>
       <c r="B1456" t="n">
-        <v>-0.01678136385941531</v>
+        <v>-0.01678136385941564</v>
       </c>
     </row>
     <row r="1457">
@@ -14980,7 +14980,7 @@
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>0.005677710960120264</v>
+        <v>0.005677710960120486</v>
       </c>
     </row>
     <row r="1458">
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="B1458" t="n">
-        <v>0.009816807544980044</v>
+        <v>0.009816807544979378</v>
       </c>
     </row>
     <row r="1459">
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="B1459" t="n">
-        <v>-0.002657875965815237</v>
+        <v>-0.002657875965814904</v>
       </c>
     </row>
     <row r="1460">
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="B1460" t="n">
-        <v>-0.01103396722972749</v>
+        <v>-0.01103396722972771</v>
       </c>
     </row>
     <row r="1461">
@@ -15020,7 +15020,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>-0.02690636055278917</v>
+        <v>-0.02690636055278883</v>
       </c>
     </row>
     <row r="1462">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="B1462" t="n">
-        <v>0.01069402968883226</v>
+        <v>0.01069402968883182</v>
       </c>
     </row>
     <row r="1463">
@@ -15040,7 +15040,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>-0.02258489017822041</v>
+        <v>-0.02258489017822063</v>
       </c>
     </row>
     <row r="1464">
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="B1464" t="n">
-        <v>0.02573203833732629</v>
+        <v>0.02573203833732651</v>
       </c>
     </row>
     <row r="1465">
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>-0.001723574825577612</v>
+        <v>-0.00172357482557739</v>
       </c>
     </row>
     <row r="1466">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>0.02777630844872014</v>
+        <v>0.0277763084487197</v>
       </c>
     </row>
     <row r="1467">
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>-0.007429491809746169</v>
+        <v>-0.007429491809745947</v>
       </c>
     </row>
     <row r="1468">
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>-0.005530375338157811</v>
+        <v>-0.005530375338158033</v>
       </c>
     </row>
     <row r="1470">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="B1470" t="n">
-        <v>-0.01127912178068213</v>
+        <v>-0.01127912178068247</v>
       </c>
     </row>
     <row r="1471">
@@ -15120,7 +15120,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>-0.004278625321892493</v>
+        <v>-0.004278625321892049</v>
       </c>
     </row>
     <row r="1472">
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="B1474" t="n">
-        <v>-0.02352477110518991</v>
+        <v>-0.02352477110519002</v>
       </c>
     </row>
     <row r="1475">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>-0.009311136943707776</v>
+        <v>-0.009311136943707665</v>
       </c>
     </row>
     <row r="1476">
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="B1476" t="n">
-        <v>-0.0003122592326069151</v>
+        <v>-0.0003122592326072482</v>
       </c>
     </row>
     <row r="1477">
@@ -15180,7 +15180,7 @@
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>0.01421202494053198</v>
+        <v>0.01421202494053153</v>
       </c>
     </row>
     <row r="1478">
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>-0.001124156165128287</v>
+        <v>-0.001124156165127843</v>
       </c>
     </row>
     <row r="1479">
@@ -15200,7 +15200,7 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>0.008109741127789283</v>
+        <v>0.008109741127789061</v>
       </c>
     </row>
     <row r="1480">
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>-0.0043933607010751</v>
+        <v>-0.004393360701074989</v>
       </c>
     </row>
     <row r="1482">
@@ -15230,7 +15230,7 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>-0.01018813675937735</v>
+        <v>-0.01018813675937758</v>
       </c>
     </row>
     <row r="1483">
@@ -15240,7 +15240,7 @@
         </is>
       </c>
       <c r="B1483" t="n">
-        <v>-0.01229448907727471</v>
+        <v>-0.0122944890772746</v>
       </c>
     </row>
     <row r="1484">
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="B1484" t="n">
-        <v>0.01797451950727647</v>
+        <v>0.01797451950727624</v>
       </c>
     </row>
     <row r="1485">
@@ -15280,7 +15280,7 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>-0.008519858712838002</v>
+        <v>-0.008519858712837669</v>
       </c>
     </row>
     <row r="1488">
@@ -15290,7 +15290,7 @@
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>-0.00425461325761356</v>
+        <v>-0.004254613257613893</v>
       </c>
     </row>
     <row r="1489">
@@ -15300,7 +15300,7 @@
         </is>
       </c>
       <c r="B1489" t="n">
-        <v>0.007296590981843876</v>
+        <v>0.007296590981844098</v>
       </c>
     </row>
     <row r="1490">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="B1492" t="n">
-        <v>-0.003315758081911757</v>
+        <v>-0.003315758081911868</v>
       </c>
     </row>
     <row r="1493">
@@ -15340,7 +15340,7 @@
         </is>
       </c>
       <c r="B1493" t="n">
-        <v>-0.008937326643320365</v>
+        <v>-0.008937326643320698</v>
       </c>
     </row>
     <row r="1494">
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="B1495" t="n">
-        <v>0.0005764758596775721</v>
+        <v>0.0005764758596782382</v>
       </c>
     </row>
     <row r="1496">
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="B1496" t="n">
-        <v>-0.009871744985375241</v>
+        <v>-0.009871744985375908</v>
       </c>
     </row>
     <row r="1497">
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="B1497" t="n">
-        <v>-0.01024429857578102</v>
+        <v>-0.0102442985757808</v>
       </c>
     </row>
     <row r="1498">
@@ -15440,7 +15440,7 @@
         </is>
       </c>
       <c r="B1503" t="n">
-        <v>-0.006580417166668351</v>
+        <v>-0.006580417166668462</v>
       </c>
     </row>
     <row r="1504">
@@ -15450,7 +15450,7 @@
         </is>
       </c>
       <c r="B1504" t="n">
-        <v>0.007713130598369311</v>
+        <v>0.007713130598369533</v>
       </c>
     </row>
     <row r="1505">
@@ -15470,7 +15470,7 @@
         </is>
       </c>
       <c r="B1506" t="n">
-        <v>0.007921695419398134</v>
+        <v>0.007921695419397912</v>
       </c>
     </row>
     <row r="1507">
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>-0.01755190530467987</v>
+        <v>-0.01755190530467965</v>
       </c>
     </row>
     <row r="1508">
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="B1508" t="n">
-        <v>-0.007266738169930842</v>
+        <v>-0.007266738169930953</v>
       </c>
     </row>
     <row r="1509">
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="B1510" t="n">
-        <v>-0.006801069580237962</v>
+        <v>-0.006801069580237851</v>
       </c>
     </row>
     <row r="1511">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>-0.007195646791729127</v>
+        <v>-0.007195646791729016</v>
       </c>
     </row>
     <row r="1513">
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="B1513" t="n">
-        <v>-0.00312219226244248</v>
+        <v>-0.003122192262442813</v>
       </c>
     </row>
     <row r="1514">
@@ -15550,7 +15550,7 @@
         </is>
       </c>
       <c r="B1514" t="n">
-        <v>0.020434819551431</v>
+        <v>0.02043481955143167</v>
       </c>
     </row>
     <row r="1515">
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="B1515" t="n">
-        <v>-0.003879105191258669</v>
+        <v>-0.003879105191259113</v>
       </c>
     </row>
     <row r="1516">
@@ -15570,7 +15570,7 @@
         </is>
       </c>
       <c r="B1516" t="n">
-        <v>-0.0005095385535641705</v>
+        <v>-0.0005095385535642816</v>
       </c>
     </row>
     <row r="1517">
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>0.02862119850419043</v>
+        <v>0.02862119850419065</v>
       </c>
     </row>
     <row r="1518">
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="B1519" t="n">
-        <v>0.02614078586982904</v>
+        <v>0.02614078586982882</v>
       </c>
     </row>
     <row r="1520">
@@ -15610,7 +15610,7 @@
         </is>
       </c>
       <c r="B1520" t="n">
-        <v>0.03877530021897413</v>
+        <v>0.03877530021897435</v>
       </c>
     </row>
     <row r="1521">
@@ -15620,7 +15620,7 @@
         </is>
       </c>
       <c r="B1521" t="n">
-        <v>0.08556737190117758</v>
+        <v>0.0855673719011778</v>
       </c>
     </row>
     <row r="1522">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="B1523" t="n">
-        <v>-0.0896439764625232</v>
+        <v>-0.08964397646252342</v>
       </c>
     </row>
     <row r="1524">
@@ -15650,7 +15650,7 @@
         </is>
       </c>
       <c r="B1524" t="n">
-        <v>0.01090922503141423</v>
+        <v>0.01090922503141445</v>
       </c>
     </row>
     <row r="1525">
@@ -15670,7 +15670,7 @@
         </is>
       </c>
       <c r="B1526" t="n">
-        <v>0.03226458937574406</v>
+        <v>0.03226458937574361</v>
       </c>
     </row>
     <row r="1527">
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="B1529" t="n">
-        <v>-0.007957251317429304</v>
+        <v>-0.007957251317428971</v>
       </c>
     </row>
     <row r="1530">
@@ -15710,7 +15710,7 @@
         </is>
       </c>
       <c r="B1530" t="n">
-        <v>0.02350024722958866</v>
+        <v>0.02350024722958843</v>
       </c>
     </row>
     <row r="1531">
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="B1536" t="n">
-        <v>0.02551897222967492</v>
+        <v>0.02551897222967514</v>
       </c>
     </row>
     <row r="1537">
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="B1537" t="n">
-        <v>-0.03145785866202566</v>
+        <v>-0.03145785866202611</v>
       </c>
     </row>
     <row r="1538">
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="B1540" t="n">
-        <v>-0.03217065808157804</v>
+        <v>-0.03217065808157793</v>
       </c>
     </row>
     <row r="1541">
@@ -15830,7 +15830,7 @@
         </is>
       </c>
       <c r="B1542" t="n">
-        <v>0.02391544345126739</v>
+        <v>0.02391544345126762</v>
       </c>
     </row>
     <row r="1543">
@@ -15840,7 +15840,7 @@
         </is>
       </c>
       <c r="B1543" t="n">
-        <v>0.003882543246889192</v>
+        <v>0.00388254324688897</v>
       </c>
     </row>
     <row r="1544">
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="B1546" t="n">
-        <v>0.01636476017632793</v>
+        <v>0.01636476017632771</v>
       </c>
     </row>
     <row r="1547">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="B1547" t="n">
-        <v>-0.004784771240559094</v>
+        <v>-0.004784771240559316</v>
       </c>
     </row>
     <row r="1548">
@@ -15890,7 +15890,7 @@
         </is>
       </c>
       <c r="B1548" t="n">
-        <v>0.01106374477479144</v>
+        <v>0.01106374477479211</v>
       </c>
     </row>
     <row r="1549">
@@ -15900,7 +15900,7 @@
         </is>
       </c>
       <c r="B1549" t="n">
-        <v>-0.02224243829935835</v>
+        <v>-0.02224243829935868</v>
       </c>
     </row>
     <row r="1550">
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="B1550" t="n">
-        <v>-0.01582135360634984</v>
+        <v>-0.01582135360634951</v>
       </c>
     </row>
     <row r="1551">
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="B1551" t="n">
-        <v>-0.02390393161544657</v>
+        <v>-0.02390393161544668</v>
       </c>
     </row>
     <row r="1552">
@@ -15940,7 +15940,7 @@
         </is>
       </c>
       <c r="B1553" t="n">
-        <v>0.02353583939684478</v>
+        <v>0.023535839396845</v>
       </c>
     </row>
     <row r="1554">
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="B1554" t="n">
-        <v>0.0001947670045263639</v>
+        <v>0.0001947670045261418</v>
       </c>
     </row>
     <row r="1555">
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="B1557" t="n">
-        <v>-0.0159773944055267</v>
+        <v>-0.01597739440552637</v>
       </c>
     </row>
     <row r="1558">
@@ -15990,7 +15990,7 @@
         </is>
       </c>
       <c r="B1558" t="n">
-        <v>0.01713059625157598</v>
+        <v>0.01713059625157531</v>
       </c>
     </row>
     <row r="1559">
@@ -16000,7 +16000,7 @@
         </is>
       </c>
       <c r="B1559" t="n">
-        <v>0.01095534250813368</v>
+        <v>0.01095534250813412</v>
       </c>
     </row>
     <row r="1560">
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="B1563" t="n">
-        <v>-0.01843262876286167</v>
+        <v>-0.01843262876286145</v>
       </c>
     </row>
     <row r="1564">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="B1565" t="n">
-        <v>0.001955770962812853</v>
+        <v>0.001955770962812631</v>
       </c>
     </row>
     <row r="1566">
@@ -16110,7 +16110,7 @@
         </is>
       </c>
       <c r="B1570" t="n">
-        <v>-0.005140303023374981</v>
+        <v>-0.005140303023375314</v>
       </c>
     </row>
     <row r="1571">
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="B1571" t="n">
-        <v>-0.01109197000381512</v>
+        <v>-0.01109197000381446</v>
       </c>
     </row>
     <row r="1572">
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="B1572" t="n">
-        <v>-0.04616953968172677</v>
+        <v>-0.0461695396817271</v>
       </c>
     </row>
     <row r="1573">
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="B1575" t="n">
-        <v>0.01173595460700327</v>
+        <v>0.01173595460700372</v>
       </c>
     </row>
     <row r="1576">
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="B1576" t="n">
-        <v>-0.05329917479100399</v>
+        <v>-0.05329917479100477</v>
       </c>
     </row>
     <row r="1577">
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="B1577" t="n">
-        <v>0.01285487440510802</v>
+        <v>0.01285487440510846</v>
       </c>
     </row>
     <row r="1578">
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="B1579" t="n">
-        <v>0.02330752130108382</v>
+        <v>0.0233075213010836</v>
       </c>
     </row>
     <row r="1580">
@@ -16210,7 +16210,7 @@
         </is>
       </c>
       <c r="B1580" t="n">
-        <v>0.007624534106426273</v>
+        <v>0.007624534106426939</v>
       </c>
     </row>
     <row r="1581">
@@ -16220,7 +16220,7 @@
         </is>
       </c>
       <c r="B1581" t="n">
-        <v>-0.01536490809005187</v>
+        <v>-0.01536490809005209</v>
       </c>
     </row>
     <row r="1582">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="B1582" t="n">
-        <v>-0.02727194585355419</v>
+        <v>-0.0272719458535543</v>
       </c>
     </row>
     <row r="1583">
@@ -16240,7 +16240,7 @@
         </is>
       </c>
       <c r="B1583" t="n">
-        <v>-0.01187516810674261</v>
+        <v>-0.01187516810674283</v>
       </c>
     </row>
     <row r="1584">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="B1584" t="n">
-        <v>-0.02356023417920794</v>
+        <v>-0.02356023417920805</v>
       </c>
     </row>
     <row r="1585">
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="B1589" t="n">
-        <v>-0.02415417781109308</v>
+        <v>-0.02415417781109297</v>
       </c>
     </row>
     <row r="1590">
@@ -16310,7 +16310,7 @@
         </is>
       </c>
       <c r="B1590" t="n">
-        <v>0.009502535652354815</v>
+        <v>0.009502535652354371</v>
       </c>
     </row>
     <row r="1591">
@@ -16320,7 +16320,7 @@
         </is>
       </c>
       <c r="B1591" t="n">
-        <v>0.04054779069623105</v>
+        <v>0.04054779069623149</v>
       </c>
     </row>
     <row r="1592">
@@ -16330,7 +16330,7 @@
         </is>
       </c>
       <c r="B1592" t="n">
-        <v>-0.001803053342543937</v>
+        <v>-0.001803053342543715</v>
       </c>
     </row>
     <row r="1593">
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="B1593" t="n">
-        <v>0.001630383464678475</v>
+        <v>0.001630383464678253</v>
       </c>
     </row>
     <row r="1594">
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="B1594" t="n">
-        <v>-0.002199811408060248</v>
+        <v>-0.00219981140806047</v>
       </c>
     </row>
     <row r="1595">
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="B1595" t="n">
-        <v>0.01072935199789948</v>
+        <v>0.01072935199789971</v>
       </c>
     </row>
     <row r="1596">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="B1598" t="n">
-        <v>0.0003278026339781359</v>
+        <v>0.000327802633978358</v>
       </c>
     </row>
     <row r="1599">
@@ -16400,7 +16400,7 @@
         </is>
       </c>
       <c r="B1599" t="n">
-        <v>0.005299620456912013</v>
+        <v>0.005299620456911791</v>
       </c>
     </row>
     <row r="1600">
@@ -16440,7 +16440,7 @@
         </is>
       </c>
       <c r="B1603" t="n">
-        <v>0.00614538182196056</v>
+        <v>0.006145381821960783</v>
       </c>
     </row>
     <row r="1604">
@@ -16450,7 +16450,7 @@
         </is>
       </c>
       <c r="B1604" t="n">
-        <v>0.001020386590736111</v>
+        <v>0.001020386590735667</v>
       </c>
     </row>
     <row r="1605">
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="B1605" t="n">
-        <v>0.006716487511363445</v>
+        <v>0.006716487511363889</v>
       </c>
     </row>
     <row r="1606">
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="B1606" t="n">
-        <v>0.00402780981656492</v>
+        <v>0.004027809816565142</v>
       </c>
     </row>
     <row r="1607">
@@ -16480,7 +16480,7 @@
         </is>
       </c>
       <c r="B1607" t="n">
-        <v>-0.01827278527387821</v>
+        <v>-0.01827278527387854</v>
       </c>
     </row>
     <row r="1608">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="B1608" t="n">
-        <v>-0.004182915993544367</v>
+        <v>-0.004182915993544145</v>
       </c>
     </row>
     <row r="1609">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="B1610" t="n">
-        <v>-0.02453578728277162</v>
+        <v>-0.02453578728277184</v>
       </c>
     </row>
     <row r="1611">
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="B1611" t="n">
-        <v>0.01997217894310821</v>
+        <v>0.01997217894310843</v>
       </c>
     </row>
     <row r="1612">
@@ -16530,7 +16530,7 @@
         </is>
       </c>
       <c r="B1612" t="n">
-        <v>0.01277987293853977</v>
+        <v>0.01277987293853955</v>
       </c>
     </row>
     <row r="1613">
@@ -16570,7 +16570,7 @@
         </is>
       </c>
       <c r="B1616" t="n">
-        <v>0.01755498101229525</v>
+        <v>0.01755498101229547</v>
       </c>
     </row>
     <row r="1617">
@@ -16580,7 +16580,7 @@
         </is>
       </c>
       <c r="B1617" t="n">
-        <v>-0.003127437136846933</v>
+        <v>-0.003127437136847044</v>
       </c>
     </row>
     <row r="1618">
@@ -16600,7 +16600,7 @@
         </is>
       </c>
       <c r="B1619" t="n">
-        <v>0.009247873390833217</v>
+        <v>0.009247873390833439</v>
       </c>
     </row>
     <row r="1620">
@@ -16630,7 +16630,7 @@
         </is>
       </c>
       <c r="B1622" t="n">
-        <v>0.01899700047420128</v>
+        <v>0.01899700047420105</v>
       </c>
     </row>
     <row r="1623">
@@ -16650,7 +16650,7 @@
         </is>
       </c>
       <c r="B1624" t="n">
-        <v>0.004611919958875221</v>
+        <v>0.004611919958875443</v>
       </c>
     </row>
     <row r="1625">
@@ -16660,7 +16660,7 @@
         </is>
       </c>
       <c r="B1625" t="n">
-        <v>0.002910395232286866</v>
+        <v>0.002910395232286644</v>
       </c>
     </row>
     <row r="1626">
@@ -16680,7 +16680,7 @@
         </is>
       </c>
       <c r="B1627" t="n">
-        <v>-0.008162961554256776</v>
+        <v>-0.008162961554256887</v>
       </c>
     </row>
     <row r="1628">
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="B1629" t="n">
-        <v>0.005782149571161632</v>
+        <v>0.005782149571161854</v>
       </c>
     </row>
     <row r="1630">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="B1631" t="n">
-        <v>0.007192622223135769</v>
+        <v>0.007192622223135547</v>
       </c>
     </row>
     <row r="1632">
@@ -16730,7 +16730,7 @@
         </is>
       </c>
       <c r="B1632" t="n">
-        <v>0.007350927449203848</v>
+        <v>0.007350927449203626</v>
       </c>
     </row>
     <row r="1633">
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="B1633" t="n">
-        <v>-0.02223425921602651</v>
+        <v>-0.02223425921602618</v>
       </c>
     </row>
     <row r="1634">
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="B1636" t="n">
-        <v>0.01450678809730466</v>
+        <v>0.01450678809730443</v>
       </c>
     </row>
     <row r="1637">
@@ -16780,7 +16780,7 @@
         </is>
       </c>
       <c r="B1637" t="n">
-        <v>-0.00864095734387782</v>
+        <v>-0.008640957343877487</v>
       </c>
     </row>
     <row r="1638">
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="B1638" t="n">
-        <v>-0.005693101611807916</v>
+        <v>-0.005693101611808138</v>
       </c>
     </row>
     <row r="1639">
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="B1641" t="n">
-        <v>-0.002059928567346825</v>
+        <v>-0.002059928567346936</v>
       </c>
     </row>
     <row r="1642">
@@ -16840,7 +16840,7 @@
         </is>
       </c>
       <c r="B1643" t="n">
-        <v>-0.1056487263423166</v>
+        <v>-0.1056487263423165</v>
       </c>
     </row>
     <row r="1644">
@@ -16850,7 +16850,7 @@
         </is>
       </c>
       <c r="B1644" t="n">
-        <v>-0.0118933813854688</v>
+        <v>-0.01189338138546858</v>
       </c>
     </row>
     <row r="1645">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="B1645" t="n">
-        <v>0.01822489260835436</v>
+        <v>0.01822489260835392</v>
       </c>
     </row>
     <row r="1646">
@@ -16870,7 +16870,7 @@
         </is>
       </c>
       <c r="B1646" t="n">
-        <v>0.0326020097635138</v>
+        <v>0.03260200976351424</v>
       </c>
     </row>
     <row r="1647">
@@ -16880,7 +16880,7 @@
         </is>
       </c>
       <c r="B1647" t="n">
-        <v>-0.0002633637638471686</v>
+        <v>-0.0002633637638473907</v>
       </c>
     </row>
     <row r="1648">
@@ -16920,7 +16920,7 @@
         </is>
       </c>
       <c r="B1651" t="n">
-        <v>0.02032731575984337</v>
+        <v>0.02032731575984292</v>
       </c>
     </row>
     <row r="1652">
@@ -16930,7 +16930,7 @@
         </is>
       </c>
       <c r="B1652" t="n">
-        <v>0.004929547463428108</v>
+        <v>0.00492954746342833</v>
       </c>
     </row>
     <row r="1653">
@@ -16940,7 +16940,7 @@
         </is>
       </c>
       <c r="B1653" t="n">
-        <v>0.02682072900867949</v>
+        <v>0.02682072900867971</v>
       </c>
     </row>
     <row r="1654">
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="B1654" t="n">
-        <v>0.01169586862946614</v>
+        <v>0.01169586862946592</v>
       </c>
     </row>
     <row r="1655">
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="B1655" t="n">
-        <v>0.01282874983113058</v>
+        <v>0.0128287498311308</v>
       </c>
     </row>
     <row r="1656">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="B1656" t="n">
-        <v>0.007823117349631259</v>
+        <v>0.007823117349631703</v>
       </c>
     </row>
     <row r="1657">
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="B1657" t="n">
-        <v>-0.01688473878601215</v>
+        <v>-0.01688473878601249</v>
       </c>
     </row>
     <row r="1658">
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="B1658" t="n">
-        <v>-0.02606678226746606</v>
+        <v>-0.02606678226746573</v>
       </c>
     </row>
     <row r="1659">
@@ -17000,7 +17000,7 @@
         </is>
       </c>
       <c r="B1659" t="n">
-        <v>-0.002959152450056846</v>
+        <v>-0.002959152450057401</v>
       </c>
     </row>
     <row r="1660">
@@ -17010,7 +17010,7 @@
         </is>
       </c>
       <c r="B1660" t="n">
-        <v>-0.006605608569459132</v>
+        <v>-0.00660560856945891</v>
       </c>
     </row>
     <row r="1661">
@@ -17020,7 +17020,7 @@
         </is>
       </c>
       <c r="B1661" t="n">
-        <v>0.02654836006901462</v>
+        <v>0.0265483600690144</v>
       </c>
     </row>
     <row r="1662">
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="B1662" t="n">
-        <v>0.009147278182450425</v>
+        <v>0.009147278182450869</v>
       </c>
     </row>
     <row r="1663">
@@ -17080,7 +17080,7 @@
         </is>
       </c>
       <c r="B1667" t="n">
-        <v>0.002888943042341108</v>
+        <v>0.002888943042340886</v>
       </c>
     </row>
     <row r="1668">
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="B1672" t="n">
-        <v>-0.007490592504773241</v>
+        <v>-0.007490592504773574</v>
       </c>
     </row>
     <row r="1673">
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="B1673" t="n">
-        <v>-0.01986364809302554</v>
+        <v>-0.01986364809302499</v>
       </c>
     </row>
     <row r="1674">
@@ -17170,7 +17170,7 @@
         </is>
       </c>
       <c r="B1676" t="n">
-        <v>0.01130203813373809</v>
+        <v>0.01130203813373787</v>
       </c>
     </row>
     <row r="1677">
@@ -17180,7 +17180,7 @@
         </is>
       </c>
       <c r="B1677" t="n">
-        <v>-0.002825517244583575</v>
+        <v>-0.002825517244583908</v>
       </c>
     </row>
     <row r="1678">
@@ -17190,7 +17190,7 @@
         </is>
       </c>
       <c r="B1678" t="n">
-        <v>0.01165671494580622</v>
+        <v>0.01165671494580667</v>
       </c>
     </row>
     <row r="1679">
@@ -17200,7 +17200,7 @@
         </is>
       </c>
       <c r="B1679" t="n">
-        <v>-0.01057324515605651</v>
+        <v>-0.01057324515605662</v>
       </c>
     </row>
     <row r="1680">
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="B1680" t="n">
-        <v>0.01812193069789392</v>
+        <v>0.01812193069789414</v>
       </c>
     </row>
     <row r="1681">
@@ -17220,7 +17220,7 @@
         </is>
       </c>
       <c r="B1681" t="n">
-        <v>0.01233275157908942</v>
+        <v>0.0123327515790892</v>
       </c>
     </row>
     <row r="1682">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="B1682" t="n">
-        <v>-0.01581695640456737</v>
+        <v>-0.01581695640456715</v>
       </c>
     </row>
     <row r="1683">
@@ -17280,7 +17280,7 @@
         </is>
       </c>
       <c r="B1687" t="n">
-        <v>0.006172078592171504</v>
+        <v>0.006172078592171726</v>
       </c>
     </row>
     <row r="1688">
@@ -17290,7 +17290,7 @@
         </is>
       </c>
       <c r="B1688" t="n">
-        <v>-0.01364940258210467</v>
+        <v>-0.01364940258210501</v>
       </c>
     </row>
     <row r="1689">
@@ -17300,7 +17300,7 @@
         </is>
       </c>
       <c r="B1689" t="n">
-        <v>0.007500410953378722</v>
+        <v>0.007500410953378944</v>
       </c>
     </row>
     <row r="1690">
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="B1690" t="n">
-        <v>0.006643470650588457</v>
+        <v>0.006643470650588235</v>
       </c>
     </row>
     <row r="1691">
@@ -17400,7 +17400,7 @@
         </is>
       </c>
       <c r="B1699" t="n">
-        <v>0.01782238960508398</v>
+        <v>0.0178223896050842</v>
       </c>
     </row>
     <row r="1700">
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="B1700" t="n">
-        <v>0.004911826826931698</v>
+        <v>0.004911826826931254</v>
       </c>
     </row>
     <row r="1701">
@@ -17420,7 +17420,7 @@
         </is>
       </c>
       <c r="B1701" t="n">
-        <v>0.002210863222984027</v>
+        <v>0.00221086322298425</v>
       </c>
     </row>
     <row r="1702">
@@ -17450,7 +17450,7 @@
         </is>
       </c>
       <c r="B1704" t="n">
-        <v>0.01308247001042506</v>
+        <v>0.01308247001042484</v>
       </c>
     </row>
     <row r="1705">
@@ -17460,7 +17460,7 @@
         </is>
       </c>
       <c r="B1705" t="n">
-        <v>0.00169694543628518</v>
+        <v>0.001696945436285402</v>
       </c>
     </row>
     <row r="1706">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="B1706" t="n">
-        <v>0.006559756041537801</v>
+        <v>0.006559756041538023</v>
       </c>
     </row>
     <row r="1707">
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="B1707" t="n">
-        <v>-0.001042996979993993</v>
+        <v>-0.001042996979994104</v>
       </c>
     </row>
     <row r="1708">
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="B1708" t="n">
-        <v>-0.002438438862038428</v>
+        <v>-0.00243843886203865</v>
       </c>
     </row>
     <row r="1709">
@@ -17500,7 +17500,7 @@
         </is>
       </c>
       <c r="B1709" t="n">
-        <v>0.007852431208950517</v>
+        <v>0.007852431208950739</v>
       </c>
     </row>
     <row r="1710">
@@ -17550,7 +17550,7 @@
         </is>
       </c>
       <c r="B1714" t="n">
-        <v>0.0166454291626168</v>
+        <v>0.01664542916261658</v>
       </c>
     </row>
     <row r="1715">
@@ -17560,7 +17560,7 @@
         </is>
       </c>
       <c r="B1715" t="n">
-        <v>0.003351154426324277</v>
+        <v>0.003351154426324499</v>
       </c>
     </row>
     <row r="1716">
@@ -17590,7 +17590,7 @@
         </is>
       </c>
       <c r="B1718" t="n">
-        <v>0.01089442825586362</v>
+        <v>0.01089442825586384</v>
       </c>
     </row>
     <row r="1719">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="B1719" t="n">
-        <v>0.007173816047436388</v>
+        <v>0.007173816047436166</v>
       </c>
     </row>
     <row r="1720">
@@ -17610,7 +17610,7 @@
         </is>
       </c>
       <c r="B1720" t="n">
-        <v>-0.004626185933872207</v>
+        <v>-0.004626185933872318</v>
       </c>
     </row>
     <row r="1721">
@@ -17620,7 +17620,7 @@
         </is>
       </c>
       <c r="B1721" t="n">
-        <v>-0.002763981564619322</v>
+        <v>-0.0027639815646191</v>
       </c>
     </row>
     <row r="1722">
@@ -17630,7 +17630,7 @@
         </is>
       </c>
       <c r="B1722" t="n">
-        <v>-0.01650937439141398</v>
+        <v>-0.0165093743914142</v>
       </c>
     </row>
     <row r="1723">
@@ -17650,7 +17650,7 @@
         </is>
       </c>
       <c r="B1724" t="n">
-        <v>0.02594911019582313</v>
+        <v>0.02594911019582291</v>
       </c>
     </row>
     <row r="1725">
@@ -17660,7 +17660,7 @@
         </is>
       </c>
       <c r="B1725" t="n">
-        <v>0.004030184143952731</v>
+        <v>0.004030184143952953</v>
       </c>
     </row>
     <row r="1726">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="B1730" t="n">
-        <v>0.02182188320001832</v>
+        <v>0.02182188320001788</v>
       </c>
     </row>
     <row r="1731">
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="B1731" t="n">
-        <v>0.00817472838668909</v>
+        <v>0.008174728386689534</v>
       </c>
     </row>
     <row r="1732">
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="B1732" t="n">
-        <v>-0.0327593662014094</v>
+        <v>-0.03275936620140962</v>
       </c>
     </row>
     <row r="1733">
@@ -17740,7 +17740,7 @@
         </is>
       </c>
       <c r="B1733" t="n">
-        <v>0.02381666121574377</v>
+        <v>0.02381666121574422</v>
       </c>
     </row>
     <row r="1734">
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="B1734" t="n">
-        <v>0.01376422540687017</v>
+        <v>0.01376422540686995</v>
       </c>
     </row>
     <row r="1735">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="B1738" t="n">
-        <v>-0.0003009761018913926</v>
+        <v>-0.0003009761018915036</v>
       </c>
     </row>
     <row r="1739">
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="B1741" t="n">
-        <v>-0.04474938961819863</v>
+        <v>-0.04474938961819885</v>
       </c>
     </row>
     <row r="1742">
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="B1742" t="n">
-        <v>-0.003922282889509909</v>
+        <v>-0.003922282889509798</v>
       </c>
     </row>
     <row r="1743">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="B1743" t="n">
-        <v>-0.00255258997767549</v>
+        <v>-0.002552589977675712</v>
       </c>
     </row>
     <row r="1744">
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="B1744" t="n">
-        <v>0.03266001726723911</v>
+        <v>0.03266001726723933</v>
       </c>
     </row>
     <row r="1745">
@@ -17860,7 +17860,7 @@
         </is>
       </c>
       <c r="B1745" t="n">
-        <v>-0.02061677841148213</v>
+        <v>-0.02061677841148235</v>
       </c>
     </row>
     <row r="1746">
@@ -17870,7 +17870,7 @@
         </is>
       </c>
       <c r="B1746" t="n">
-        <v>-0.02167805487909813</v>
+        <v>-0.02167805487909802</v>
       </c>
     </row>
     <row r="1747">
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="B1747" t="n">
-        <v>-0.009590264894392853</v>
+        <v>-0.009590264894392742</v>
       </c>
     </row>
     <row r="1748">
@@ -17900,7 +17900,7 @@
         </is>
       </c>
       <c r="B1749" t="n">
-        <v>0.02101259652588161</v>
+        <v>0.02101259652588139</v>
       </c>
     </row>
     <row r="1750">
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="B1750" t="n">
-        <v>-0.01001426344024658</v>
+        <v>-0.01001426344024636</v>
       </c>
     </row>
     <row r="1751">
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="B1752" t="n">
-        <v>0.01620442885819307</v>
+        <v>0.01620442885819284</v>
       </c>
     </row>
     <row r="1753">
@@ -17950,7 +17950,7 @@
         </is>
       </c>
       <c r="B1754" t="n">
-        <v>-0.0005193309779543132</v>
+        <v>-0.0005193309779542021</v>
       </c>
     </row>
     <row r="1755">
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="B1756" t="n">
-        <v>-0.003088750655270922</v>
+        <v>-0.003088750655270811</v>
       </c>
     </row>
     <row r="1757">
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="B1757" t="n">
-        <v>-0.01801511596394834</v>
+        <v>-0.01801511596394856</v>
       </c>
     </row>
     <row r="1758">
@@ -18030,7 +18030,7 @@
         </is>
       </c>
       <c r="B1762" t="n">
-        <v>-0.01019241695084894</v>
+        <v>-0.01019241695084883</v>
       </c>
     </row>
     <row r="1763">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="B1763" t="n">
-        <v>-0.002632215142658767</v>
+        <v>-0.002632215142658878</v>
       </c>
     </row>
     <row r="1764">
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="B1764" t="n">
-        <v>0.00791301321507798</v>
+        <v>0.007913013215078202</v>
       </c>
     </row>
     <row r="1765">
@@ -18060,7 +18060,7 @@
         </is>
       </c>
       <c r="B1765" t="n">
-        <v>0.00117578046858613</v>
+        <v>0.001175780468585907</v>
       </c>
     </row>
     <row r="1766">
@@ -18070,7 +18070,7 @@
         </is>
       </c>
       <c r="B1766" t="n">
-        <v>0.005108259331807918</v>
+        <v>0.00510825933180814</v>
       </c>
     </row>
     <row r="1767">
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="B1769" t="n">
-        <v>-0.00136952689199199</v>
+        <v>-0.001369526891992101</v>
       </c>
     </row>
     <row r="1770">
@@ -18140,7 +18140,7 @@
         </is>
       </c>
       <c r="B1773" t="n">
-        <v>0.01022830575472367</v>
+        <v>0.01022830575472344</v>
       </c>
     </row>
     <row r="1774">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="B1779" t="n">
-        <v>0.0009781809466509195</v>
+        <v>0.0009781809466506974</v>
       </c>
     </row>
     <row r="1780">
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="B1781" t="n">
-        <v>-0.004905170627413358</v>
+        <v>-0.004905170627413247</v>
       </c>
     </row>
     <row r="1782">
@@ -18230,7 +18230,7 @@
         </is>
       </c>
       <c r="B1782" t="n">
-        <v>0.006240890729486415</v>
+        <v>0.006240890729486193</v>
       </c>
     </row>
     <row r="1783">
@@ -18250,7 +18250,7 @@
         </is>
       </c>
       <c r="B1784" t="n">
-        <v>-0.002470423196390126</v>
+        <v>-0.002470423196390015</v>
       </c>
     </row>
     <row r="1785">
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="B1787" t="n">
-        <v>-0.0008347167303475178</v>
+        <v>-0.0008347167303476288</v>
       </c>
     </row>
     <row r="1788">
@@ -18330,7 +18330,7 @@
         </is>
       </c>
       <c r="B1792" t="n">
-        <v>-0.004542398008232418</v>
+        <v>-0.004542398008232307</v>
       </c>
     </row>
     <row r="1793">
@@ -18350,7 +18350,7 @@
         </is>
       </c>
       <c r="B1794" t="n">
-        <v>-0.01903419971899112</v>
+        <v>-0.01903419971899123</v>
       </c>
     </row>
     <row r="1795">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="B1796" t="n">
-        <v>-0.00492453268500348</v>
+        <v>-0.004924532685003702</v>
       </c>
     </row>
     <row r="1797">
@@ -18380,7 +18380,7 @@
         </is>
       </c>
       <c r="B1797" t="n">
-        <v>-0.02776924095343269</v>
+        <v>-0.02776924095343247</v>
       </c>
     </row>
     <row r="1798">
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="B1798" t="n">
-        <v>0.02260504103657235</v>
+        <v>0.02260504103657213</v>
       </c>
     </row>
     <row r="1799">
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="B1803" t="n">
-        <v>0.01540519916397476</v>
+        <v>0.01540519916397454</v>
       </c>
     </row>
     <row r="1804">
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="B1805" t="n">
-        <v>-0.01285946919518977</v>
+        <v>-0.01285946919518954</v>
       </c>
     </row>
     <row r="1806">
@@ -18470,7 +18470,7 @@
         </is>
       </c>
       <c r="B1806" t="n">
-        <v>-0.02064586544405733</v>
+        <v>-0.02064586544405744</v>
       </c>
     </row>
     <row r="1807">
@@ -18500,7 +18500,7 @@
         </is>
       </c>
       <c r="B1809" t="n">
-        <v>-0.01122941038211911</v>
+        <v>-0.01122941038211922</v>
       </c>
     </row>
     <row r="1810">
@@ -18550,7 +18550,7 @@
         </is>
       </c>
       <c r="B1814" t="n">
-        <v>-0.02768984295205612</v>
+        <v>-0.02768984295205623</v>
       </c>
     </row>
     <row r="1815">
@@ -18590,7 +18590,7 @@
         </is>
       </c>
       <c r="B1818" t="n">
-        <v>-0.002363932939665303</v>
+        <v>-0.002363932939665192</v>
       </c>
     </row>
     <row r="1819">
@@ -18630,7 +18630,7 @@
         </is>
       </c>
       <c r="B1822" t="n">
-        <v>-0.01300553898259571</v>
+        <v>-0.01300553898259593</v>
       </c>
     </row>
     <row r="1823">
@@ -18640,7 +18640,7 @@
         </is>
       </c>
       <c r="B1823" t="n">
-        <v>-0.01180272432455232</v>
+        <v>-0.01180272432455221</v>
       </c>
     </row>
     <row r="1824">
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="B1825" t="n">
-        <v>0.009705632072783299</v>
+        <v>0.009705632072783077</v>
       </c>
     </row>
     <row r="1826">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="B1826" t="n">
-        <v>0.01748474166260272</v>
+        <v>0.01748474166260294</v>
       </c>
     </row>
     <row r="1827">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="B1828" t="n">
-        <v>-0.002793239813542736</v>
+        <v>-0.002793239813542847</v>
       </c>
     </row>
     <row r="1829">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="B1829" t="n">
-        <v>0.01211100937969234</v>
+        <v>0.01211100937969256</v>
       </c>
     </row>
     <row r="1830">
@@ -18730,7 +18730,7 @@
         </is>
       </c>
       <c r="B1832" t="n">
-        <v>-0.004730792791704186</v>
+        <v>-0.004730792791704408</v>
       </c>
     </row>
     <row r="1833">
@@ -18760,7 +18760,7 @@
         </is>
       </c>
       <c r="B1835" t="n">
-        <v>-0.001822874919492068</v>
+        <v>-0.001822874919491957</v>
       </c>
     </row>
     <row r="1836">
@@ -18780,7 +18780,7 @@
         </is>
       </c>
       <c r="B1837" t="n">
-        <v>0.0007819437882174984</v>
+        <v>0.0007819437882177205</v>
       </c>
     </row>
     <row r="1838">
@@ -18810,7 +18810,7 @@
         </is>
       </c>
       <c r="B1840" t="n">
-        <v>0.005798011961389404</v>
+        <v>0.005798011961389182</v>
       </c>
     </row>
     <row r="1841">
@@ -18830,7 +18830,7 @@
         </is>
       </c>
       <c r="B1842" t="n">
-        <v>-0.002428010956527449</v>
+        <v>-0.002428010956527227</v>
       </c>
     </row>
     <row r="1843">
@@ -18840,7 +18840,7 @@
         </is>
       </c>
       <c r="B1843" t="n">
-        <v>-0.01066742571820933</v>
+        <v>-0.01066742571820978</v>
       </c>
     </row>
     <row r="1844">
@@ -18850,7 +18850,7 @@
         </is>
       </c>
       <c r="B1844" t="n">
-        <v>-0.01339273823585851</v>
+        <v>-0.01339273823585818</v>
       </c>
     </row>
     <row r="1845">
@@ -18870,7 +18870,7 @@
         </is>
       </c>
       <c r="B1846" t="n">
-        <v>-0.02430529559486194</v>
+        <v>-0.02430529559486216</v>
       </c>
     </row>
     <row r="1847">
@@ -18880,7 +18880,7 @@
         </is>
       </c>
       <c r="B1847" t="n">
-        <v>0.01599709253795445</v>
+        <v>0.01599709253795489</v>
       </c>
     </row>
     <row r="1848">
@@ -18890,7 +18890,7 @@
         </is>
       </c>
       <c r="B1848" t="n">
-        <v>0.009692543345447557</v>
+        <v>0.009692543345447335</v>
       </c>
     </row>
     <row r="1849">
@@ -18910,7 +18910,7 @@
         </is>
       </c>
       <c r="B1850" t="n">
-        <v>0.006280139381210414</v>
+        <v>0.006280139381210637</v>
       </c>
     </row>
     <row r="1851">
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="B1854" t="n">
-        <v>-0.002811297551890135</v>
+        <v>-0.002811297551890357</v>
       </c>
     </row>
     <row r="1855">
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="B1856" t="n">
-        <v>0.01795266813743757</v>
+        <v>0.01795266813743779</v>
       </c>
     </row>
     <row r="1857">
@@ -18990,7 +18990,7 @@
         </is>
       </c>
       <c r="B1858" t="n">
-        <v>0.003704625100737546</v>
+        <v>0.003704625100737324</v>
       </c>
     </row>
     <row r="1859">
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="B1859" t="n">
-        <v>0.005866502432354315</v>
+        <v>0.005866502432354537</v>
       </c>
     </row>
     <row r="1860">
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="B1860" t="n">
-        <v>-0.0145478636145403</v>
+        <v>-0.01454786361454075</v>
       </c>
     </row>
     <row r="1861">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="B1861" t="n">
-        <v>-0.009903373000211158</v>
+        <v>-0.009903373000210935</v>
       </c>
     </row>
     <row r="1862">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="B1862" t="n">
-        <v>-0.005775282679171823</v>
+        <v>-0.005775282679172045</v>
       </c>
     </row>
     <row r="1863">
@@ -19040,7 +19040,7 @@
         </is>
       </c>
       <c r="B1863" t="n">
-        <v>0.009025495303527364</v>
+        <v>0.009025495303527808</v>
       </c>
     </row>
     <row r="1864">
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="B1864" t="n">
-        <v>0.02288443043503108</v>
+        <v>0.02288443043503086</v>
       </c>
     </row>
     <row r="1865">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="B1865" t="n">
-        <v>-0.01401879907540671</v>
+        <v>-0.01401879907540649</v>
       </c>
     </row>
     <row r="1866">
@@ -19070,7 +19070,7 @@
         </is>
       </c>
       <c r="B1866" t="n">
-        <v>0.02249191216867241</v>
+        <v>0.02249191216867197</v>
       </c>
     </row>
     <row r="1867">
@@ -19080,7 +19080,7 @@
         </is>
       </c>
       <c r="B1867" t="n">
-        <v>-0.003802018974499943</v>
+        <v>-0.00380201897449961</v>
       </c>
     </row>
     <row r="1868">
@@ -19110,7 +19110,7 @@
         </is>
       </c>
       <c r="B1870" t="n">
-        <v>-0.007566385623475225</v>
+        <v>-0.007566385623475447</v>
       </c>
     </row>
     <row r="1871">
@@ -19130,7 +19130,17 @@
         </is>
       </c>
       <c r="B1872" t="n">
-        <v>0.02371801219346792</v>
+        <v>0.02371801219346814</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>20260320</t>
+        </is>
+      </c>
+      <c r="B1873" t="n">
+        <v>-0.02133711846221431</v>
       </c>
     </row>
   </sheetData>

--- a/data/收益明细.xlsx
+++ b/data/收益明细.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1878"/>
+  <dimension ref="A1:B1879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.01572404920229209</v>
+        <v>-0.01572404920229198</v>
       </c>
     </row>
     <row r="7">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.02482113306987566</v>
+        <v>-0.02482113306987555</v>
       </c>
     </row>
     <row r="11">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02359580203466405</v>
+        <v>0.0235958020346636</v>
       </c>
     </row>
     <row r="12">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001036335405173228</v>
+        <v>0.00103633540517345</v>
       </c>
     </row>
     <row r="13">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0002830345069972928</v>
+        <v>0.0002830345069970708</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0002762734190075999</v>
+        <v>-0.0002762734190071559</v>
       </c>
     </row>
     <row r="15">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0001149061768455084</v>
+        <v>-0.0001149061768457305</v>
       </c>
     </row>
     <row r="16">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01271406228042671</v>
+        <v>0.01271406228042693</v>
       </c>
     </row>
     <row r="19">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01770705818691232</v>
+        <v>0.01770705818691187</v>
       </c>
     </row>
     <row r="20">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.002380161989391949</v>
+        <v>-0.002380161989391505</v>
       </c>
     </row>
     <row r="21">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0078953901868557</v>
+        <v>0.007895390186855478</v>
       </c>
     </row>
     <row r="22">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001300529274144813</v>
+        <v>0.001300529274145257</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.01419384410462055</v>
+        <v>-0.01419384410462099</v>
       </c>
     </row>
     <row r="26">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.02093991851095012</v>
+        <v>-0.0209399185109499</v>
       </c>
     </row>
     <row r="27">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.003845426417374731</v>
+        <v>-0.003845426417374953</v>
       </c>
     </row>
     <row r="28">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0249584099948289</v>
+        <v>-0.02495840999482879</v>
       </c>
     </row>
     <row r="29">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002525375130285834</v>
+        <v>-0.002525375130286056</v>
       </c>
     </row>
     <row r="31">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01973963642471421</v>
+        <v>0.01973963642471444</v>
       </c>
     </row>
     <row r="32">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001884967431883489</v>
+        <v>-0.001884967431883267</v>
       </c>
     </row>
     <row r="35">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.01742029164600889</v>
+        <v>-0.017420291646009</v>
       </c>
     </row>
     <row r="36">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.01117478896934132</v>
+        <v>-0.01117478896934154</v>
       </c>
     </row>
     <row r="37">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0115287847481369</v>
+        <v>0.01152878474813712</v>
       </c>
     </row>
     <row r="39">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.01068624917555994</v>
+        <v>-0.01068624917556005</v>
       </c>
     </row>
     <row r="41">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.01329983493200615</v>
+        <v>0.01329983493200593</v>
       </c>
     </row>
     <row r="44">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0147089054839411</v>
+        <v>-0.01470890548394099</v>
       </c>
     </row>
     <row r="47">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001516813142787621</v>
+        <v>0.001516813142787399</v>
       </c>
     </row>
     <row r="48">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0005533604486389621</v>
+        <v>0.0005533604486391841</v>
       </c>
     </row>
     <row r="49">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.007930184982597455</v>
+        <v>0.007930184982597233</v>
       </c>
     </row>
     <row r="50">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.007840190198024288</v>
+        <v>-0.007840190198024177</v>
       </c>
     </row>
     <row r="51">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.02053072188950733</v>
+        <v>-0.02053072188950744</v>
       </c>
     </row>
     <row r="54">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.001853243456947928</v>
+        <v>-0.001853243456947817</v>
       </c>
     </row>
     <row r="55">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0005818242947028818</v>
+        <v>-0.0005818242947029928</v>
       </c>
     </row>
     <row r="56">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.001965305837336229</v>
+        <v>-0.00196530583733634</v>
       </c>
     </row>
     <row r="58">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.01025040173899894</v>
+        <v>-0.01025040173899872</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.01423955478730554</v>
+        <v>0.01423955478730576</v>
       </c>
     </row>
     <row r="60">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.00606834310060389</v>
+        <v>0.006068343100603446</v>
       </c>
     </row>
     <row r="61">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.001618041480692445</v>
+        <v>-0.001618041480692334</v>
       </c>
     </row>
     <row r="64">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.01366958542725949</v>
+        <v>0.01366958542725971</v>
       </c>
     </row>
     <row r="67">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.03071406754613115</v>
+        <v>-0.03071406754613137</v>
       </c>
     </row>
     <row r="68">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.0794284173998604</v>
+        <v>-0.07942841739986028</v>
       </c>
     </row>
     <row r="71">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.01660011531513839</v>
+        <v>-0.01660011531513828</v>
       </c>
     </row>
     <row r="73">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.009629834844572249</v>
+        <v>0.009629834844571805</v>
       </c>
     </row>
     <row r="75">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.02379802663933739</v>
+        <v>-0.02379802663933717</v>
       </c>
     </row>
     <row r="76">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.01157491216086104</v>
+        <v>-0.01157491216086137</v>
       </c>
     </row>
     <row r="79">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0008419080480057684</v>
+        <v>0.0008419080480059904</v>
       </c>
     </row>
     <row r="80">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.001611284363969623</v>
+        <v>-0.001611284363969401</v>
       </c>
     </row>
     <row r="81">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.01353832413503753</v>
+        <v>0.01353832413503708</v>
       </c>
     </row>
     <row r="82">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.01171909526792148</v>
+        <v>-0.01171909526792103</v>
       </c>
     </row>
     <row r="83">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.01554090893306848</v>
+        <v>0.01554090893306825</v>
       </c>
     </row>
     <row r="84">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.001314389597141918</v>
+        <v>0.001314389597141696</v>
       </c>
     </row>
     <row r="90">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.04487543075745504</v>
+        <v>-0.04487543075745515</v>
       </c>
     </row>
     <row r="102">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.003506676924670993</v>
+        <v>0.003506676924671437</v>
       </c>
     </row>
     <row r="104">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.01717319003679041</v>
+        <v>0.01717319003678996</v>
       </c>
     </row>
     <row r="105">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.02806041603567322</v>
+        <v>0.02806041603567344</v>
       </c>
     </row>
     <row r="108">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.01988985853059544</v>
+        <v>-0.01988985853059533</v>
       </c>
     </row>
     <row r="111">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.001760312165028477</v>
+        <v>0.001760312165028255</v>
       </c>
     </row>
     <row r="112">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.0009545143989889704</v>
+        <v>-0.0009545143989890814</v>
       </c>
     </row>
     <row r="115">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.006605522591641266</v>
+        <v>0.006605522591641488</v>
       </c>
     </row>
     <row r="116">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.02328849049392767</v>
+        <v>-0.02328849049392756</v>
       </c>
     </row>
     <row r="117">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.0003016526979852108</v>
+        <v>-0.0003016526979855438</v>
       </c>
     </row>
     <row r="118">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.009754986468771154</v>
+        <v>-0.009754986468771265</v>
       </c>
     </row>
     <row r="122">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.0062851318911058</v>
+        <v>-0.006285131891105911</v>
       </c>
     </row>
     <row r="124">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.01315178967089414</v>
+        <v>0.01315178967089436</v>
       </c>
     </row>
     <row r="125">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.02128995667108347</v>
+        <v>-0.02128995667108358</v>
       </c>
     </row>
     <row r="126">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.00908474837449913</v>
+        <v>-0.009084748374499019</v>
       </c>
     </row>
     <row r="128">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.002058478204177483</v>
+        <v>0.002058478204177261</v>
       </c>
     </row>
     <row r="129">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.01446645442484762</v>
+        <v>0.01446645442484784</v>
       </c>
     </row>
     <row r="131">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0005815331128491419</v>
+        <v>0.0005815331128493639</v>
       </c>
     </row>
     <row r="133">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.004238824136808206</v>
+        <v>-0.004238824136808317</v>
       </c>
     </row>
     <row r="134">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-0.003723496416957572</v>
+        <v>-0.003723496416957794</v>
       </c>
     </row>
     <row r="136">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.01331679645708284</v>
+        <v>-0.01331679645708272</v>
       </c>
     </row>
     <row r="139">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.003361413291861792</v>
+        <v>0.003361413291862014</v>
       </c>
     </row>
     <row r="143">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.004837334158117379</v>
+        <v>0.004837334158117157</v>
       </c>
     </row>
     <row r="144">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.008830116758630879</v>
+        <v>-0.008830116758631101</v>
       </c>
     </row>
     <row r="149">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.02485377751131201</v>
+        <v>0.02485377751131224</v>
       </c>
     </row>
     <row r="150">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.01784074568619753</v>
+        <v>0.01784074568619776</v>
       </c>
     </row>
     <row r="153">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.009033886812290337</v>
+        <v>0.009033886812289893</v>
       </c>
     </row>
     <row r="154">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-0.007732975320105417</v>
+        <v>-0.007732975320104973</v>
       </c>
     </row>
     <row r="155">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.03214452421634473</v>
+        <v>0.03214452421634428</v>
       </c>
     </row>
     <row r="156">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.002353167351975438</v>
+        <v>0.00235316735197566</v>
       </c>
     </row>
     <row r="157">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-0.00631456467637026</v>
+        <v>-0.006314564676370482</v>
       </c>
     </row>
     <row r="159">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.01816743827592315</v>
+        <v>0.01816743827592338</v>
       </c>
     </row>
     <row r="160">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.01083382668003274</v>
+        <v>0.01083382668003252</v>
       </c>
     </row>
     <row r="164">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.007047262977707192</v>
+        <v>0.007047262977707636</v>
       </c>
     </row>
     <row r="165">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.006753402007583009</v>
+        <v>0.006753402007582787</v>
       </c>
     </row>
     <row r="166">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-0.04380152335984722</v>
+        <v>-0.04380152335984699</v>
       </c>
     </row>
     <row r="170">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.03897267939271387</v>
+        <v>0.03897267939271365</v>
       </c>
     </row>
     <row r="171">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.01576083647396964</v>
+        <v>0.01576083647396942</v>
       </c>
     </row>
     <row r="172">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-0.01287047771256211</v>
+        <v>-0.01287047771256189</v>
       </c>
     </row>
     <row r="173">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.02206458867388972</v>
+        <v>0.02206458867388994</v>
       </c>
     </row>
     <row r="176">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.004439060335924783</v>
+        <v>0.004439060335925005</v>
       </c>
     </row>
     <row r="177">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-0.001520686523289849</v>
+        <v>-0.00152068652328996</v>
       </c>
     </row>
     <row r="178">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.008013929700946942</v>
+        <v>0.008013929700947386</v>
       </c>
     </row>
     <row r="179">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.01031824873170417</v>
+        <v>0.01031824873170395</v>
       </c>
     </row>
     <row r="180">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-0.02444113099089784</v>
+        <v>-0.02444113099089773</v>
       </c>
     </row>
     <row r="182">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.01248103249230414</v>
+        <v>0.01248103249230392</v>
       </c>
     </row>
     <row r="183">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.002428842704102374</v>
+        <v>0.002428842704102596</v>
       </c>
     </row>
     <row r="187">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.002689492976064134</v>
+        <v>0.002689492976064356</v>
       </c>
     </row>
     <row r="188">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.01232785125458724</v>
+        <v>0.0123278512545868</v>
       </c>
     </row>
     <row r="189">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.003925367534164392</v>
+        <v>0.003925367534164614</v>
       </c>
     </row>
     <row r="190">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-0.002302682745264795</v>
+        <v>-0.002302682745265017</v>
       </c>
     </row>
     <row r="195">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-0.005911016976345773</v>
+        <v>-0.005911016976345662</v>
       </c>
     </row>
     <row r="198">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.01004284323608684</v>
+        <v>0.01004284323608662</v>
       </c>
     </row>
     <row r="199">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-0.008152161234351252</v>
+        <v>-0.008152161234351141</v>
       </c>
     </row>
     <row r="200">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-0.01554208955406389</v>
+        <v>-0.01554208955406366</v>
       </c>
     </row>
     <row r="201">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>-0.03137538638839776</v>
+        <v>-0.03137538638839787</v>
       </c>
     </row>
     <row r="203">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-0.007432472344896524</v>
+        <v>-0.007432472344896857</v>
       </c>
     </row>
     <row r="204">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-0.01586853705332925</v>
+        <v>-0.0158685370533288</v>
       </c>
     </row>
     <row r="205">
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-0.007820309839754236</v>
+        <v>-0.007820309839754014</v>
       </c>
     </row>
     <row r="212">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.01324712114319904</v>
+        <v>0.01324712114319859</v>
       </c>
     </row>
     <row r="215">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-0.03583974939327306</v>
+        <v>-0.03583974939327284</v>
       </c>
     </row>
     <row r="216">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-0.004714606047454106</v>
+        <v>-0.004714606047453884</v>
       </c>
     </row>
     <row r="219">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-0.02549538223839132</v>
+        <v>-0.02549538223839143</v>
       </c>
     </row>
     <row r="220">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.0030072393679208</v>
+        <v>0.003007239367921244</v>
       </c>
     </row>
     <row r="223">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.00782286390458653</v>
+        <v>0.007822863904586086</v>
       </c>
     </row>
     <row r="224">
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>-0.006981161745919007</v>
+        <v>-0.006981161745918896</v>
       </c>
     </row>
     <row r="225">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.007676112411729497</v>
+        <v>0.007676112411729719</v>
       </c>
     </row>
     <row r="226">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>-0.01203276405873144</v>
+        <v>-0.01203276405873188</v>
       </c>
     </row>
     <row r="227">
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>-0.01656158391641094</v>
+        <v>-0.01656158391641072</v>
       </c>
     </row>
     <row r="228">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.004457846351092476</v>
+        <v>0.004457846351092698</v>
       </c>
     </row>
     <row r="229">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-0.01888008452601775</v>
+        <v>-0.01888008452601797</v>
       </c>
     </row>
     <row r="230">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.0116685781428485</v>
+        <v>0.01166857814284827</v>
       </c>
     </row>
     <row r="231">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.03093200369612159</v>
+        <v>0.03093200369612181</v>
       </c>
     </row>
     <row r="232">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-0.02230753052044887</v>
+        <v>-0.02230753052044865</v>
       </c>
     </row>
     <row r="235">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.001288611809082019</v>
+        <v>0.001288611809081797</v>
       </c>
     </row>
     <row r="236">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.008182175199939579</v>
+        <v>0.008182175199939801</v>
       </c>
     </row>
     <row r="239">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.01288002243911635</v>
+        <v>0.01288002243911612</v>
       </c>
     </row>
     <row r="240">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.00765432241265751</v>
+        <v>0.007654322412657732</v>
       </c>
     </row>
     <row r="247">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.003156926335925236</v>
+        <v>0.003156926335925014</v>
       </c>
     </row>
     <row r="249">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.009953939649229415</v>
+        <v>0.009953939649229637</v>
       </c>
     </row>
     <row r="250">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>-0.02475288513342866</v>
+        <v>-0.02475288513342844</v>
       </c>
     </row>
     <row r="251">
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>-0.004173510490497523</v>
+        <v>-0.004173510490497634</v>
       </c>
     </row>
     <row r="252">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>-0.003399587844266416</v>
+        <v>-0.003399587844266749</v>
       </c>
     </row>
     <row r="253">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>-0.002933628876201189</v>
+        <v>-0.0029336288762013</v>
       </c>
     </row>
     <row r="254">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.008188714848466283</v>
+        <v>0.008188714848466949</v>
       </c>
     </row>
     <row r="255">
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.009926371010728907</v>
+        <v>0.009926371010728685</v>
       </c>
     </row>
     <row r="257">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.001379341962310265</v>
+        <v>0.001379341962310043</v>
       </c>
     </row>
     <row r="260">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>-0.02430784936589214</v>
+        <v>-0.02430784936589159</v>
       </c>
     </row>
     <row r="261">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.01545389369577221</v>
+        <v>0.01545389369577177</v>
       </c>
     </row>
     <row r="262">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.01302890856467109</v>
+        <v>0.01302890856467132</v>
       </c>
     </row>
     <row r="264">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>-0.001001787967991996</v>
+        <v>-0.001001787967992107</v>
       </c>
     </row>
     <row r="265">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>-0.001369522740997886</v>
+        <v>-0.001369522740997664</v>
       </c>
     </row>
     <row r="267">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>-0.006195873821834064</v>
+        <v>-0.006195873821834397</v>
       </c>
     </row>
     <row r="268">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>-0.003875213419964774</v>
+        <v>-0.003875213419964552</v>
       </c>
     </row>
     <row r="269">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.008929135062472948</v>
+        <v>0.008929135062472726</v>
       </c>
     </row>
     <row r="274">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>-0.01036636592066786</v>
+        <v>-0.01036636592066764</v>
       </c>
     </row>
     <row r="275">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>-0.001090543703367808</v>
+        <v>-0.00109054370336803</v>
       </c>
     </row>
     <row r="277">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.008449611388157141</v>
+        <v>0.008449611388157585</v>
       </c>
     </row>
     <row r="278">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.02683243182111195</v>
+        <v>0.0268324318211115</v>
       </c>
     </row>
     <row r="281">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>-0.00290058493460188</v>
+        <v>-0.002900584934601658</v>
       </c>
     </row>
     <row r="282">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>-0.003094739345946174</v>
+        <v>-0.003094739345945841</v>
       </c>
     </row>
     <row r="284">
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>-0.009092287423267731</v>
+        <v>-0.009092287423268064</v>
       </c>
     </row>
     <row r="285">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>-0.011810053845697</v>
+        <v>-0.01181005384569678</v>
       </c>
     </row>
     <row r="286">
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>-0.02111459339307475</v>
+        <v>-0.02111459339307442</v>
       </c>
     </row>
     <row r="290">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.02973578085217965</v>
+        <v>0.02973578085217921</v>
       </c>
     </row>
     <row r="291">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.01089437243547264</v>
+        <v>0.01089437243547287</v>
       </c>
     </row>
     <row r="293">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.01223922349769868</v>
+        <v>0.01223922349769846</v>
       </c>
     </row>
     <row r="294">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.001914057068349573</v>
+        <v>0.001914057068349795</v>
       </c>
     </row>
     <row r="295">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.02006307618460035</v>
+        <v>0.02006307618460013</v>
       </c>
     </row>
     <row r="296">
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.006155233025518125</v>
+        <v>0.006155233025518347</v>
       </c>
     </row>
     <row r="297">
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>-0.005523292544501235</v>
+        <v>-0.005523292544501457</v>
       </c>
     </row>
     <row r="298">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.006675465865011443</v>
+        <v>0.006675465865010999</v>
       </c>
     </row>
     <row r="300">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.00864995668149926</v>
+        <v>0.008649956681499482</v>
       </c>
     </row>
     <row r="302">
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.01355506652850247</v>
+        <v>0.01355506652850225</v>
       </c>
     </row>
     <row r="303">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>-0.005541326993856566</v>
+        <v>-0.005541326993856455</v>
       </c>
     </row>
     <row r="304">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>-0.006010935248334182</v>
+        <v>-0.006010935248334293</v>
       </c>
     </row>
     <row r="305">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>-0.00135216149689088</v>
+        <v>-0.001352161496890325</v>
       </c>
     </row>
     <row r="306">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>-0.02334943685624769</v>
+        <v>-0.02334943685624824</v>
       </c>
     </row>
     <row r="307">
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>-0.0210656075403538</v>
+        <v>-0.02106560754035358</v>
       </c>
     </row>
     <row r="308">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>-0.02020860387000645</v>
+        <v>-0.02020860387000667</v>
       </c>
     </row>
     <row r="310">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>-0.0005930943150083134</v>
+        <v>-0.0005930943150077583</v>
       </c>
     </row>
     <row r="311">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.01101039574764084</v>
+        <v>0.01101039574764062</v>
       </c>
     </row>
     <row r="313">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>-0.003522594787756073</v>
+        <v>-0.003522594787755962</v>
       </c>
     </row>
     <row r="314">
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.01088365655079371</v>
+        <v>0.01088365655079282</v>
       </c>
     </row>
     <row r="315">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>-0.00153342422972691</v>
+        <v>-0.001533424229726688</v>
       </c>
     </row>
     <row r="317">
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>-0.006510350869090575</v>
+        <v>-0.006510350869090242</v>
       </c>
     </row>
     <row r="320">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>-0.005486541052190042</v>
+        <v>-0.005486541052190597</v>
       </c>
     </row>
     <row r="322">
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.001595259789025194</v>
+        <v>0.001595259789025638</v>
       </c>
     </row>
     <row r="323">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>-0.001705044302586667</v>
+        <v>-0.001705044302587111</v>
       </c>
     </row>
     <row r="324">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.008334179621441118</v>
+        <v>0.008334179621440896</v>
       </c>
     </row>
     <row r="325">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>-0.01449800143915247</v>
+        <v>-0.01449800143915192</v>
       </c>
     </row>
     <row r="326">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>-0.01232677210542976</v>
+        <v>-0.01232677210542998</v>
       </c>
     </row>
     <row r="327">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>-0.006854435087049748</v>
+        <v>-0.00685443508704997</v>
       </c>
     </row>
     <row r="328">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.01220059766004677</v>
+        <v>0.012200597660047</v>
       </c>
     </row>
     <row r="329">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>-0.001263157861184028</v>
+        <v>-0.00126315786118425</v>
       </c>
     </row>
     <row r="331">
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>-0.005500699935398701</v>
+        <v>-0.005500699935399256</v>
       </c>
     </row>
     <row r="332">
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.004488847892388126</v>
+        <v>0.004488847892388792</v>
       </c>
     </row>
     <row r="333">
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>-0.02448851298872012</v>
+        <v>-0.0244885129887199</v>
       </c>
     </row>
     <row r="335">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.008275082204899364</v>
+        <v>0.008275082204899142</v>
       </c>
     </row>
     <row r="336">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>-0.005173421113665255</v>
+        <v>-0.005173421113665366</v>
       </c>
     </row>
     <row r="337">
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.007236830405759953</v>
+        <v>0.007236830405760175</v>
       </c>
     </row>
     <row r="338">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>-0.01014791819777405</v>
+        <v>-0.01014791819777394</v>
       </c>
     </row>
     <row r="339">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.006374669706664893</v>
+        <v>0.006374669706664227</v>
       </c>
     </row>
     <row r="340">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>-0.01135995920824207</v>
+        <v>-0.01135995920824184</v>
       </c>
     </row>
     <row r="342">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>-0.008379181153892579</v>
+        <v>-0.008379181153892246</v>
       </c>
     </row>
     <row r="343">
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>-0.01387592626980594</v>
+        <v>-0.01387592626980616</v>
       </c>
     </row>
     <row r="344">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>-0.002782156350307763</v>
+        <v>-0.002782156350307652</v>
       </c>
     </row>
     <row r="345">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>-0.003610320803900779</v>
+        <v>-0.003610320803901002</v>
       </c>
     </row>
     <row r="347">
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>-0.009184960887139937</v>
+        <v>-0.009184960887139715</v>
       </c>
     </row>
     <row r="348">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.001007103384676133</v>
+        <v>0.001007103384675911</v>
       </c>
     </row>
     <row r="349">
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.01163120442100829</v>
+        <v>0.01163120442100807</v>
       </c>
     </row>
     <row r="351">
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.0066182085746469</v>
+        <v>0.006618208574647122</v>
       </c>
     </row>
     <row r="353">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.002151945837539859</v>
+        <v>0.002151945837540081</v>
       </c>
     </row>
     <row r="356">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>-0.006191151837085629</v>
+        <v>-0.006191151837085851</v>
       </c>
     </row>
     <row r="357">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>-0.001880755448676497</v>
+        <v>-0.001880755448676164</v>
       </c>
     </row>
     <row r="358">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.02701511919701227</v>
+        <v>0.02701511919701183</v>
       </c>
     </row>
     <row r="360">
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.006522330516067543</v>
+        <v>0.006522330516067987</v>
       </c>
     </row>
     <row r="362">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.005299692600070127</v>
+        <v>0.005299692600069905</v>
       </c>
     </row>
     <row r="363">
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>-0.005655717661048665</v>
+        <v>-0.005655717661048443</v>
       </c>
     </row>
     <row r="364">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>-0.02311019446650908</v>
+        <v>-0.0231101944665093</v>
       </c>
     </row>
     <row r="365">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.01286389659004628</v>
+        <v>0.01286389659004605</v>
       </c>
     </row>
     <row r="366">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>-0.0001029041837979916</v>
+        <v>-0.0001029041837977696</v>
       </c>
     </row>
     <row r="367">
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.008999472983212575</v>
+        <v>0.008999472983212797</v>
       </c>
     </row>
     <row r="368">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>-0.005860139699446321</v>
+        <v>-0.005860139699447098</v>
       </c>
     </row>
     <row r="369">
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.01828277426452374</v>
+        <v>0.01828277426452418</v>
       </c>
     </row>
     <row r="370">
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.00909577748498358</v>
+        <v>0.009095777484984024</v>
       </c>
     </row>
     <row r="374">
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>-0.02053844666690186</v>
+        <v>-0.0205384466669023</v>
       </c>
     </row>
     <row r="376">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.003342652224972209</v>
+        <v>0.003342652224972431</v>
       </c>
     </row>
     <row r="378">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.001242923364402237</v>
+        <v>0.001242923364402682</v>
       </c>
     </row>
     <row r="380">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>-0.008146908209493264</v>
+        <v>-0.008146908209493597</v>
       </c>
     </row>
     <row r="381">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.01600727832757132</v>
+        <v>0.0160072783275711</v>
       </c>
     </row>
     <row r="384">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>-0.01481711756951409</v>
+        <v>-0.01481711756951387</v>
       </c>
     </row>
     <row r="385">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>-0.03308939982960224</v>
+        <v>-0.03308939982960246</v>
       </c>
     </row>
     <row r="387">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>-0.09131435188878068</v>
+        <v>-0.09131435188878045</v>
       </c>
     </row>
     <row r="388">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.003038939331235335</v>
+        <v>0.003038939331235113</v>
       </c>
     </row>
     <row r="389">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.01812735598908177</v>
+        <v>0.01812735598908244</v>
       </c>
     </row>
     <row r="391">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.004965689461810197</v>
+        <v>0.004965689461809975</v>
       </c>
     </row>
     <row r="392">
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.01086509874309893</v>
+        <v>0.01086509874309871</v>
       </c>
     </row>
     <row r="393">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>-0.009827756990878678</v>
+        <v>-0.009827756990878567</v>
       </c>
     </row>
     <row r="394">
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>-0.008465207238736228</v>
+        <v>-0.008465207238736117</v>
       </c>
     </row>
     <row r="396">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.008436786564158805</v>
+        <v>0.008436786564158583</v>
       </c>
     </row>
     <row r="403">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>-0.008826251506837357</v>
+        <v>-0.008826251506837024</v>
       </c>
     </row>
     <row r="404">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.009106102770877644</v>
+        <v>0.009106102770877866</v>
       </c>
     </row>
     <row r="406">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>-0.04896627391785813</v>
+        <v>-0.04896627391785846</v>
       </c>
     </row>
     <row r="407">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.04172978601929511</v>
+        <v>0.04172978601929489</v>
       </c>
     </row>
     <row r="408">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.01216304385588263</v>
+        <v>0.01216304385588285</v>
       </c>
     </row>
     <row r="409">
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.01936679716532286</v>
+        <v>0.0193667971653233</v>
       </c>
     </row>
     <row r="410">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.01224126726095753</v>
+        <v>0.01224126726095709</v>
       </c>
     </row>
     <row r="411">
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.003113205722677259</v>
+        <v>0.003113205722677481</v>
       </c>
     </row>
     <row r="412">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>-0.03349448699330726</v>
+        <v>-0.03349448699330715</v>
       </c>
     </row>
     <row r="413">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.01060550488299206</v>
+        <v>0.01060550488299228</v>
       </c>
     </row>
     <row r="414">
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>-0.00363690084746715</v>
+        <v>-0.003636900847467373</v>
       </c>
     </row>
     <row r="415">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>-0.02557605268971042</v>
+        <v>-0.02557605268971053</v>
       </c>
     </row>
     <row r="416">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>-0.02296701761624353</v>
+        <v>-0.0229670176162432</v>
       </c>
     </row>
     <row r="417">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>-0.03491033290410706</v>
+        <v>-0.03491033290410739</v>
       </c>
     </row>
     <row r="418">
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>-0.006209158219779187</v>
+        <v>-0.006209158219778965</v>
       </c>
     </row>
     <row r="419">
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>-0.01526608795400342</v>
+        <v>-0.01526608795400364</v>
       </c>
     </row>
     <row r="420">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.01033798928833729</v>
+        <v>0.01033798928833707</v>
       </c>
     </row>
     <row r="421">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.01490065915636429</v>
+        <v>0.01490065915636452</v>
       </c>
     </row>
     <row r="422">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>-0.03458288890524741</v>
+        <v>-0.03458288890524719</v>
       </c>
     </row>
     <row r="423">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.02475000900510982</v>
+        <v>0.0247500090051096</v>
       </c>
     </row>
     <row r="424">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.01490309600931927</v>
+        <v>0.01490309600931949</v>
       </c>
     </row>
     <row r="425">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>-0.006893406642113131</v>
+        <v>-0.006893406642112909</v>
       </c>
     </row>
     <row r="426">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.0009047571579681168</v>
+        <v>0.0009047571579676728</v>
       </c>
     </row>
     <row r="427">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.03037471200362951</v>
+        <v>0.03037471200362929</v>
       </c>
     </row>
     <row r="433">
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.001231795358022314</v>
+        <v>0.001231795358022536</v>
       </c>
     </row>
     <row r="434">
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.0007396833555963767</v>
+        <v>0.0007396833555961546</v>
       </c>
     </row>
     <row r="435">
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>-0.02181224228192313</v>
+        <v>-0.02181224228192291</v>
       </c>
     </row>
     <row r="436">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>-0.003335737501230507</v>
+        <v>-0.003335737501230285</v>
       </c>
     </row>
     <row r="437">
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.01987431504523718</v>
+        <v>0.01987431504523696</v>
       </c>
     </row>
     <row r="438">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.0081354472842321</v>
+        <v>0.008135447284232322</v>
       </c>
     </row>
     <row r="441">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.02167770844210826</v>
+        <v>0.02167770844210803</v>
       </c>
     </row>
     <row r="442">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.006475397478528766</v>
+        <v>0.006475397478528322</v>
       </c>
     </row>
     <row r="444">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>-0.0004944293018722679</v>
+        <v>-0.0004944293018717127</v>
       </c>
     </row>
     <row r="445">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>-0.02149598040882583</v>
+        <v>-0.02149598040882561</v>
       </c>
     </row>
     <row r="446">
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>-0.014430282947552</v>
+        <v>-0.01443028294755222</v>
       </c>
     </row>
     <row r="447">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>-0.02248491331951818</v>
+        <v>-0.02248491331951796</v>
       </c>
     </row>
     <row r="448">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.00566209108907012</v>
+        <v>0.005662091089069676</v>
       </c>
     </row>
     <row r="449">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.01993196853143875</v>
+        <v>0.01993196853143897</v>
       </c>
     </row>
     <row r="450">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>-0.002313182865839036</v>
+        <v>-0.002313182865839147</v>
       </c>
     </row>
     <row r="452">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.00774727495116001</v>
+        <v>0.007747274951159788</v>
       </c>
     </row>
     <row r="456">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>-0.007643306224190183</v>
+        <v>-0.00764330622418985</v>
       </c>
     </row>
     <row r="457">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.006920068579011174</v>
+        <v>0.006920068579010952</v>
       </c>
     </row>
     <row r="458">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.005232954186440431</v>
+        <v>0.005232954186441097</v>
       </c>
     </row>
     <row r="459">
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.01210303384659484</v>
+        <v>0.01210303384659417</v>
       </c>
     </row>
     <row r="460">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>-0.01724962403879438</v>
+        <v>-0.01724962403879393</v>
       </c>
     </row>
     <row r="461">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.009299351689033619</v>
+        <v>0.009299351689033397</v>
       </c>
     </row>
     <row r="464">
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.001972104666916552</v>
+        <v>0.00197210466691633</v>
       </c>
     </row>
     <row r="467">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.02863390981250213</v>
+        <v>0.02863390981250191</v>
       </c>
     </row>
     <row r="469">
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>-0.0110317957187881</v>
+        <v>-0.01103179571878754</v>
       </c>
     </row>
     <row r="471">
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.005266615557885546</v>
+        <v>0.005266615557885324</v>
       </c>
     </row>
     <row r="472">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>-0.008933623130661039</v>
+        <v>-0.008933623130660817</v>
       </c>
     </row>
     <row r="473">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.001938198312465111</v>
+        <v>0.001938198312464889</v>
       </c>
     </row>
     <row r="475">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>-0.001060223337485233</v>
+        <v>-0.001060223337485011</v>
       </c>
     </row>
     <row r="476">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>-0.009176808538234105</v>
+        <v>-0.009176808538234438</v>
       </c>
     </row>
     <row r="477">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>-0.0005272518926355829</v>
+        <v>-0.0005272518926352499</v>
       </c>
     </row>
     <row r="478">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>-0.006246128305675169</v>
+        <v>-0.00624612830567528</v>
       </c>
     </row>
     <row r="479">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.01811142667082533</v>
+        <v>0.01811142667082555</v>
       </c>
     </row>
     <row r="480">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.004757453237038245</v>
+        <v>0.004757453237038023</v>
       </c>
     </row>
     <row r="481">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>-0.002878368490649819</v>
+        <v>-0.002878368490650263</v>
       </c>
     </row>
     <row r="482">
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.002073991493245275</v>
+        <v>0.002073991493245497</v>
       </c>
     </row>
     <row r="483">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>-0.004314204397194432</v>
+        <v>-0.004314204397194654</v>
       </c>
     </row>
     <row r="484">
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.004097487506269371</v>
+        <v>0.004097487506269593</v>
       </c>
     </row>
     <row r="485">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>-0.005492885407306081</v>
+        <v>-0.005492885407306192</v>
       </c>
     </row>
     <row r="486">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>-0.002644135485008525</v>
+        <v>-0.002644135485008303</v>
       </c>
     </row>
     <row r="487">
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.02355079610812716</v>
+        <v>0.02355079610812694</v>
       </c>
     </row>
     <row r="488">
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.003832492134195453</v>
+        <v>0.003832492134195897</v>
       </c>
     </row>
     <row r="489">
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.009493299217094853</v>
+        <v>0.009493299217095297</v>
       </c>
     </row>
     <row r="490">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.004874150743594541</v>
+        <v>0.004874150743594319</v>
       </c>
     </row>
     <row r="491">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.0123888217947139</v>
+        <v>0.01238882179471368</v>
       </c>
     </row>
     <row r="493">
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.02822860587138276</v>
+        <v>0.02822860587138254</v>
       </c>
     </row>
     <row r="495">
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>-0.0145278925920973</v>
+        <v>-0.01452789259209708</v>
       </c>
     </row>
     <row r="496">
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.03889900706732852</v>
+        <v>0.03889900706732896</v>
       </c>
     </row>
     <row r="497">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>-0.006480168006391729</v>
+        <v>-0.006480168006391951</v>
       </c>
     </row>
     <row r="498">
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>-0.02814688117720843</v>
+        <v>-0.02814688117720832</v>
       </c>
     </row>
     <row r="499">
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.00501147529104129</v>
+        <v>0.005011475291041068</v>
       </c>
     </row>
     <row r="501">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.04951011788526216</v>
+        <v>0.04951011788526194</v>
       </c>
     </row>
     <row r="502">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.01074995876976881</v>
+        <v>0.01074995876976903</v>
       </c>
     </row>
     <row r="503">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>-0.05254779292324019</v>
+        <v>-0.05254779292323997</v>
       </c>
     </row>
     <row r="506">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.008213510075204322</v>
+        <v>0.008213510075203656</v>
       </c>
     </row>
     <row r="507">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.01741503481269557</v>
+        <v>0.01741503481269602</v>
       </c>
     </row>
     <row r="508">
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.01780656547524639</v>
+        <v>0.01780656547524662</v>
       </c>
     </row>
     <row r="509">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.01669654611587412</v>
+        <v>0.01669654611587457</v>
       </c>
     </row>
     <row r="512">
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.004231700811225592</v>
+        <v>0.00423170081122537</v>
       </c>
     </row>
     <row r="514">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>-0.008077353307121893</v>
+        <v>-0.008077353307121671</v>
       </c>
     </row>
     <row r="516">
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.00202205481980644</v>
+        <v>0.002022054819806218</v>
       </c>
     </row>
     <row r="517">
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>-0.02868292357675528</v>
+        <v>-0.02868292357675561</v>
       </c>
     </row>
     <row r="518">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>-0.01298705135180234</v>
+        <v>-0.01298705135180223</v>
       </c>
     </row>
     <row r="519">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.0176868019864922</v>
+        <v>0.01768680198649264</v>
       </c>
     </row>
     <row r="520">
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.009977765461579136</v>
+        <v>0.009977765461578914</v>
       </c>
     </row>
     <row r="523">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.00229893671027015</v>
+        <v>0.002298936710269928</v>
       </c>
     </row>
     <row r="524">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.01418104100344508</v>
+        <v>0.0141810410034453</v>
       </c>
     </row>
     <row r="526">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>-0.02080957825508178</v>
+        <v>-0.02080957825508212</v>
       </c>
     </row>
     <row r="529">
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.006390635458470406</v>
+        <v>0.006390635458470628</v>
       </c>
     </row>
     <row r="530">
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>-0.005409322674520434</v>
+        <v>-0.005409322674520545</v>
       </c>
     </row>
     <row r="533">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>-0.008472748391228357</v>
+        <v>-0.008472748391228135</v>
       </c>
     </row>
     <row r="535">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>4.48538764972195e-05</v>
+        <v>4.485387649699746e-05</v>
       </c>
     </row>
     <row r="536">
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>-0.01669079095289905</v>
+        <v>-0.01669079095289894</v>
       </c>
     </row>
     <row r="537">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.0129903143171306</v>
+        <v>0.01299031431713016</v>
       </c>
     </row>
     <row r="538">
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>-0.03886091819749893</v>
+        <v>-0.03886091819749848</v>
       </c>
     </row>
     <row r="539">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>-0.03221633779963773</v>
+        <v>-0.03221633779963784</v>
       </c>
     </row>
     <row r="540">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.001091302496142976</v>
+        <v>0.00109130249614342</v>
       </c>
     </row>
     <row r="543">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.004322185428705883</v>
+        <v>0.00432218542870566</v>
       </c>
     </row>
     <row r="544">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>-0.0003754175504778745</v>
+        <v>-0.0003754175504779855</v>
       </c>
     </row>
     <row r="547">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>-0.01675788646693299</v>
+        <v>-0.01675788646693321</v>
       </c>
     </row>
     <row r="548">
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.0037713759302056</v>
+        <v>0.003771375930205823</v>
       </c>
     </row>
     <row r="549">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>-0.02525034700361461</v>
+        <v>-0.02525034700361439</v>
       </c>
     </row>
     <row r="550">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>-0.01461878471546241</v>
+        <v>-0.01461878471546252</v>
       </c>
     </row>
     <row r="552">
@@ -5940,7 +5940,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.001590759801055164</v>
+        <v>0.001590759801055386</v>
       </c>
     </row>
     <row r="554">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.02838983318117272</v>
+        <v>0.0283898331811725</v>
       </c>
     </row>
     <row r="555">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.01746235865632362</v>
+        <v>0.0174623586563234</v>
       </c>
     </row>
     <row r="556">
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.004020104940424041</v>
+        <v>0.004020104940423819</v>
       </c>
     </row>
     <row r="557">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>-0.003846846795515613</v>
+        <v>-0.00384684679551528</v>
       </c>
     </row>
     <row r="559">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>-0.005353784530419348</v>
+        <v>-0.005353784530419681</v>
       </c>
     </row>
     <row r="560">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.007911651255398278</v>
+        <v>0.007911651255398722</v>
       </c>
     </row>
     <row r="562">
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>-0.0006360827663565161</v>
+        <v>-0.0006360827663567381</v>
       </c>
     </row>
     <row r="564">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>-0.003608328315347853</v>
+        <v>-0.00360832831534752</v>
       </c>
     </row>
     <row r="569">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>-0.02512374053322208</v>
+        <v>-0.02512374053322264</v>
       </c>
     </row>
     <row r="570">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.01749409490975373</v>
+        <v>0.01749409490975395</v>
       </c>
     </row>
     <row r="572">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>-0.002252944814642777</v>
+        <v>-0.002252944814642666</v>
       </c>
     </row>
     <row r="575">
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.001906925307008089</v>
+        <v>0.001906925307007867</v>
       </c>
     </row>
     <row r="578">
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>-0.001860940325802973</v>
+        <v>-0.001860940325803195</v>
       </c>
     </row>
     <row r="580">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.02114026211980824</v>
+        <v>0.02114026211980846</v>
       </c>
     </row>
     <row r="581">
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.004073477318173424</v>
+        <v>0.004073477318173202</v>
       </c>
     </row>
     <row r="584">
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.01363591550751719</v>
+        <v>0.01363591550751742</v>
       </c>
     </row>
     <row r="586">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>-0.001748455951844141</v>
+        <v>-0.001748455951844252</v>
       </c>
     </row>
     <row r="587">
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>-0.01288210213264129</v>
+        <v>-0.0128821021326414</v>
       </c>
     </row>
     <row r="588">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>-0.007302565802489558</v>
+        <v>-0.007302565802489114</v>
       </c>
     </row>
     <row r="589">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>-0.01023982910577237</v>
+        <v>-0.0102398291057727</v>
       </c>
     </row>
     <row r="593">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>-0.004693092202182392</v>
+        <v>-0.004693092202182059</v>
       </c>
     </row>
     <row r="594">
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.01320752459737107</v>
+        <v>0.01320752459737085</v>
       </c>
     </row>
     <row r="595">
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>-0.003937489043642217</v>
+        <v>-0.003937489043641995</v>
       </c>
     </row>
     <row r="596">
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>-0.001052366189168819</v>
+        <v>-0.001052366189169041</v>
       </c>
     </row>
     <row r="599">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>-0.0001487296738683641</v>
+        <v>-0.0001487296738686972</v>
       </c>
     </row>
     <row r="603">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.0181542856236474</v>
+        <v>0.01815428562364785</v>
       </c>
     </row>
     <row r="604">
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.01156393786613519</v>
+        <v>0.01156393786613497</v>
       </c>
     </row>
     <row r="605">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.01709738385458359</v>
+        <v>0.01709738385458381</v>
       </c>
     </row>
     <row r="606">
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.001374504912855734</v>
+        <v>0.001374504912855956</v>
       </c>
     </row>
     <row r="608">
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.01070874258165055</v>
+        <v>0.01070874258165033</v>
       </c>
     </row>
     <row r="610">
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>-0.01558542855035561</v>
+        <v>-0.01558542855035538</v>
       </c>
     </row>
     <row r="612">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.0170422704517692</v>
+        <v>0.01704227045176898</v>
       </c>
     </row>
     <row r="613">
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.02231524301961718</v>
+        <v>0.02231524301961696</v>
       </c>
     </row>
     <row r="614">
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>-0.001183534588888979</v>
+        <v>-0.001183534588888757</v>
       </c>
     </row>
     <row r="616">
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>-0.01504511376612516</v>
+        <v>-0.01504511376612505</v>
       </c>
     </row>
     <row r="617">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>-0.02768781188503822</v>
+        <v>-0.02768781188503844</v>
       </c>
     </row>
     <row r="618">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.001143720783812308</v>
+        <v>0.00114372078381253</v>
       </c>
     </row>
     <row r="619">
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.01046370205155234</v>
+        <v>0.01046370205155189</v>
       </c>
     </row>
     <row r="621">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>-0.01178512857627367</v>
+        <v>-0.01178512857627345</v>
       </c>
     </row>
     <row r="622">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.01913193901544008</v>
+        <v>0.01913193901543986</v>
       </c>
     </row>
     <row r="624">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.01648272950754981</v>
+        <v>0.01648272950755003</v>
       </c>
     </row>
     <row r="625">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>-0.004193955199407906</v>
+        <v>-0.004193955199407795</v>
       </c>
     </row>
     <row r="626">
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.001884927107094869</v>
+        <v>0.001884927107094425</v>
       </c>
     </row>
     <row r="627">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.006633761807357308</v>
+        <v>0.00663376180735753</v>
       </c>
     </row>
     <row r="628">
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>-0.01110773892570915</v>
+        <v>-0.01110773892570938</v>
       </c>
     </row>
     <row r="629">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>-0.01209497106859692</v>
+        <v>-0.01209497106859703</v>
       </c>
     </row>
     <row r="633">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.01375680540203339</v>
+        <v>0.01375680540203361</v>
       </c>
     </row>
     <row r="635">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>-0.009106928572388262</v>
+        <v>-0.009106928572388373</v>
       </c>
     </row>
     <row r="637">
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>-0.02999871169997914</v>
+        <v>-0.02999871169997892</v>
       </c>
     </row>
     <row r="638">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.005811059899313742</v>
+        <v>0.00581105989931352</v>
       </c>
     </row>
     <row r="642">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.01770234076684862</v>
+        <v>0.01770234076684885</v>
       </c>
     </row>
     <row r="644">
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>-0.003054564348571098</v>
+        <v>-0.003054564348571209</v>
       </c>
     </row>
     <row r="648">
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.02686758816739965</v>
+        <v>0.02686758816739943</v>
       </c>
     </row>
     <row r="650">
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>-0.00262339414910262</v>
+        <v>-0.002623394149102398</v>
       </c>
     </row>
     <row r="651">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>-0.008463543386216243</v>
+        <v>-0.008463543386216132</v>
       </c>
     </row>
     <row r="653">
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>-0.001637104120313704</v>
+        <v>-0.001637104120313815</v>
       </c>
     </row>
     <row r="654">
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>-0.006162735151731158</v>
+        <v>-0.006162735151731269</v>
       </c>
     </row>
     <row r="655">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>-0.02030760893394656</v>
+        <v>-0.02030760893394612</v>
       </c>
     </row>
     <row r="656">
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>-0.01282302577462224</v>
+        <v>-0.01282302577462258</v>
       </c>
     </row>
     <row r="657">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>-0.001187048072705865</v>
+        <v>-0.001187048072706087</v>
       </c>
     </row>
     <row r="659">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.01500969163912447</v>
+        <v>0.01500969163912469</v>
       </c>
     </row>
     <row r="660">
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.007809466681571564</v>
+        <v>0.007809466681571342</v>
       </c>
     </row>
     <row r="663">
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.001636267172866246</v>
+        <v>0.00163626717286669</v>
       </c>
     </row>
     <row r="664">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.02691745233958387</v>
+        <v>0.02691745233958343</v>
       </c>
     </row>
     <row r="665">
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>-0.004261654684649008</v>
+        <v>-0.004261654684648564</v>
       </c>
     </row>
     <row r="666">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>-0.01852656794806462</v>
+        <v>-0.01852656794806495</v>
       </c>
     </row>
     <row r="668">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.001700064093659304</v>
+        <v>0.001700064093659082</v>
       </c>
     </row>
     <row r="671">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.004422957963121421</v>
+        <v>0.004422957963121643</v>
       </c>
     </row>
     <row r="672">
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>-0.000207404085205809</v>
+        <v>-0.0002074040852054759</v>
       </c>
     </row>
     <row r="673">
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.005292779588009555</v>
+        <v>0.005292779588009777</v>
       </c>
     </row>
     <row r="676">
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>-0.002839743308270415</v>
+        <v>-0.002839743308270637</v>
       </c>
     </row>
     <row r="677">
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>-0.01645923237218816</v>
+        <v>-0.01645923237218794</v>
       </c>
     </row>
     <row r="679">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.006456087379874464</v>
+        <v>0.006456087379874242</v>
       </c>
     </row>
     <row r="681">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.01428114335994302</v>
+        <v>0.01428114335994324</v>
       </c>
     </row>
     <row r="683">
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.02239186085432077</v>
+        <v>0.02239186085432054</v>
       </c>
     </row>
     <row r="684">
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.001718081707446473</v>
+        <v>0.001718081707446695</v>
       </c>
     </row>
     <row r="685">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>-0.001793955407853987</v>
+        <v>-0.001793955407854098</v>
       </c>
     </row>
     <row r="686">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.007670762788845487</v>
+        <v>0.007670762788845709</v>
       </c>
     </row>
     <row r="687">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>-0.008673348495482736</v>
+        <v>-0.00867334849548318</v>
       </c>
     </row>
     <row r="688">
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>-0.005787848824408082</v>
+        <v>-0.00578784882440786</v>
       </c>
     </row>
     <row r="689">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>-0.01023804355096469</v>
+        <v>-0.01023804355096458</v>
       </c>
     </row>
     <row r="695">
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>-0.002523742280109209</v>
+        <v>-0.002523742280109098</v>
       </c>
     </row>
     <row r="696">
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>-0.0006672215988469121</v>
+        <v>-0.0006672215988470231</v>
       </c>
     </row>
     <row r="697">
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>-0.006478125983297889</v>
+        <v>-0.006478125983297667</v>
       </c>
     </row>
     <row r="699">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>-0.007638768501797011</v>
+        <v>-0.0076387685017969</v>
       </c>
     </row>
     <row r="701">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.0001384351425266495</v>
+        <v>0.0001384351425268715</v>
       </c>
     </row>
     <row r="705">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.005557164339933696</v>
+        <v>0.005557164339933474</v>
       </c>
     </row>
     <row r="706">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>-0.003373726460938919</v>
+        <v>-0.003373726460938586</v>
       </c>
     </row>
     <row r="707">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.01216754008275567</v>
+        <v>0.01216754008275545</v>
       </c>
     </row>
     <row r="708">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.001478340715997506</v>
+        <v>0.00147834071599795</v>
       </c>
     </row>
     <row r="712">
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>-0.004834084516302739</v>
+        <v>-0.004834084516303183</v>
       </c>
     </row>
     <row r="713">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.0004622694345124412</v>
+        <v>0.0004622694345122191</v>
       </c>
     </row>
     <row r="715">
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>-0.0006463753444282405</v>
+        <v>-0.0006463753444280185</v>
       </c>
     </row>
     <row r="718">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.007283761315447279</v>
+        <v>0.007283761315447057</v>
       </c>
     </row>
     <row r="719">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>-0.001691837374784733</v>
+        <v>-0.001691837374784622</v>
       </c>
     </row>
     <row r="727">
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.007776677403925181</v>
+        <v>0.007776677403925403</v>
       </c>
     </row>
     <row r="730">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>-0.003938692061450921</v>
+        <v>-0.003938692061451032</v>
       </c>
     </row>
     <row r="731">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.008041293706905428</v>
+        <v>0.008041293706905206</v>
       </c>
     </row>
     <row r="732">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>-0.00273428702564682</v>
+        <v>-0.002734287025646487</v>
       </c>
     </row>
     <row r="733">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>-0.004588615118149786</v>
+        <v>-0.004588615118149564</v>
       </c>
     </row>
     <row r="734">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>-0.003365710899696284</v>
+        <v>-0.003365710899696395</v>
       </c>
     </row>
     <row r="736">
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.005614458440339698</v>
+        <v>0.00561445844033992</v>
       </c>
     </row>
     <row r="737">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>-0.01238889369916729</v>
+        <v>-0.01238889369916718</v>
       </c>
     </row>
     <row r="749">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>-0.00817991637043014</v>
+        <v>-0.008179916370430251</v>
       </c>
     </row>
     <row r="752">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>-0.008291937939607696</v>
+        <v>-0.008291937939607807</v>
       </c>
     </row>
     <row r="758">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.01129220468961378</v>
+        <v>0.011292204689614</v>
       </c>
     </row>
     <row r="761">
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>-0.006612738183550126</v>
+        <v>-0.006612738183550237</v>
       </c>
     </row>
     <row r="762">
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>-0.002577114554888293</v>
+        <v>-0.002577114554888404</v>
       </c>
     </row>
     <row r="764">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.00222740557136536</v>
+        <v>0.002227405571365582</v>
       </c>
     </row>
     <row r="765">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>-0.006338144789897249</v>
+        <v>-0.00633814478989736</v>
       </c>
     </row>
     <row r="768">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>-0.00916916182256089</v>
+        <v>-0.009169161822560778</v>
       </c>
     </row>
     <row r="774">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>-0.01323207441516572</v>
+        <v>-0.0132320744151655</v>
       </c>
     </row>
     <row r="775">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.001572674083657688</v>
+        <v>0.001572674083657466</v>
       </c>
     </row>
     <row r="776">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>-0.0001263149668087049</v>
+        <v>-0.0001263149668088159</v>
       </c>
     </row>
     <row r="777">
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.002722966674784333</v>
+        <v>0.002722966674784555</v>
       </c>
     </row>
     <row r="778">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.006369287444235372</v>
+        <v>0.006369287444235594</v>
       </c>
     </row>
     <row r="785">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>-0.01731482823958352</v>
+        <v>-0.01731482823958364</v>
       </c>
     </row>
     <row r="786">
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>-0.004371128133826896</v>
+        <v>-0.004371128133827118</v>
       </c>
     </row>
     <row r="789">
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.0181835216875863</v>
+        <v>0.01818352168758652</v>
       </c>
     </row>
     <row r="791">
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>-0.01795844489313625</v>
+        <v>-0.01795844489313614</v>
       </c>
     </row>
     <row r="793">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>-0.02583203567799441</v>
+        <v>-0.0258320356779943</v>
       </c>
     </row>
     <row r="795">
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.01925279482107856</v>
+        <v>0.01925279482107878</v>
       </c>
     </row>
     <row r="797">
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>-0.004636184424598344</v>
+        <v>-0.004636184424598455</v>
       </c>
     </row>
     <row r="798">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>-0.01802431996932663</v>
+        <v>-0.01802431996932652</v>
       </c>
     </row>
     <row r="799">
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.005328700347206228</v>
+        <v>0.005328700347206006</v>
       </c>
     </row>
     <row r="800">
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.003206510212589331</v>
+        <v>0.003206510212589553</v>
       </c>
     </row>
     <row r="801">
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>-0.01215807615023723</v>
+        <v>-0.01215807615023745</v>
       </c>
     </row>
     <row r="802">
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>-0.006293815757486998</v>
+        <v>-0.006293815757486887</v>
       </c>
     </row>
     <row r="805">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>-0.01335402341728498</v>
+        <v>-0.0133540234172852</v>
       </c>
     </row>
     <row r="807">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>-0.00606836001844302</v>
+        <v>-0.006068360018442465</v>
       </c>
     </row>
     <row r="808">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>-0.002650653403889369</v>
+        <v>-0.002650653403889702</v>
       </c>
     </row>
     <row r="809">
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>-0.01867016110677377</v>
+        <v>-0.01867016110677344</v>
       </c>
     </row>
     <row r="810">
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>-0.01807505154975841</v>
+        <v>-0.01807505154975875</v>
       </c>
     </row>
     <row r="811">
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.01281619668621103</v>
+        <v>0.01281619668621126</v>
       </c>
     </row>
     <row r="813">
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.002738229549205773</v>
+        <v>0.002738229549205329</v>
       </c>
     </row>
     <row r="814">
@@ -8550,7 +8550,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.002539037622713014</v>
+        <v>0.002539037622713236</v>
       </c>
     </row>
     <row r="815">
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.009461147441427897</v>
+        <v>0.009461147441428341</v>
       </c>
     </row>
     <row r="818">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.01662797647068781</v>
+        <v>0.01662797647068759</v>
       </c>
     </row>
     <row r="819">
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.01166462215380748</v>
+        <v>0.01166462215380726</v>
       </c>
     </row>
     <row r="823">
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>-0.01171874014931129</v>
+        <v>-0.01171874014931118</v>
       </c>
     </row>
     <row r="824">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.01436321736450119</v>
+        <v>0.01436321736450097</v>
       </c>
     </row>
     <row r="825">
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>-0.008404541488628015</v>
+        <v>-0.008404541488627904</v>
       </c>
     </row>
     <row r="826">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.005728896102225267</v>
+        <v>0.005728896102225489</v>
       </c>
     </row>
     <row r="827">
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>-0.0005655845203755838</v>
+        <v>-0.0005655845203760279</v>
       </c>
     </row>
     <row r="828">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.008264977637864712</v>
+        <v>0.00826497763786449</v>
       </c>
     </row>
     <row r="829">
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>-0.004898818952927875</v>
+        <v>-0.004898818952927764</v>
       </c>
     </row>
     <row r="830">
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.01122744332805903</v>
+        <v>0.01122744332805881</v>
       </c>
     </row>
     <row r="833">
@@ -8740,7 +8740,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.01603401026523787</v>
+        <v>0.01603401026523854</v>
       </c>
     </row>
     <row r="834">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.01957758187783076</v>
+        <v>0.01957758187783054</v>
       </c>
     </row>
     <row r="835">
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>-0.02969843724133736</v>
+        <v>-0.02969843724133758</v>
       </c>
     </row>
     <row r="838">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>-0.002936994804152437</v>
+        <v>-0.002936994804152326</v>
       </c>
     </row>
     <row r="839">
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.007099160330689358</v>
+        <v>0.007099160330689802</v>
       </c>
     </row>
     <row r="840">
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>-0.003781130413605838</v>
+        <v>-0.003781130413606282</v>
       </c>
     </row>
     <row r="841">
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.007308981235338852</v>
+        <v>0.00730898123533863</v>
       </c>
     </row>
     <row r="842">
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.002507688818412568</v>
+        <v>0.00250768881841279</v>
       </c>
     </row>
     <row r="843">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>-0.009032861983044316</v>
+        <v>-0.009032861983044538</v>
       </c>
     </row>
     <row r="845">
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.003939646246366557</v>
+        <v>0.003939646246366779</v>
       </c>
     </row>
     <row r="846">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>-0.005961273014209678</v>
+        <v>-0.005961273014209789</v>
       </c>
     </row>
     <row r="847">
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>-0.009721085996666767</v>
+        <v>-0.009721085996666434</v>
       </c>
     </row>
     <row r="848">
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.01345349440736121</v>
+        <v>0.01345349440736099</v>
       </c>
     </row>
     <row r="849">
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>-0.0002300118368530057</v>
+        <v>-0.0002300118368528947</v>
       </c>
     </row>
     <row r="851">
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>-0.0183999383002571</v>
+        <v>-0.01839993830025699</v>
       </c>
     </row>
     <row r="852">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.01774275347314824</v>
+        <v>0.01774275347314802</v>
       </c>
     </row>
     <row r="853">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.001903142640189426</v>
+        <v>0.001903142640189648</v>
       </c>
     </row>
     <row r="855">
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>-0.003461214680701374</v>
+        <v>-0.003461214680701263</v>
       </c>
     </row>
     <row r="857">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.01264646475609821</v>
+        <v>0.01264646475609865</v>
       </c>
     </row>
     <row r="858">
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>-0.0242723515746831</v>
+        <v>-0.02427235157468322</v>
       </c>
     </row>
     <row r="859">
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.00667560526956823</v>
+        <v>0.006675605269568008</v>
       </c>
     </row>
     <row r="860">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>-0.02041433200672949</v>
+        <v>-0.02041433200672937</v>
       </c>
     </row>
     <row r="861">
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>-8.407791363873596e-05</v>
+        <v>-8.407791363862493e-05</v>
       </c>
     </row>
     <row r="863">
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.02006744836312468</v>
+        <v>0.02006744836312491</v>
       </c>
     </row>
     <row r="864">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>-0.001978164576057484</v>
+        <v>-0.001978164576057817</v>
       </c>
     </row>
     <row r="865">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>-0.001256135137375436</v>
+        <v>-0.001256135137375547</v>
       </c>
     </row>
     <row r="866">
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.01229459389460641</v>
+        <v>0.01229459389460597</v>
       </c>
     </row>
     <row r="869">
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>-0.03085535503197601</v>
+        <v>-0.0308553550319759</v>
       </c>
     </row>
     <row r="870">
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.0007217149921017185</v>
+        <v>0.0007217149921019406</v>
       </c>
     </row>
     <row r="871">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>-0.01185892682263123</v>
+        <v>-0.01185892682263145</v>
       </c>
     </row>
     <row r="872">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>-0.05287430603675802</v>
+        <v>-0.0528743060367578</v>
       </c>
     </row>
     <row r="873">
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>-0.02676464883343033</v>
+        <v>-0.02676464883343044</v>
       </c>
     </row>
     <row r="875">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.008846186374128706</v>
+        <v>0.008846186374128484</v>
       </c>
     </row>
     <row r="876">
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>-0.002546475484619726</v>
+        <v>-0.002546475484619504</v>
       </c>
     </row>
     <row r="880">
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>-0.02687770664946465</v>
+        <v>-0.02687770664946476</v>
       </c>
     </row>
     <row r="881">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.002871707314528349</v>
+        <v>0.002871707314528127</v>
       </c>
     </row>
     <row r="882">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>-0.003616435026220222</v>
+        <v>-0.003616435026220333</v>
       </c>
     </row>
     <row r="885">
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.01346177487852418</v>
+        <v>0.01346177487852396</v>
       </c>
     </row>
     <row r="886">
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.0131129859977368</v>
+        <v>0.01311298599773747</v>
       </c>
     </row>
     <row r="887">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>-0.01574620650592595</v>
+        <v>-0.01574620650592606</v>
       </c>
     </row>
     <row r="888">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>-0.03077984789993371</v>
+        <v>-0.03077984789993415</v>
       </c>
     </row>
     <row r="890">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.01587468231271183</v>
+        <v>0.01587468231271227</v>
       </c>
     </row>
     <row r="891">
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.008161032176681848</v>
+        <v>0.00816103217668207</v>
       </c>
     </row>
     <row r="892">
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>-0.007617557027504995</v>
+        <v>-0.007617557027505106</v>
       </c>
     </row>
     <row r="895">
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>-0.01355477226386692</v>
+        <v>-0.01355477226386703</v>
       </c>
     </row>
     <row r="896">
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>-0.005248251859024111</v>
+        <v>-0.005248251859023778</v>
       </c>
     </row>
     <row r="897">
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>-0.009382867163117314</v>
+        <v>-0.009382867163117647</v>
       </c>
     </row>
     <row r="899">
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.01452034972315719</v>
+        <v>0.01452034972315697</v>
       </c>
     </row>
     <row r="900">
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>-0.04536117353824243</v>
+        <v>-0.04536117353824221</v>
       </c>
     </row>
     <row r="903">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.01195971654985395</v>
+        <v>0.01195971654985373</v>
       </c>
     </row>
     <row r="905">
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.01627273518425754</v>
+        <v>0.01627273518425731</v>
       </c>
     </row>
     <row r="907">
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>-0.008609047926023128</v>
+        <v>-0.008609047926023017</v>
       </c>
     </row>
     <row r="908">
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>-0.001651562906852644</v>
+        <v>-0.001651562906852866</v>
       </c>
     </row>
     <row r="909">
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>-0.009087010801110296</v>
+        <v>-0.009087010801110074</v>
       </c>
     </row>
     <row r="910">
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.002507451783112513</v>
+        <v>0.002507451783112291</v>
       </c>
     </row>
     <row r="912">
@@ -9530,7 +9530,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>-0.003512367374535974</v>
+        <v>-0.003512367374535863</v>
       </c>
     </row>
     <row r="913">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.02120922245701706</v>
+        <v>0.02120922245701684</v>
       </c>
     </row>
     <row r="914">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.01283923671550879</v>
+        <v>0.01283923671550902</v>
       </c>
     </row>
     <row r="915">
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>-0.007180387489376883</v>
+        <v>-0.007180387489377216</v>
       </c>
     </row>
     <row r="916">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.01348506982872011</v>
+        <v>0.01348506982872033</v>
       </c>
     </row>
     <row r="917">
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>-0.02951621523098713</v>
+        <v>-0.02951621523098702</v>
       </c>
     </row>
     <row r="918">
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.0009150719888137981</v>
+        <v>0.0009150719888135761</v>
       </c>
     </row>
     <row r="919">
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>-0.01614598427896963</v>
+        <v>-0.01614598427896952</v>
       </c>
     </row>
     <row r="920">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>-0.01584099504267888</v>
+        <v>-0.015840995042679</v>
       </c>
     </row>
     <row r="922">
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>-0.01884155466777648</v>
+        <v>-0.01884155466777659</v>
       </c>
     </row>
     <row r="924">
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.01509911676827391</v>
+        <v>0.01509911676827369</v>
       </c>
     </row>
     <row r="926">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>-0.003787806878785327</v>
+        <v>-0.003787806878784772</v>
       </c>
     </row>
     <row r="927">
@@ -9680,7 +9680,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>-0.03074337549969508</v>
+        <v>-0.03074337549969519</v>
       </c>
     </row>
     <row r="928">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>-0.01639302215556271</v>
+        <v>-0.0163930221555626</v>
       </c>
     </row>
     <row r="929">
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>-0.05727072922346144</v>
+        <v>-0.05727072922346133</v>
       </c>
     </row>
     <row r="930">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.02785003639245942</v>
+        <v>0.02785003639245898</v>
       </c>
     </row>
     <row r="932">
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>-0.01609057501152855</v>
+        <v>-0.01609057501152833</v>
       </c>
     </row>
     <row r="933">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>-0.009770089210499155</v>
+        <v>-0.009770089210498822</v>
       </c>
     </row>
     <row r="936">
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.02439593822905972</v>
+        <v>0.0243959382290595</v>
       </c>
     </row>
     <row r="937">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>-0.009250610430398987</v>
+        <v>-0.009250610430399098</v>
       </c>
     </row>
     <row r="939">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.0004441928617495705</v>
+        <v>0.0004441928617497926</v>
       </c>
     </row>
     <row r="941">
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.02074903899339442</v>
+        <v>0.0207490389933942</v>
       </c>
     </row>
     <row r="947">
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>-0.05224396074816096</v>
+        <v>-0.05224396074816062</v>
       </c>
     </row>
     <row r="948">
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.02348694933766238</v>
+        <v>0.02348694933766216</v>
       </c>
     </row>
     <row r="949">
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>-0.002483967960698386</v>
+        <v>-0.002483967960697941</v>
       </c>
     </row>
     <row r="950">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.008985201378606034</v>
+        <v>0.00898520137860559</v>
       </c>
     </row>
     <row r="951">
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.01920549403114946</v>
+        <v>0.01920549403114968</v>
       </c>
     </row>
     <row r="952">
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.002612835135950009</v>
+        <v>0.002612835135950231</v>
       </c>
     </row>
     <row r="953">
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>-0.006450835012679956</v>
+        <v>-0.006450835012679734</v>
       </c>
     </row>
     <row r="957">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>-0.005468739357935681</v>
+        <v>-0.005468739357936125</v>
       </c>
     </row>
     <row r="958">
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>-0.01713457939268526</v>
+        <v>-0.01713457939268492</v>
       </c>
     </row>
     <row r="959">
@@ -10000,7 +10000,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.01970592743179234</v>
+        <v>0.01970592743179211</v>
       </c>
     </row>
     <row r="960">
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.003773654668152604</v>
+        <v>0.003773654668152826</v>
       </c>
     </row>
     <row r="961">
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>-0.002510323087110744</v>
+        <v>-0.002510323087110855</v>
       </c>
     </row>
     <row r="963">
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.007131147268863103</v>
+        <v>0.007131147268862881</v>
       </c>
     </row>
     <row r="965">
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.007449045502256668</v>
+        <v>0.00744904550225689</v>
       </c>
     </row>
     <row r="970">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.01399454214757956</v>
+        <v>0.01399454214757934</v>
       </c>
     </row>
     <row r="972">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>-0.02183379252242734</v>
+        <v>-0.02183379252242723</v>
       </c>
     </row>
     <row r="973">
@@ -10140,7 +10140,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>-0.002232229131369112</v>
+        <v>-0.002232229131369001</v>
       </c>
     </row>
     <row r="974">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>-0.0006225305559330874</v>
+        <v>-0.0006225305559334204</v>
       </c>
     </row>
     <row r="975">
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>-0.002596754297616855</v>
+        <v>-0.002596754297616632</v>
       </c>
     </row>
     <row r="977">
@@ -10180,7 +10180,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>-0.01479631283169502</v>
+        <v>-0.01479631283169491</v>
       </c>
     </row>
     <row r="978">
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>-0.003336029333235513</v>
+        <v>-0.003336029333235402</v>
       </c>
     </row>
     <row r="980">
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>-0.01013931298710935</v>
+        <v>-0.01013931298710946</v>
       </c>
     </row>
     <row r="981">
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.01199963064489951</v>
+        <v>0.01199963064489928</v>
       </c>
     </row>
     <row r="984">
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>-0.003654271716960089</v>
+        <v>-0.003654271716959978</v>
       </c>
     </row>
     <row r="985">
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>-0.01160389346474755</v>
+        <v>-0.01160389346474766</v>
       </c>
     </row>
     <row r="989">
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.005893542318945011</v>
+        <v>0.005893542318945233</v>
       </c>
     </row>
     <row r="992">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>-0.002272837751593149</v>
+        <v>-0.00227283775159326</v>
       </c>
     </row>
     <row r="995">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.0107676618700614</v>
+        <v>0.01076766187006162</v>
       </c>
     </row>
     <row r="999">
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.008764189917862764</v>
+        <v>0.008764189917862542</v>
       </c>
     </row>
     <row r="1000">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.01616773732429855</v>
+        <v>0.01616773732429877</v>
       </c>
     </row>
     <row r="1001">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.01649921637084972</v>
+        <v>0.0164992163708495</v>
       </c>
     </row>
     <row r="1002">
@@ -10440,7 +10440,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.009727578945346371</v>
+        <v>0.009727578945346593</v>
       </c>
     </row>
     <row r="1004">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>-0.008720930572255092</v>
+        <v>-0.008720930572255314</v>
       </c>
     </row>
     <row r="1005">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.008049484721175171</v>
+        <v>0.008049484721174949</v>
       </c>
     </row>
     <row r="1011">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.01592332223870074</v>
+        <v>0.01592332223870097</v>
       </c>
     </row>
     <row r="1012">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>-0.003180039434085846</v>
+        <v>-0.003180039434085624</v>
       </c>
     </row>
     <row r="1014">
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.007635541687579073</v>
+        <v>0.007635541687578851</v>
       </c>
     </row>
     <row r="1015">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.009074221255804371</v>
+        <v>0.009074221255804593</v>
       </c>
     </row>
     <row r="1016">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>-0.01042932187807855</v>
+        <v>-0.01042932187807877</v>
       </c>
     </row>
     <row r="1017">
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>-0.03477636690597119</v>
+        <v>-0.03477636690597097</v>
       </c>
     </row>
     <row r="1018">
@@ -10590,7 +10590,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.007016031264256428</v>
+        <v>0.007016031264255984</v>
       </c>
     </row>
     <row r="1019">
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.007113886388666835</v>
+        <v>0.007113886388667057</v>
       </c>
     </row>
     <row r="1021">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>-0.0003729258722201534</v>
+        <v>-0.0003729258722199313</v>
       </c>
     </row>
     <row r="1023">
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.01007534358401552</v>
+        <v>0.01007534358401529</v>
       </c>
     </row>
     <row r="1026">
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>-0.01305108122702947</v>
+        <v>-0.01305108122702969</v>
       </c>
     </row>
     <row r="1027">
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>-0.02403817491825444</v>
+        <v>-0.02403817491825422</v>
       </c>
     </row>
     <row r="1028">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>-0.01829093865658427</v>
+        <v>-0.01829093865658438</v>
       </c>
     </row>
     <row r="1029">
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>-0.01550002662593453</v>
+        <v>-0.01550002662593442</v>
       </c>
     </row>
     <row r="1030">
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.008313027443095589</v>
+        <v>0.008313027443095811</v>
       </c>
     </row>
     <row r="1032">
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>-0.002777189986378881</v>
+        <v>-0.00277718998637877</v>
       </c>
     </row>
     <row r="1033">
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>-0.01658249273285239</v>
+        <v>-0.01658249273285262</v>
       </c>
     </row>
     <row r="1034">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>-0.01044878661851334</v>
+        <v>-0.01044878661851345</v>
       </c>
     </row>
     <row r="1035">
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>-0.01842160400038051</v>
+        <v>-0.01842160400038018</v>
       </c>
     </row>
     <row r="1037">
@@ -10790,7 +10790,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>-0.01403268254800005</v>
+        <v>-0.01403268254800016</v>
       </c>
     </row>
     <row r="1039">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>-0.02306447929752553</v>
+        <v>-0.02306447929752531</v>
       </c>
     </row>
     <row r="1040">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.01192250194109934</v>
+        <v>0.01192250194109912</v>
       </c>
     </row>
     <row r="1041">
@@ -10830,7 +10830,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.02336373822881987</v>
+        <v>0.02336373822882032</v>
       </c>
     </row>
     <row r="1043">
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.0193826718183896</v>
+        <v>0.01938267181838915</v>
       </c>
     </row>
     <row r="1044">
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>-0.002170950630673074</v>
+        <v>-0.00217095063067263</v>
       </c>
     </row>
     <row r="1048">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>-0.01334137027498483</v>
+        <v>-0.01334137027498505</v>
       </c>
     </row>
     <row r="1051">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.02745808023947616</v>
+        <v>0.02745808023947593</v>
       </c>
     </row>
     <row r="1052">
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>-0.004396291537364094</v>
+        <v>-0.004396291537363983</v>
       </c>
     </row>
     <row r="1053">
@@ -10940,7 +10940,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>-0.05474391666424894</v>
+        <v>-0.05474391666424905</v>
       </c>
     </row>
     <row r="1054">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.01087680791005829</v>
+        <v>0.01087680791005852</v>
       </c>
     </row>
     <row r="1055">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.004001549284388117</v>
+        <v>0.004001549284387673</v>
       </c>
     </row>
     <row r="1060">
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.006624528702390053</v>
+        <v>0.006624528702390275</v>
       </c>
     </row>
     <row r="1061">
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>-0.00590198667683639</v>
+        <v>-0.005901986676836168</v>
       </c>
     </row>
     <row r="1062">
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.0152772056521282</v>
+        <v>0.01527720565212798</v>
       </c>
     </row>
     <row r="1066">
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>-0.007985798919504017</v>
+        <v>-0.007985798919503795</v>
       </c>
     </row>
     <row r="1067">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.00508312081697726</v>
+        <v>0.005083120816977038</v>
       </c>
     </row>
     <row r="1068">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>-0.0194255400667539</v>
+        <v>-0.01942554006675412</v>
       </c>
     </row>
     <row r="1071">
@@ -11120,7 +11120,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>-0.007317974766921198</v>
+        <v>-0.007317974766920976</v>
       </c>
     </row>
     <row r="1072">
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>-0.008653895420259849</v>
+        <v>-0.008653895420259738</v>
       </c>
     </row>
     <row r="1074">
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>-0.001970124550798258</v>
+        <v>-0.001970124550798369</v>
       </c>
     </row>
     <row r="1075">
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.01686443716937025</v>
+        <v>0.01686443716937003</v>
       </c>
     </row>
     <row r="1076">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.003170386643203793</v>
+        <v>0.003170386643204015</v>
       </c>
     </row>
     <row r="1077">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.01391704591329268</v>
+        <v>0.0139170459132929</v>
       </c>
     </row>
     <row r="1079">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>-0.002063727315754549</v>
+        <v>-0.002063727315754993</v>
       </c>
     </row>
     <row r="1080">
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>-0.003533328305863948</v>
+        <v>-0.003533328305863725</v>
       </c>
     </row>
     <row r="1083">
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.002529683784929571</v>
+        <v>0.002529683784930015</v>
       </c>
     </row>
     <row r="1085">
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>-0.01072368807296731</v>
+        <v>-0.01072368807296775</v>
       </c>
     </row>
     <row r="1086">
@@ -11270,7 +11270,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.002346017293623159</v>
+        <v>0.002346017293622937</v>
       </c>
     </row>
     <row r="1087">
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>-0.001032965158952015</v>
+        <v>-0.001032965158951571</v>
       </c>
     </row>
     <row r="1088">
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>-0.022327341499076</v>
+        <v>-0.02232734149907634</v>
       </c>
     </row>
     <row r="1090">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>-0.01946199108892699</v>
+        <v>-0.01946199108892688</v>
       </c>
     </row>
     <row r="1093">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>-0.01251152387576304</v>
+        <v>-0.01251152387576293</v>
       </c>
     </row>
     <row r="1097">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>-0.006574370112642169</v>
+        <v>-0.006574370112641947</v>
       </c>
     </row>
     <row r="1098">
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.006809366944742878</v>
+        <v>0.006809366944742434</v>
       </c>
     </row>
     <row r="1099">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.001590331943461587</v>
+        <v>0.001590331943461809</v>
       </c>
     </row>
     <row r="1104">
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.002661212489138309</v>
+        <v>0.002661212489138087</v>
       </c>
     </row>
     <row r="1105">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>-0.00996827470713646</v>
+        <v>-0.009968274707136238</v>
       </c>
     </row>
     <row r="1110">
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>-0.001064815785798201</v>
+        <v>-0.001064815785798423</v>
       </c>
     </row>
     <row r="1111">
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.02479351554262998</v>
+        <v>0.02479351554263021</v>
       </c>
     </row>
     <row r="1114">
@@ -11550,7 +11550,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>0.01054565858478607</v>
+        <v>0.01054565858478562</v>
       </c>
     </row>
     <row r="1115">
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0.0329951979882297</v>
+        <v>0.03299519798822992</v>
       </c>
     </row>
     <row r="1116">
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.00446341646565096</v>
+        <v>0.004463416465650738</v>
       </c>
     </row>
     <row r="1118">
@@ -11590,7 +11590,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>-0.004606097024200895</v>
+        <v>-0.004606097024200673</v>
       </c>
     </row>
     <row r="1119">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>-0.01072999925606888</v>
+        <v>-0.01072999925606843</v>
       </c>
     </row>
     <row r="1121">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>0.01030514516700576</v>
+        <v>0.01030514516700509</v>
       </c>
     </row>
     <row r="1122">
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.01329571743440883</v>
+        <v>0.01329571743440905</v>
       </c>
     </row>
     <row r="1124">
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>0.001618646590117123</v>
+        <v>0.001618646590116901</v>
       </c>
     </row>
     <row r="1126">
@@ -11670,7 +11670,7 @@
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>-0.033708009220493</v>
+        <v>-0.03370800922049277</v>
       </c>
     </row>
     <row r="1127">
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>-0.002769417196588519</v>
+        <v>-0.002769417196588075</v>
       </c>
     </row>
     <row r="1128">
@@ -11690,7 +11690,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>0.01638750797245536</v>
+        <v>0.01638750797245492</v>
       </c>
     </row>
     <row r="1129">
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>0.007933848024928469</v>
+        <v>0.007933848024928247</v>
       </c>
     </row>
     <row r="1131">
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="B1131" t="n">
-        <v>-0.002907747217093415</v>
+        <v>-0.002907747217093193</v>
       </c>
     </row>
     <row r="1132">
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>-0.003251827210925318</v>
+        <v>-0.003251827210925207</v>
       </c>
     </row>
     <row r="1133">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>-0.006515008108428977</v>
+        <v>-0.006515008108429199</v>
       </c>
     </row>
     <row r="1134">
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>-0.01103167676647554</v>
+        <v>-0.01103167676647576</v>
       </c>
     </row>
     <row r="1138">
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>0.003635445179374752</v>
+        <v>0.003635445179375196</v>
       </c>
     </row>
     <row r="1139">
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>-0.02215157709837268</v>
+        <v>-0.0221515770983729</v>
       </c>
     </row>
     <row r="1140">
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>0.01564493698569702</v>
+        <v>0.0156449369856968</v>
       </c>
     </row>
     <row r="1141">
@@ -11820,7 +11820,7 @@
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>0.01498535994606609</v>
+        <v>0.01498535994606631</v>
       </c>
     </row>
     <row r="1142">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>-0.01908330480741638</v>
+        <v>-0.01908330480741649</v>
       </c>
     </row>
     <row r="1145">
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>0.009915245617338142</v>
+        <v>0.009915245617338364</v>
       </c>
     </row>
     <row r="1146">
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>-0.006382761616758437</v>
+        <v>-0.006382761616758659</v>
       </c>
     </row>
     <row r="1152">
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>-0.003941316579944676</v>
+        <v>-0.003941316579944454</v>
       </c>
     </row>
     <row r="1153">
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>0.01130903820118001</v>
+        <v>0.01130903820117979</v>
       </c>
     </row>
     <row r="1154">
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>-0.02426953109935848</v>
+        <v>-0.02426953109935825</v>
       </c>
     </row>
     <row r="1155">
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>-0.007084652982432438</v>
+        <v>-0.007084652982432216</v>
       </c>
     </row>
     <row r="1156">
@@ -11970,7 +11970,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>-0.01135993395996127</v>
+        <v>-0.01135993395996138</v>
       </c>
     </row>
     <row r="1157">
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>0.009424615194588482</v>
+        <v>0.009424615194588037</v>
       </c>
     </row>
     <row r="1159">
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>-0.0141085572459575</v>
+        <v>-0.01410855724595728</v>
       </c>
     </row>
     <row r="1160">
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>-0.009124770218550626</v>
+        <v>-0.009124770218550848</v>
       </c>
     </row>
     <row r="1166">
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>0.00345957678844222</v>
+        <v>0.003459576788442442</v>
       </c>
     </row>
     <row r="1167">
@@ -12080,7 +12080,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>-0.002807021897575535</v>
+        <v>-0.002807021897575757</v>
       </c>
     </row>
     <row r="1168">
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>0.0002924664760584061</v>
+        <v>0.0002924664760586282</v>
       </c>
     </row>
     <row r="1169">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>0.006382802943589283</v>
+        <v>0.006382802943588839</v>
       </c>
     </row>
     <row r="1170">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>-0.008930247147526438</v>
+        <v>-0.008930247147525994</v>
       </c>
     </row>
     <row r="1171">
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>-0.03773790998610305</v>
+        <v>-0.03773790998610327</v>
       </c>
     </row>
     <row r="1172">
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>-0.001643853407003015</v>
+        <v>-0.001643853407002793</v>
       </c>
     </row>
     <row r="1173">
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>-0.03382134807378623</v>
+        <v>-0.03382134807378634</v>
       </c>
     </row>
     <row r="1174">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>0.02341936267874312</v>
+        <v>0.02341936267874289</v>
       </c>
     </row>
     <row r="1175">
@@ -12190,7 +12190,7 @@
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>-0.01085513343040734</v>
+        <v>-0.01085513343040712</v>
       </c>
     </row>
     <row r="1179">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>0.008380706573581254</v>
+        <v>0.008380706573581476</v>
       </c>
     </row>
     <row r="1182">
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>0.006205211920169207</v>
+        <v>0.006205211920168985</v>
       </c>
     </row>
     <row r="1183">
@@ -12250,7 +12250,7 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>0.01206354093523987</v>
+        <v>0.01206354093523965</v>
       </c>
     </row>
     <row r="1185">
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="B1188" t="n">
-        <v>-0.006298549730003988</v>
+        <v>-0.006298549730003877</v>
       </c>
     </row>
     <row r="1189">
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>-0.01238610745130564</v>
+        <v>-0.01238610745130575</v>
       </c>
     </row>
     <row r="1191">
@@ -12330,7 +12330,7 @@
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>0.001755096140356516</v>
+        <v>0.001755096140356738</v>
       </c>
     </row>
     <row r="1193">
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>0.005827947192267091</v>
+        <v>0.005827947192266869</v>
       </c>
     </row>
     <row r="1196">
@@ -12390,7 +12390,7 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>-0.0004356370445011137</v>
+        <v>-0.0004356370445006696</v>
       </c>
     </row>
     <row r="1199">
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>0.007900104494809712</v>
+        <v>0.00790010449480949</v>
       </c>
     </row>
     <row r="1200">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>-0.006415003751271797</v>
+        <v>-0.006415003751271575</v>
       </c>
     </row>
     <row r="1203">
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="B1204" t="n">
-        <v>0.00439716524858258</v>
+        <v>0.004397165248582358</v>
       </c>
     </row>
     <row r="1205">
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>0.01019126084526767</v>
+        <v>0.01019126084526789</v>
       </c>
     </row>
     <row r="1207">
@@ -12480,7 +12480,7 @@
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>-0.006475023406139813</v>
+        <v>-0.006475023406140035</v>
       </c>
     </row>
     <row r="1208">
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>-0.00161455550823475</v>
+        <v>-0.001614555508234528</v>
       </c>
     </row>
     <row r="1211">
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>-0.02664514695555986</v>
+        <v>-0.02664514695555997</v>
       </c>
     </row>
     <row r="1212">
@@ -12550,7 +12550,7 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>0.007449648013698962</v>
+        <v>0.00744964801369874</v>
       </c>
     </row>
     <row r="1215">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>0.01562053719362</v>
+        <v>0.01562053719362022</v>
       </c>
     </row>
     <row r="1216">
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>0.0143878760000018</v>
+        <v>0.01438787600000202</v>
       </c>
     </row>
     <row r="1217">
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>-0.001065633927076926</v>
+        <v>-0.001065633927077148</v>
       </c>
     </row>
     <row r="1218">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>0.003388352163433028</v>
+        <v>0.00338835216343325</v>
       </c>
     </row>
     <row r="1219">
@@ -12600,7 +12600,7 @@
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>-0.004887538168462879</v>
+        <v>-0.004887538168463323</v>
       </c>
     </row>
     <row r="1220">
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>-0.000575697811410425</v>
+        <v>-0.0005756978114102029</v>
       </c>
     </row>
     <row r="1221">
@@ -12630,7 +12630,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>-0.0006144229793902944</v>
+        <v>-0.0006144229793905165</v>
       </c>
     </row>
     <row r="1223">
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>0.01288513344958964</v>
+        <v>0.01288513344958986</v>
       </c>
     </row>
     <row r="1224">
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>-0.003713523724295009</v>
+        <v>-0.003713523724295564</v>
       </c>
     </row>
     <row r="1225">
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>0.009037734687209031</v>
+        <v>0.009037734687209475</v>
       </c>
     </row>
     <row r="1226">
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>-0.00293455155194855</v>
+        <v>-0.002934551551948439</v>
       </c>
     </row>
     <row r="1227">
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>-0.01718553996961369</v>
+        <v>-0.01718553996961392</v>
       </c>
     </row>
     <row r="1231">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>-0.0006885681689040579</v>
+        <v>-0.0006885681689038359</v>
       </c>
     </row>
     <row r="1232">
@@ -12750,7 +12750,7 @@
         </is>
       </c>
       <c r="B1234" t="n">
-        <v>-0.002173004850961835</v>
+        <v>-0.002173004850961724</v>
       </c>
     </row>
     <row r="1235">
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>0.003337183657649012</v>
+        <v>0.003337183657649234</v>
       </c>
     </row>
     <row r="1237">
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>0.001035445920764655</v>
+        <v>0.001035445920764433</v>
       </c>
     </row>
     <row r="1238">
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>-0.006060841025893771</v>
+        <v>-0.006060841025893882</v>
       </c>
     </row>
     <row r="1239">
@@ -12800,7 +12800,7 @@
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>-0.007807938764420763</v>
+        <v>-0.007807938764420652</v>
       </c>
     </row>
     <row r="1240">
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>-0.008569863521394994</v>
+        <v>-0.008569863521394772</v>
       </c>
     </row>
     <row r="1241">
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>-0.005913908129421497</v>
+        <v>-0.005913908129421941</v>
       </c>
     </row>
     <row r="1242">
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>0.00245328200531425</v>
+        <v>0.002453282005314472</v>
       </c>
     </row>
     <row r="1244">
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>-0.01486872687637286</v>
+        <v>-0.01486872687637297</v>
       </c>
     </row>
     <row r="1245">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>-0.01201661023136613</v>
+        <v>-0.01201661023136591</v>
       </c>
     </row>
     <row r="1247">
@@ -12880,7 +12880,7 @@
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>0.002431303661456274</v>
+        <v>0.002431303661456052</v>
       </c>
     </row>
     <row r="1248">
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>-0.003687107598763339</v>
+        <v>-0.003687107598762895</v>
       </c>
     </row>
     <row r="1249">
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>-0.008545212717551376</v>
+        <v>-0.008545212717551709</v>
       </c>
     </row>
     <row r="1250">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>-0.009933317999790581</v>
+        <v>-0.009933317999790359</v>
       </c>
     </row>
     <row r="1253">
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>-0.0001153766708044124</v>
+        <v>-0.0001153766708046344</v>
       </c>
     </row>
     <row r="1254">
@@ -13020,7 +13020,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>0.00358462057791531</v>
+        <v>0.003584620577915532</v>
       </c>
     </row>
     <row r="1262">
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>0.012713176620887</v>
+        <v>0.01271317662088678</v>
       </c>
     </row>
     <row r="1263">
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>-0.005007166986337519</v>
+        <v>-0.005007166986337741</v>
       </c>
     </row>
     <row r="1264">
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>-0.006109304102065893</v>
+        <v>-0.006109304102065671</v>
       </c>
     </row>
     <row r="1266">
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>0.00695361167705788</v>
+        <v>0.006953611677057658</v>
       </c>
     </row>
     <row r="1267">
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>0.000880763589701683</v>
+        <v>0.000880763589701905</v>
       </c>
     </row>
     <row r="1268">
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>-0.003682499578741671</v>
+        <v>-0.003682499578742116</v>
       </c>
     </row>
     <row r="1270">
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>-0.004917722651364143</v>
+        <v>-0.004917722651363698</v>
       </c>
     </row>
     <row r="1271">
@@ -13130,7 +13130,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>0.006711500491789701</v>
+        <v>0.006711500491789923</v>
       </c>
     </row>
     <row r="1273">
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>-0.01457274225042626</v>
+        <v>-0.01457274225042637</v>
       </c>
     </row>
     <row r="1274">
@@ -13160,7 +13160,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>-0.01248043176391112</v>
+        <v>-0.01248043176391123</v>
       </c>
     </row>
     <row r="1276">
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>0.01257045717820637</v>
+        <v>0.0125704571782066</v>
       </c>
     </row>
     <row r="1277">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>0.005068501902759426</v>
+        <v>0.005068501902759648</v>
       </c>
     </row>
     <row r="1280">
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>0.00267150415617734</v>
+        <v>0.002671504156177562</v>
       </c>
     </row>
     <row r="1284">
@@ -13250,7 +13250,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>0.008764262056524474</v>
+        <v>0.008764262056524252</v>
       </c>
     </row>
     <row r="1285">
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>-0.002084567408704774</v>
+        <v>-0.002084567408704996</v>
       </c>
     </row>
     <row r="1291">
@@ -13320,7 +13320,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>-0.0246230371256726</v>
+        <v>-0.02462303712567249</v>
       </c>
     </row>
     <row r="1292">
@@ -13350,7 +13350,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>0.004252151122708492</v>
+        <v>0.004252151122708936</v>
       </c>
     </row>
     <row r="1295">
@@ -13380,7 +13380,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>-0.001930876090826872</v>
+        <v>-0.001930876090827316</v>
       </c>
     </row>
     <row r="1298">
@@ -13400,7 +13400,7 @@
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>-0.0130535273557324</v>
+        <v>-0.01305352735573218</v>
       </c>
     </row>
     <row r="1300">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>0.0117085382402089</v>
+        <v>0.01170853824020868</v>
       </c>
     </row>
     <row r="1301">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>0.01107774715226739</v>
+        <v>0.01107774715226784</v>
       </c>
     </row>
     <row r="1302">
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>0.009678606706172044</v>
+        <v>0.0096786067061716</v>
       </c>
     </row>
     <row r="1303">
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>0.004161192416284543</v>
+        <v>0.004161192416284321</v>
       </c>
     </row>
     <row r="1306">
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>0.01030314917591646</v>
+        <v>0.01030314917591668</v>
       </c>
     </row>
     <row r="1307">
@@ -13480,7 +13480,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>-0.0004902150543658612</v>
+        <v>-0.0004902150543663053</v>
       </c>
     </row>
     <row r="1308">
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>0.01335196167070274</v>
+        <v>0.01335196167070296</v>
       </c>
     </row>
     <row r="1309">
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>-0.007480463170962626</v>
+        <v>-0.007480463170962404</v>
       </c>
     </row>
     <row r="1310">
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>0.009222879504946047</v>
+        <v>0.009222879504945825</v>
       </c>
     </row>
     <row r="1312">
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>0.008697832859458021</v>
+        <v>0.008697832859458465</v>
       </c>
     </row>
     <row r="1315">
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>-0.01036181248407497</v>
+        <v>-0.01036181248407531</v>
       </c>
     </row>
     <row r="1316">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>-0.002062717621641119</v>
+        <v>-0.002062717621641341</v>
       </c>
     </row>
     <row r="1317">
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>0.01398800043484094</v>
+        <v>0.01398800043484116</v>
       </c>
     </row>
     <row r="1318">
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>-0.003832206216542233</v>
+        <v>-0.003832206216542455</v>
       </c>
     </row>
     <row r="1321">
@@ -13620,7 +13620,7 @@
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>0.002644916672936315</v>
+        <v>0.002644916672936093</v>
       </c>
     </row>
     <row r="1322">
@@ -13630,7 +13630,7 @@
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>-0.01695050097809658</v>
+        <v>-0.01695050097809603</v>
       </c>
     </row>
     <row r="1323">
@@ -13650,7 +13650,7 @@
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>-0.01073000053663442</v>
+        <v>-0.01073000053663464</v>
       </c>
     </row>
     <row r="1325">
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>-0.02001960001027248</v>
+        <v>-0.0200196000102727</v>
       </c>
     </row>
     <row r="1326">
@@ -13670,7 +13670,7 @@
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>0.01046216428301272</v>
+        <v>0.01046216428301294</v>
       </c>
     </row>
     <row r="1327">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>-0.0003877422885957271</v>
+        <v>-0.0003877422885959492</v>
       </c>
     </row>
     <row r="1329">
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1329" t="n">
-        <v>0.005329024021541118</v>
+        <v>0.00532902402154134</v>
       </c>
     </row>
     <row r="1330">
@@ -13730,7 +13730,7 @@
         </is>
       </c>
       <c r="B1332" t="n">
-        <v>0.009033147768030991</v>
+        <v>0.009033147768030769</v>
       </c>
     </row>
     <row r="1333">
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="B1333" t="n">
-        <v>0.002797468702911088</v>
+        <v>0.002797468702911532</v>
       </c>
     </row>
     <row r="1334">
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="B1334" t="n">
-        <v>0.01024245905611765</v>
+        <v>0.01024245905611743</v>
       </c>
     </row>
     <row r="1335">
@@ -13760,7 +13760,7 @@
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>-0.01277412936422495</v>
+        <v>-0.01277412936422517</v>
       </c>
     </row>
     <row r="1336">
@@ -13770,7 +13770,7 @@
         </is>
       </c>
       <c r="B1336" t="n">
-        <v>-0.01369011862275704</v>
+        <v>-0.01369011862275682</v>
       </c>
     </row>
     <row r="1337">
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="B1337" t="n">
-        <v>0.0005357226755635658</v>
+        <v>0.0005357226755637878</v>
       </c>
     </row>
     <row r="1338">
@@ -13790,7 +13790,7 @@
         </is>
       </c>
       <c r="B1338" t="n">
-        <v>0.00620433161641043</v>
+        <v>0.006204331616410208</v>
       </c>
     </row>
     <row r="1339">
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>0.0196005313790204</v>
+        <v>0.01960053137902018</v>
       </c>
     </row>
     <row r="1342">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>0.006712826606764866</v>
+        <v>0.006712826606765088</v>
       </c>
     </row>
     <row r="1343">
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>-0.004704219566368795</v>
+        <v>-0.004704219566368573</v>
       </c>
     </row>
     <row r="1344">
@@ -13850,7 +13850,7 @@
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>-0.02338575500616902</v>
+        <v>-0.02338575500616924</v>
       </c>
     </row>
     <row r="1345">
@@ -13870,7 +13870,7 @@
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>0.01262582946823354</v>
+        <v>0.01262582946823398</v>
       </c>
     </row>
     <row r="1347">
@@ -13880,7 +13880,7 @@
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>-0.01053153886180491</v>
+        <v>-0.01053153886180525</v>
       </c>
     </row>
     <row r="1348">
@@ -13920,7 +13920,7 @@
         </is>
       </c>
       <c r="B1351" t="n">
-        <v>-0.01071796187695595</v>
+        <v>-0.01071796187695573</v>
       </c>
     </row>
     <row r="1352">
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>-0.02123052998797781</v>
+        <v>-0.02123052998797803</v>
       </c>
     </row>
     <row r="1353">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>-0.01200946454131335</v>
+        <v>-0.01200946454131302</v>
       </c>
     </row>
     <row r="1354">
@@ -13950,7 +13950,7 @@
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>0.002514680374813505</v>
+        <v>0.002514680374813061</v>
       </c>
     </row>
     <row r="1355">
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>-0.05810723940700113</v>
+        <v>-0.05810723940700124</v>
       </c>
     </row>
     <row r="1356">
@@ -13970,7 +13970,7 @@
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>0.001837475323617443</v>
+        <v>0.001837475323617666</v>
       </c>
     </row>
     <row r="1357">
@@ -13990,7 +13990,7 @@
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>0.02344172439259351</v>
+        <v>0.02344172439259329</v>
       </c>
     </row>
     <row r="1359">
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>-0.03967265244533436</v>
+        <v>-0.03967265244533424</v>
       </c>
     </row>
     <row r="1361">
@@ -14020,7 +14020,7 @@
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>-0.03820198234398198</v>
+        <v>-0.03820198234398187</v>
       </c>
     </row>
     <row r="1362">
@@ -14040,7 +14040,7 @@
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>-0.02336054233143792</v>
+        <v>-0.02336054233143781</v>
       </c>
     </row>
     <row r="1364">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>-0.05089259130777313</v>
+        <v>-0.05089259130777324</v>
       </c>
     </row>
     <row r="1365">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="B1369" t="n">
-        <v>0.03001243749520865</v>
+        <v>0.03001243749520821</v>
       </c>
     </row>
     <row r="1370">
@@ -14110,7 +14110,7 @@
         </is>
       </c>
       <c r="B1370" t="n">
-        <v>0.02547611946713713</v>
+        <v>0.02547611946713735</v>
       </c>
     </row>
     <row r="1371">
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>0.01044794269251281</v>
+        <v>0.01044794269251259</v>
       </c>
     </row>
     <row r="1372">
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>0.0284488592880543</v>
+        <v>0.02844885928805452</v>
       </c>
     </row>
     <row r="1373">
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="B1374" t="n">
-        <v>0.01455757294592974</v>
+        <v>0.01455757294592952</v>
       </c>
     </row>
     <row r="1375">
@@ -14160,7 +14160,7 @@
         </is>
       </c>
       <c r="B1375" t="n">
-        <v>0.03005545259423137</v>
+        <v>0.03005545259423159</v>
       </c>
     </row>
     <row r="1376">
@@ -14170,7 +14170,7 @@
         </is>
       </c>
       <c r="B1376" t="n">
-        <v>-0.08128911428467533</v>
+        <v>-0.08128911428467556</v>
       </c>
     </row>
     <row r="1377">
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="B1379" t="n">
-        <v>-0.004016286919828138</v>
+        <v>-0.004016286919828027</v>
       </c>
     </row>
     <row r="1380">
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>0.0226712605361139</v>
+        <v>0.02267126053611412</v>
       </c>
     </row>
     <row r="1386">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>-0.005959807548667206</v>
+        <v>-0.005959807548667428</v>
       </c>
     </row>
     <row r="1389">
@@ -14340,7 +14340,7 @@
         </is>
       </c>
       <c r="B1393" t="n">
-        <v>0.0003643870495533275</v>
+        <v>0.0003643870495531054</v>
       </c>
     </row>
     <row r="1394">
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>-0.03436653109692778</v>
+        <v>-0.03436653109692756</v>
       </c>
     </row>
     <row r="1395">
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>0.006950048820967059</v>
+        <v>0.006950048820966837</v>
       </c>
     </row>
     <row r="1396">
@@ -14370,7 +14370,7 @@
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>-0.02910627207066196</v>
+        <v>-0.02910627207066185</v>
       </c>
     </row>
     <row r="1397">
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>0.02006979762826266</v>
+        <v>0.02006979762826244</v>
       </c>
     </row>
     <row r="1398">
@@ -14390,7 +14390,7 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>0.01571026665756636</v>
+        <v>0.01571026665756659</v>
       </c>
     </row>
     <row r="1399">
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>0.02102553010064301</v>
+        <v>0.02102553010064279</v>
       </c>
     </row>
     <row r="1400">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>0.004029046316505136</v>
+        <v>0.004029046316505358</v>
       </c>
     </row>
     <row r="1402">
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>-0.01537738586530535</v>
+        <v>-0.01537738586530546</v>
       </c>
     </row>
     <row r="1405">
@@ -14460,7 +14460,7 @@
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>-0.008884883680810418</v>
+        <v>-0.008884883680810307</v>
       </c>
     </row>
     <row r="1406">
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>0.006838149120933501</v>
+        <v>0.006838149120933279</v>
       </c>
     </row>
     <row r="1407">
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1407" t="n">
-        <v>-0.05463894666076674</v>
+        <v>-0.05463894666076663</v>
       </c>
     </row>
     <row r="1408">
@@ -14520,7 +14520,7 @@
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>0.005087519156264708</v>
+        <v>0.00508751915626493</v>
       </c>
     </row>
     <row r="1412">
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>0.000672595450638358</v>
+        <v>0.0006725954506379139</v>
       </c>
     </row>
     <row r="1413">
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>0.0197997078002432</v>
+        <v>0.01979970780024343</v>
       </c>
     </row>
     <row r="1416">
@@ -14580,7 +14580,7 @@
         </is>
       </c>
       <c r="B1417" t="n">
-        <v>0.02932534904619</v>
+        <v>0.02932534904618977</v>
       </c>
     </row>
     <row r="1418">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>-8.09152305418781e-05</v>
+        <v>-8.091523054154504e-05</v>
       </c>
     </row>
     <row r="1426">
@@ -14680,7 +14680,7 @@
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>-0.00866127360050295</v>
+        <v>-0.008661273600503061</v>
       </c>
     </row>
     <row r="1428">
@@ -14690,7 +14690,7 @@
         </is>
       </c>
       <c r="B1428" t="n">
-        <v>0.001162942145930268</v>
+        <v>0.00116294214593049</v>
       </c>
     </row>
     <row r="1429">
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>0.01218757053062203</v>
+        <v>0.01218757053062181</v>
       </c>
     </row>
     <row r="1430">
@@ -14720,7 +14720,7 @@
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>-0.002277196998621944</v>
+        <v>-0.002277196998621722</v>
       </c>
     </row>
     <row r="1432">
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>-0.009366340555973185</v>
+        <v>-0.009366340555972741</v>
       </c>
     </row>
     <row r="1434">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>0.01649582674977301</v>
+        <v>0.01649582674977257</v>
       </c>
     </row>
     <row r="1435">
@@ -14780,7 +14780,7 @@
         </is>
       </c>
       <c r="B1437" t="n">
-        <v>-0.002248085805530264</v>
+        <v>-0.002248085805530597</v>
       </c>
     </row>
     <row r="1438">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>-0.005723034689423256</v>
+        <v>-0.005723034689423034</v>
       </c>
     </row>
     <row r="1439">
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="B1439" t="n">
-        <v>-0.01707602033155431</v>
+        <v>-0.01707602033155409</v>
       </c>
     </row>
     <row r="1440">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>-0.03466528251470591</v>
+        <v>-0.03466528251470613</v>
       </c>
     </row>
     <row r="1443">
@@ -14850,7 +14850,7 @@
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>0.007268138207110253</v>
+        <v>0.007268138207110475</v>
       </c>
     </row>
     <row r="1445">
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>0.01534889182051269</v>
+        <v>0.01534889182051247</v>
       </c>
     </row>
     <row r="1446">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>-0.004884440252956535</v>
+        <v>-0.004884440252956423</v>
       </c>
     </row>
     <row r="1451">
@@ -14980,7 +14980,7 @@
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>0.005677710960120486</v>
+        <v>0.005677710960120708</v>
       </c>
     </row>
     <row r="1458">
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="B1458" t="n">
-        <v>0.0098168075449796</v>
+        <v>0.009816807544979156</v>
       </c>
     </row>
     <row r="1459">
@@ -15040,7 +15040,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>-0.02258489017822041</v>
+        <v>-0.02258489017822052</v>
       </c>
     </row>
     <row r="1464">
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>-0.001723574825577612</v>
+        <v>-0.001723574825577501</v>
       </c>
     </row>
     <row r="1466">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>0.0277763084487197</v>
+        <v>0.02777630844871992</v>
       </c>
     </row>
     <row r="1467">
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>-0.007429491809745947</v>
+        <v>-0.007429491809745836</v>
       </c>
     </row>
     <row r="1468">
@@ -15090,7 +15090,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>-0.01394197630946137</v>
+        <v>-0.01394197630946159</v>
       </c>
     </row>
     <row r="1469">
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>-0.0055303753381577</v>
+        <v>-0.005530375338157811</v>
       </c>
     </row>
     <row r="1470">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="B1470" t="n">
-        <v>-0.01127912178068247</v>
+        <v>-0.01127912178068224</v>
       </c>
     </row>
     <row r="1471">
@@ -15120,7 +15120,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>-0.004278625321892271</v>
+        <v>-0.004278625321892382</v>
       </c>
     </row>
     <row r="1472">
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="B1472" t="n">
-        <v>0.004343023713970773</v>
+        <v>0.004343023713970551</v>
       </c>
     </row>
     <row r="1473">
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>0.001856007609605248</v>
+        <v>0.00185600760960547</v>
       </c>
     </row>
     <row r="1474">
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="B1474" t="n">
-        <v>-0.02352477110519002</v>
+        <v>-0.02352477110518991</v>
       </c>
     </row>
     <row r="1475">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>-0.009311136943707776</v>
+        <v>-0.009311136943707665</v>
       </c>
     </row>
     <row r="1476">
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="B1476" t="n">
-        <v>-0.0003122592326068041</v>
+        <v>-0.0003122592326070261</v>
       </c>
     </row>
     <row r="1477">
@@ -15180,7 +15180,7 @@
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>0.01421202494053153</v>
+        <v>0.01421202494053175</v>
       </c>
     </row>
     <row r="1478">
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>-0.001124156165127843</v>
+        <v>-0.001124156165128287</v>
       </c>
     </row>
     <row r="1479">
@@ -15200,7 +15200,7 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>0.008109741127789061</v>
+        <v>0.008109741127789283</v>
       </c>
     </row>
     <row r="1480">
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>-0.004393360701074989</v>
+        <v>-0.0043933607010751</v>
       </c>
     </row>
     <row r="1482">
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="B1484" t="n">
-        <v>0.01797451950727624</v>
+        <v>0.01797451950727647</v>
       </c>
     </row>
     <row r="1485">
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="B1485" t="n">
-        <v>0.004672336928619236</v>
+        <v>0.004672336928619014</v>
       </c>
     </row>
     <row r="1486">
@@ -15280,7 +15280,7 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>-0.008519858712837891</v>
+        <v>-0.008519858712838002</v>
       </c>
     </row>
     <row r="1488">
@@ -15290,7 +15290,7 @@
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>-0.004254613257613671</v>
+        <v>-0.00425461325761356</v>
       </c>
     </row>
     <row r="1489">
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="B1491" t="n">
-        <v>0.002925939052439208</v>
+        <v>0.00292593905243943</v>
       </c>
     </row>
     <row r="1492">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="B1492" t="n">
-        <v>-0.003315758081911646</v>
+        <v>-0.003315758081911535</v>
       </c>
     </row>
     <row r="1493">
@@ -15340,7 +15340,7 @@
         </is>
       </c>
       <c r="B1493" t="n">
-        <v>-0.008937326643320365</v>
+        <v>-0.008937326643320809</v>
       </c>
     </row>
     <row r="1494">
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="B1497" t="n">
-        <v>-0.01024429857578113</v>
+        <v>-0.01024429857578091</v>
       </c>
     </row>
     <row r="1498">
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="B1500" t="n">
-        <v>0.01252248844714376</v>
+        <v>0.01252248844714354</v>
       </c>
     </row>
     <row r="1501">
@@ -15430,7 +15430,7 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>0.006348820123413423</v>
+        <v>0.006348820123413201</v>
       </c>
     </row>
     <row r="1503">
@@ -15440,7 +15440,7 @@
         </is>
       </c>
       <c r="B1503" t="n">
-        <v>-0.006580417166668462</v>
+        <v>-0.00658041716666824</v>
       </c>
     </row>
     <row r="1504">
@@ -15460,7 +15460,7 @@
         </is>
       </c>
       <c r="B1505" t="n">
-        <v>-0.002610585532105025</v>
+        <v>-0.002610585532104803</v>
       </c>
     </row>
     <row r="1506">
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>-0.01755190530467965</v>
+        <v>-0.01755190530467998</v>
       </c>
     </row>
     <row r="1508">
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="B1508" t="n">
-        <v>-0.007266738169930731</v>
+        <v>-0.007266738169930509</v>
       </c>
     </row>
     <row r="1509">
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="B1509" t="n">
-        <v>0.01163839027189217</v>
+        <v>0.0116383902718924</v>
       </c>
     </row>
     <row r="1510">
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="B1510" t="n">
-        <v>-0.006801069580237851</v>
+        <v>-0.006801069580238073</v>
       </c>
     </row>
     <row r="1511">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>-0.007195646791729127</v>
+        <v>-0.007195646791729016</v>
       </c>
     </row>
     <row r="1513">
@@ -15550,7 +15550,7 @@
         </is>
       </c>
       <c r="B1514" t="n">
-        <v>0.02043481955143145</v>
+        <v>0.02043481955143123</v>
       </c>
     </row>
     <row r="1515">
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="B1515" t="n">
-        <v>-0.003879105191259002</v>
+        <v>-0.003879105191258669</v>
       </c>
     </row>
     <row r="1516">
@@ -15570,7 +15570,7 @@
         </is>
       </c>
       <c r="B1516" t="n">
-        <v>-0.0005095385535637265</v>
+        <v>-0.0005095385535640595</v>
       </c>
     </row>
     <row r="1517">
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="B1519" t="n">
-        <v>0.02614078586982904</v>
+        <v>0.02614078586982882</v>
       </c>
     </row>
     <row r="1520">
@@ -15610,7 +15610,7 @@
         </is>
       </c>
       <c r="B1520" t="n">
-        <v>0.03877530021897413</v>
+        <v>0.03877530021897435</v>
       </c>
     </row>
     <row r="1521">
@@ -15620,7 +15620,7 @@
         </is>
       </c>
       <c r="B1521" t="n">
-        <v>0.0855673719011778</v>
+        <v>0.08556737190117758</v>
       </c>
     </row>
     <row r="1522">
@@ -15630,7 +15630,7 @@
         </is>
       </c>
       <c r="B1522" t="n">
-        <v>0.07652640321457183</v>
+        <v>0.07652640321457227</v>
       </c>
     </row>
     <row r="1523">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="B1523" t="n">
-        <v>-0.08964397646252331</v>
+        <v>-0.08964397646252342</v>
       </c>
     </row>
     <row r="1524">
@@ -15660,7 +15660,7 @@
         </is>
       </c>
       <c r="B1525" t="n">
-        <v>-0.03966411915735535</v>
+        <v>-0.03966411915735513</v>
       </c>
     </row>
     <row r="1526">
@@ -15670,7 +15670,7 @@
         </is>
       </c>
       <c r="B1526" t="n">
-        <v>0.03226458937574361</v>
+        <v>0.03226458937574339</v>
       </c>
     </row>
     <row r="1527">
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="B1531" t="n">
-        <v>0.01226433641726277</v>
+        <v>0.01226433641726254</v>
       </c>
     </row>
     <row r="1532">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="B1532" t="n">
-        <v>0.01258620695241897</v>
+        <v>0.01258620695241919</v>
       </c>
     </row>
     <row r="1533">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="B1533" t="n">
-        <v>-0.00517925414235032</v>
+        <v>-0.005179254142350098</v>
       </c>
     </row>
     <row r="1534">
@@ -15750,7 +15750,7 @@
         </is>
       </c>
       <c r="B1534" t="n">
-        <v>0.004491987187897895</v>
+        <v>0.004491987187897672</v>
       </c>
     </row>
     <row r="1535">
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="B1537" t="n">
-        <v>-0.03145785866202588</v>
+        <v>-0.03145785866202611</v>
       </c>
     </row>
     <row r="1538">
@@ -15790,7 +15790,7 @@
         </is>
       </c>
       <c r="B1538" t="n">
-        <v>-0.003231351891966217</v>
+        <v>-0.003231351891965994</v>
       </c>
     </row>
     <row r="1539">
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="B1540" t="n">
-        <v>-0.03217065808157815</v>
+        <v>-0.03217065808157793</v>
       </c>
     </row>
     <row r="1541">
@@ -15820,7 +15820,7 @@
         </is>
       </c>
       <c r="B1541" t="n">
-        <v>0.02364285506837982</v>
+        <v>0.0236428550683796</v>
       </c>
     </row>
     <row r="1542">
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="B1546" t="n">
-        <v>0.01636476017632771</v>
+        <v>0.01636476017632793</v>
       </c>
     </row>
     <row r="1547">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="B1547" t="n">
-        <v>-0.004784771240559094</v>
+        <v>-0.004784771240559538</v>
       </c>
     </row>
     <row r="1548">
@@ -15900,7 +15900,7 @@
         </is>
       </c>
       <c r="B1549" t="n">
-        <v>-0.02224243829935868</v>
+        <v>-0.02224243829935846</v>
       </c>
     </row>
     <row r="1550">
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="B1550" t="n">
-        <v>-0.01582135360634984</v>
+        <v>-0.01582135360634973</v>
       </c>
     </row>
     <row r="1551">
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="B1551" t="n">
-        <v>-0.02390393161544635</v>
+        <v>-0.02390393161544657</v>
       </c>
     </row>
     <row r="1552">
@@ -16000,7 +16000,7 @@
         </is>
       </c>
       <c r="B1559" t="n">
-        <v>0.0109553425081339</v>
+        <v>0.01095534250813412</v>
       </c>
     </row>
     <row r="1560">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="B1560" t="n">
-        <v>0.01714914935500866</v>
+        <v>0.01714914935500844</v>
       </c>
     </row>
     <row r="1561">
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="B1563" t="n">
-        <v>-0.01843262876286134</v>
+        <v>-0.01843262876286167</v>
       </c>
     </row>
     <row r="1564">
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="B1564" t="n">
-        <v>0.01175381290353616</v>
+        <v>0.01175381290353661</v>
       </c>
     </row>
     <row r="1565">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="B1565" t="n">
-        <v>0.001955770962812853</v>
+        <v>0.001955770962812631</v>
       </c>
     </row>
     <row r="1566">
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="B1566" t="n">
-        <v>0.01199357999421524</v>
+        <v>0.01199357999421546</v>
       </c>
     </row>
     <row r="1567">
@@ -16090,7 +16090,7 @@
         </is>
       </c>
       <c r="B1568" t="n">
-        <v>0.00356085162076103</v>
+        <v>0.003560851620760808</v>
       </c>
     </row>
     <row r="1569">
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="B1569" t="n">
-        <v>0.02136597200898338</v>
+        <v>0.0213659720089836</v>
       </c>
     </row>
     <row r="1570">
@@ -16110,7 +16110,7 @@
         </is>
       </c>
       <c r="B1570" t="n">
-        <v>-0.005140303023374981</v>
+        <v>-0.005140303023375203</v>
       </c>
     </row>
     <row r="1571">
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="B1571" t="n">
-        <v>-0.01109197000381512</v>
+        <v>-0.0110919700038149</v>
       </c>
     </row>
     <row r="1572">
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="B1572" t="n">
-        <v>-0.04616953968172699</v>
+        <v>-0.04616953968172732</v>
       </c>
     </row>
     <row r="1573">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="B1573" t="n">
-        <v>0.0005026221032606859</v>
+        <v>0.0005026221032609079</v>
       </c>
     </row>
     <row r="1574">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="B1574" t="n">
-        <v>0.01640181249346018</v>
+        <v>0.01640181249346062</v>
       </c>
     </row>
     <row r="1575">
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="B1575" t="n">
-        <v>0.01173595460700327</v>
+        <v>0.01173595460700305</v>
       </c>
     </row>
     <row r="1576">
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="B1576" t="n">
-        <v>-0.05329917479100432</v>
+        <v>-0.05329917479100454</v>
       </c>
     </row>
     <row r="1577">
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="B1578" t="n">
-        <v>-0.02578153923913196</v>
+        <v>-0.02578153923913185</v>
       </c>
     </row>
     <row r="1579">
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="B1579" t="n">
-        <v>0.02330752130108382</v>
+        <v>0.02330752130108338</v>
       </c>
     </row>
     <row r="1580">
@@ -16210,7 +16210,7 @@
         </is>
       </c>
       <c r="B1580" t="n">
-        <v>0.007624534106426717</v>
+        <v>0.007624534106426939</v>
       </c>
     </row>
     <row r="1581">
@@ -16240,7 +16240,7 @@
         </is>
       </c>
       <c r="B1583" t="n">
-        <v>-0.01187516810674261</v>
+        <v>-0.01187516810674283</v>
       </c>
     </row>
     <row r="1584">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="B1586" t="n">
-        <v>0.02526539708143027</v>
+        <v>0.02526539708143072</v>
       </c>
     </row>
     <row r="1587">
@@ -16280,7 +16280,7 @@
         </is>
       </c>
       <c r="B1587" t="n">
-        <v>-0.000458169259132335</v>
+        <v>-0.000458169259132668</v>
       </c>
     </row>
     <row r="1588">
@@ -16330,7 +16330,7 @@
         </is>
       </c>
       <c r="B1592" t="n">
-        <v>-0.001803053342543715</v>
+        <v>-0.001803053342543492</v>
       </c>
     </row>
     <row r="1593">
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="B1593" t="n">
-        <v>0.001630383464678475</v>
+        <v>0.001630383464678253</v>
       </c>
     </row>
     <row r="1594">
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="B1594" t="n">
-        <v>-0.002199811408059804</v>
+        <v>-0.002199811408060248</v>
       </c>
     </row>
     <row r="1595">
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="B1595" t="n">
-        <v>0.01072935199789904</v>
+        <v>0.01072935199789926</v>
       </c>
     </row>
     <row r="1596">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="B1598" t="n">
-        <v>0.0003278026339781359</v>
+        <v>0.000327802633978358</v>
       </c>
     </row>
     <row r="1599">
@@ -16410,7 +16410,7 @@
         </is>
       </c>
       <c r="B1600" t="n">
-        <v>-0.000291150285729902</v>
+        <v>-0.0002911502857303461</v>
       </c>
     </row>
     <row r="1601">
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="B1602" t="n">
-        <v>0.02320358680974732</v>
+        <v>0.02320358680974755</v>
       </c>
     </row>
     <row r="1603">
@@ -16450,7 +16450,7 @@
         </is>
       </c>
       <c r="B1604" t="n">
-        <v>0.001020386590735445</v>
+        <v>0.001020386590735667</v>
       </c>
     </row>
     <row r="1605">
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="B1606" t="n">
-        <v>0.00402780981656492</v>
+        <v>0.004027809816565142</v>
       </c>
     </row>
     <row r="1607">
@@ -16480,7 +16480,7 @@
         </is>
       </c>
       <c r="B1607" t="n">
-        <v>-0.01827278527387843</v>
+        <v>-0.01827278527387854</v>
       </c>
     </row>
     <row r="1608">
@@ -16500,7 +16500,7 @@
         </is>
       </c>
       <c r="B1609" t="n">
-        <v>0.01573593032789233</v>
+        <v>0.01573593032789211</v>
       </c>
     </row>
     <row r="1610">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="B1610" t="n">
-        <v>-0.02453578728277173</v>
+        <v>-0.02453578728277139</v>
       </c>
     </row>
     <row r="1611">
@@ -16520,7 +16520,7 @@
         </is>
       </c>
       <c r="B1611" t="n">
-        <v>0.01997217894310865</v>
+        <v>0.01997217894310821</v>
       </c>
     </row>
     <row r="1612">
@@ -16540,7 +16540,7 @@
         </is>
       </c>
       <c r="B1613" t="n">
-        <v>-7.545678536369227e-05</v>
+        <v>-7.545678536347022e-05</v>
       </c>
     </row>
     <row r="1614">
@@ -16570,7 +16570,7 @@
         </is>
       </c>
       <c r="B1616" t="n">
-        <v>0.01755498101229547</v>
+        <v>0.01755498101229525</v>
       </c>
     </row>
     <row r="1617">
@@ -16580,7 +16580,7 @@
         </is>
       </c>
       <c r="B1617" t="n">
-        <v>-0.003127437136847266</v>
+        <v>-0.003127437136847044</v>
       </c>
     </row>
     <row r="1618">
@@ -16590,7 +16590,7 @@
         </is>
       </c>
       <c r="B1618" t="n">
-        <v>-0.02451147428755573</v>
+        <v>-0.02451147428755551</v>
       </c>
     </row>
     <row r="1619">
@@ -16600,7 +16600,7 @@
         </is>
       </c>
       <c r="B1619" t="n">
-        <v>0.009247873390833439</v>
+        <v>0.009247873390833217</v>
       </c>
     </row>
     <row r="1620">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="B1621" t="n">
-        <v>0.001827684389998474</v>
+        <v>0.001827684389998696</v>
       </c>
     </row>
     <row r="1622">
@@ -16630,7 +16630,7 @@
         </is>
       </c>
       <c r="B1622" t="n">
-        <v>0.0189970004742015</v>
+        <v>0.01899700047420105</v>
       </c>
     </row>
     <row r="1623">
@@ -16640,7 +16640,7 @@
         </is>
       </c>
       <c r="B1623" t="n">
-        <v>0.01614577641028836</v>
+        <v>0.01614577641028792</v>
       </c>
     </row>
     <row r="1624">
@@ -16650,7 +16650,7 @@
         </is>
       </c>
       <c r="B1624" t="n">
-        <v>0.004611919958874777</v>
+        <v>0.004611919958875221</v>
       </c>
     </row>
     <row r="1625">
@@ -16670,7 +16670,7 @@
         </is>
       </c>
       <c r="B1626" t="n">
-        <v>0.0028298566866507</v>
+        <v>0.002829856686650922</v>
       </c>
     </row>
     <row r="1627">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="B1631" t="n">
-        <v>0.007192622223135547</v>
+        <v>0.007192622223135769</v>
       </c>
     </row>
     <row r="1632">
@@ -16730,7 +16730,7 @@
         </is>
       </c>
       <c r="B1632" t="n">
-        <v>0.00735092744920407</v>
+        <v>0.007350927449203626</v>
       </c>
     </row>
     <row r="1633">
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="B1633" t="n">
-        <v>-0.02223425921602684</v>
+        <v>-0.02223425921602651</v>
       </c>
     </row>
     <row r="1634">
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="B1634" t="n">
-        <v>-0.01955228630033723</v>
+        <v>-0.01955228630033745</v>
       </c>
     </row>
     <row r="1635">
@@ -16760,7 +16760,7 @@
         </is>
       </c>
       <c r="B1635" t="n">
-        <v>0.009328833611419007</v>
+        <v>0.009328833611418785</v>
       </c>
     </row>
     <row r="1636">
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="B1636" t="n">
-        <v>0.01450678809730421</v>
+        <v>0.01450678809730443</v>
       </c>
     </row>
     <row r="1637">
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="B1639" t="n">
-        <v>-0.001876385008765857</v>
+        <v>-0.001876385008766079</v>
       </c>
     </row>
     <row r="1640">
@@ -16810,7 +16810,7 @@
         </is>
       </c>
       <c r="B1640" t="n">
-        <v>0.0153289339268361</v>
+        <v>0.01532893392683632</v>
       </c>
     </row>
     <row r="1641">
@@ -16830,7 +16830,7 @@
         </is>
       </c>
       <c r="B1642" t="n">
-        <v>-0.002826299774555618</v>
+        <v>-0.002826299774555507</v>
       </c>
     </row>
     <row r="1643">
@@ -16850,7 +16850,7 @@
         </is>
       </c>
       <c r="B1644" t="n">
-        <v>-0.01189338138546858</v>
+        <v>-0.0118933813854688</v>
       </c>
     </row>
     <row r="1645">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="B1645" t="n">
-        <v>0.01822489260835392</v>
+        <v>0.01822489260835414</v>
       </c>
     </row>
     <row r="1646">
@@ -16880,7 +16880,7 @@
         </is>
       </c>
       <c r="B1647" t="n">
-        <v>-0.0002633637638476127</v>
+        <v>-0.0002633637638473907</v>
       </c>
     </row>
     <row r="1648">
@@ -16890,7 +16890,7 @@
         </is>
       </c>
       <c r="B1648" t="n">
-        <v>0.0166686599145951</v>
+        <v>0.01666865991459465</v>
       </c>
     </row>
     <row r="1649">
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="B1649" t="n">
-        <v>0.008934959518384966</v>
+        <v>0.008934959518385188</v>
       </c>
     </row>
     <row r="1650">
@@ -16920,7 +16920,7 @@
         </is>
       </c>
       <c r="B1651" t="n">
-        <v>0.02032731575984315</v>
+        <v>0.02032731575984337</v>
       </c>
     </row>
     <row r="1652">
@@ -16930,7 +16930,7 @@
         </is>
       </c>
       <c r="B1652" t="n">
-        <v>0.004929547463428108</v>
+        <v>0.004929547463427886</v>
       </c>
     </row>
     <row r="1653">
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="B1654" t="n">
-        <v>0.01169586862946592</v>
+        <v>0.01169586862946614</v>
       </c>
     </row>
     <row r="1655">
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="B1655" t="n">
-        <v>0.01282874983113125</v>
+        <v>0.01282874983113103</v>
       </c>
     </row>
     <row r="1656">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="B1656" t="n">
-        <v>0.007823117349631259</v>
+        <v>0.007823117349631037</v>
       </c>
     </row>
     <row r="1657">
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="B1658" t="n">
-        <v>-0.02606678226746606</v>
+        <v>-0.02606678226746573</v>
       </c>
     </row>
     <row r="1659">
@@ -17000,7 +17000,7 @@
         </is>
       </c>
       <c r="B1659" t="n">
-        <v>-0.002959152450057179</v>
+        <v>-0.002959152450057401</v>
       </c>
     </row>
     <row r="1660">
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="B1662" t="n">
-        <v>0.009147278182450203</v>
+        <v>0.009147278182450647</v>
       </c>
     </row>
     <row r="1663">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="B1664" t="n">
-        <v>-0.005451699081732264</v>
+        <v>-0.005451699081732042</v>
       </c>
     </row>
     <row r="1665">
@@ -17060,7 +17060,7 @@
         </is>
       </c>
       <c r="B1665" t="n">
-        <v>0.003259510696829837</v>
+        <v>0.003259510696829393</v>
       </c>
     </row>
     <row r="1666">
@@ -17090,7 +17090,7 @@
         </is>
       </c>
       <c r="B1668" t="n">
-        <v>0.006593993621998973</v>
+        <v>0.006593993621999195</v>
       </c>
     </row>
     <row r="1669">
@@ -17110,7 +17110,7 @@
         </is>
       </c>
       <c r="B1670" t="n">
-        <v>0.01105311765482964</v>
+        <v>0.01105311765482941</v>
       </c>
     </row>
     <row r="1671">
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="B1671" t="n">
-        <v>0.000827762864600734</v>
+        <v>0.0008277628646011781</v>
       </c>
     </row>
     <row r="1672">
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="B1672" t="n">
-        <v>-0.007490592504773463</v>
+        <v>-0.007490592504773796</v>
       </c>
     </row>
     <row r="1673">
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="B1673" t="n">
-        <v>-0.01986364809302532</v>
+        <v>-0.01986364809302499</v>
       </c>
     </row>
     <row r="1674">
@@ -17160,7 +17160,7 @@
         </is>
       </c>
       <c r="B1675" t="n">
-        <v>0.01296730249478029</v>
+        <v>0.01296730249478006</v>
       </c>
     </row>
     <row r="1676">
@@ -17180,7 +17180,7 @@
         </is>
       </c>
       <c r="B1677" t="n">
-        <v>-0.00282551724458413</v>
+        <v>-0.002825517244583797</v>
       </c>
     </row>
     <row r="1678">
@@ -17190,7 +17190,7 @@
         </is>
       </c>
       <c r="B1678" t="n">
-        <v>0.01165671494580667</v>
+        <v>0.01165671494580622</v>
       </c>
     </row>
     <row r="1679">
@@ -17200,7 +17200,7 @@
         </is>
       </c>
       <c r="B1679" t="n">
-        <v>-0.01057324515605651</v>
+        <v>-0.01057324515605662</v>
       </c>
     </row>
     <row r="1680">
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="B1680" t="n">
-        <v>0.01812193069789436</v>
+        <v>0.01812193069789458</v>
       </c>
     </row>
     <row r="1681">
@@ -17220,7 +17220,7 @@
         </is>
       </c>
       <c r="B1681" t="n">
-        <v>0.01233275157908897</v>
+        <v>0.01233275157908875</v>
       </c>
     </row>
     <row r="1682">
@@ -17240,7 +17240,7 @@
         </is>
       </c>
       <c r="B1683" t="n">
-        <v>0.001385189267291143</v>
+        <v>0.001385189267291365</v>
       </c>
     </row>
     <row r="1684">
@@ -17250,7 +17250,7 @@
         </is>
       </c>
       <c r="B1684" t="n">
-        <v>0.004364449784621804</v>
+        <v>0.004364449784621582</v>
       </c>
     </row>
     <row r="1685">
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="B1685" t="n">
-        <v>-0.009159046363722334</v>
+        <v>-0.009159046363722112</v>
       </c>
     </row>
     <row r="1686">
@@ -17290,7 +17290,7 @@
         </is>
       </c>
       <c r="B1688" t="n">
-        <v>-0.01364940258210467</v>
+        <v>-0.01364940258210445</v>
       </c>
     </row>
     <row r="1689">
@@ -17300,7 +17300,7 @@
         </is>
       </c>
       <c r="B1689" t="n">
-        <v>0.007500410953379166</v>
+        <v>0.007500410953378722</v>
       </c>
     </row>
     <row r="1690">
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="B1690" t="n">
-        <v>0.006643470650588013</v>
+        <v>0.006643470650588457</v>
       </c>
     </row>
     <row r="1691">
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="B1691" t="n">
-        <v>0.003141472945911383</v>
+        <v>0.003141472945910939</v>
       </c>
     </row>
     <row r="1692">
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="B1692" t="n">
-        <v>-0.01753571604278625</v>
+        <v>-0.01753571604278592</v>
       </c>
     </row>
     <row r="1693">
@@ -17390,7 +17390,7 @@
         </is>
       </c>
       <c r="B1698" t="n">
-        <v>0.01485070024873791</v>
+        <v>0.01485070024873814</v>
       </c>
     </row>
     <row r="1699">
@@ -17400,7 +17400,7 @@
         </is>
       </c>
       <c r="B1699" t="n">
-        <v>0.0178223896050842</v>
+        <v>0.01782238960508398</v>
       </c>
     </row>
     <row r="1700">
@@ -17440,7 +17440,7 @@
         </is>
       </c>
       <c r="B1703" t="n">
-        <v>-0.01452356663881327</v>
+        <v>-0.01452356663881316</v>
       </c>
     </row>
     <row r="1704">
@@ -17450,7 +17450,7 @@
         </is>
       </c>
       <c r="B1704" t="n">
-        <v>0.01308247001042506</v>
+        <v>0.01308247001042484</v>
       </c>
     </row>
     <row r="1705">
@@ -17460,7 +17460,7 @@
         </is>
       </c>
       <c r="B1705" t="n">
-        <v>0.00169694543628518</v>
+        <v>0.001696945436285402</v>
       </c>
     </row>
     <row r="1706">
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="B1708" t="n">
-        <v>-0.00243843886203865</v>
+        <v>-0.002438438862038428</v>
       </c>
     </row>
     <row r="1709">
@@ -17500,7 +17500,7 @@
         </is>
       </c>
       <c r="B1709" t="n">
-        <v>0.007852431208950739</v>
+        <v>0.007852431208950517</v>
       </c>
     </row>
     <row r="1710">
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="B1711" t="n">
-        <v>0.01507162411611151</v>
+        <v>0.01507162411611107</v>
       </c>
     </row>
     <row r="1712">
@@ -17530,7 +17530,7 @@
         </is>
       </c>
       <c r="B1712" t="n">
-        <v>0.008695153211889517</v>
+        <v>0.008695153211889739</v>
       </c>
     </row>
     <row r="1713">
@@ -17560,7 +17560,7 @@
         </is>
       </c>
       <c r="B1715" t="n">
-        <v>0.003351154426324721</v>
+        <v>0.003351154426324499</v>
       </c>
     </row>
     <row r="1716">
@@ -17620,7 +17620,7 @@
         </is>
       </c>
       <c r="B1721" t="n">
-        <v>-0.002763981564619322</v>
+        <v>-0.0027639815646191</v>
       </c>
     </row>
     <row r="1722">
@@ -17630,7 +17630,7 @@
         </is>
       </c>
       <c r="B1722" t="n">
-        <v>-0.01650937439141398</v>
+        <v>-0.0165093743914142</v>
       </c>
     </row>
     <row r="1723">
@@ -17640,7 +17640,7 @@
         </is>
       </c>
       <c r="B1723" t="n">
-        <v>0.01266400507276955</v>
+        <v>0.01266400507276977</v>
       </c>
     </row>
     <row r="1724">
@@ -17660,7 +17660,7 @@
         </is>
       </c>
       <c r="B1725" t="n">
-        <v>0.004030184143952953</v>
+        <v>0.004030184143952731</v>
       </c>
     </row>
     <row r="1726">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="B1730" t="n">
-        <v>0.02182188320001788</v>
+        <v>0.0218218832000181</v>
       </c>
     </row>
     <row r="1731">
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="B1732" t="n">
-        <v>-0.03275936620140951</v>
+        <v>-0.0327593662014094</v>
       </c>
     </row>
     <row r="1733">
@@ -17740,7 +17740,7 @@
         </is>
       </c>
       <c r="B1733" t="n">
-        <v>0.02381666121574399</v>
+        <v>0.02381666121574377</v>
       </c>
     </row>
     <row r="1734">
@@ -17760,7 +17760,7 @@
         </is>
       </c>
       <c r="B1735" t="n">
-        <v>0.009060106853546301</v>
+        <v>0.009060106853546079</v>
       </c>
     </row>
     <row r="1736">
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="B1737" t="n">
-        <v>-0.01111308458046922</v>
+        <v>-0.01111308458046933</v>
       </c>
     </row>
     <row r="1738">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="B1738" t="n">
-        <v>-0.0003009761018916146</v>
+        <v>-0.0003009761018913926</v>
       </c>
     </row>
     <row r="1739">
@@ -17810,7 +17810,7 @@
         </is>
       </c>
       <c r="B1740" t="n">
-        <v>-0.0005637926052189934</v>
+        <v>-0.0005637926052188824</v>
       </c>
     </row>
     <row r="1741">
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="B1741" t="n">
-        <v>-0.04474938961819896</v>
+        <v>-0.04474938961819885</v>
       </c>
     </row>
     <row r="1742">
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="B1742" t="n">
-        <v>-0.003922282889509798</v>
+        <v>-0.00392228288951002</v>
       </c>
     </row>
     <row r="1743">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="B1743" t="n">
-        <v>-0.00255258997767549</v>
+        <v>-0.002552589977675379</v>
       </c>
     </row>
     <row r="1744">
@@ -17870,7 +17870,7 @@
         </is>
       </c>
       <c r="B1746" t="n">
-        <v>-0.02167805487909802</v>
+        <v>-0.02167805487909813</v>
       </c>
     </row>
     <row r="1747">
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="B1747" t="n">
-        <v>-0.009590264894392964</v>
+        <v>-0.009590264894392853</v>
       </c>
     </row>
     <row r="1748">
@@ -17900,7 +17900,7 @@
         </is>
       </c>
       <c r="B1749" t="n">
-        <v>0.02101259652588183</v>
+        <v>0.02101259652588161</v>
       </c>
     </row>
     <row r="1750">
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="B1750" t="n">
-        <v>-0.01001426344024658</v>
+        <v>-0.01001426344024647</v>
       </c>
     </row>
     <row r="1751">
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="B1752" t="n">
-        <v>0.01620442885819284</v>
+        <v>0.01620442885819307</v>
       </c>
     </row>
     <row r="1753">
@@ -17940,7 +17940,7 @@
         </is>
       </c>
       <c r="B1753" t="n">
-        <v>0.001906777398629211</v>
+        <v>0.001906777398628989</v>
       </c>
     </row>
     <row r="1754">
@@ -17950,7 +17950,7 @@
         </is>
       </c>
       <c r="B1754" t="n">
-        <v>-0.0005193309779542021</v>
+        <v>-0.0005193309779543132</v>
       </c>
     </row>
     <row r="1755">
@@ -17960,7 +17960,7 @@
         </is>
       </c>
       <c r="B1755" t="n">
-        <v>0.01496603877922476</v>
+        <v>0.01496603877922498</v>
       </c>
     </row>
     <row r="1756">
@@ -17970,7 +17970,7 @@
         </is>
       </c>
       <c r="B1756" t="n">
-        <v>-0.0030887506552707</v>
+        <v>-0.003088750655270922</v>
       </c>
     </row>
     <row r="1757">
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="B1757" t="n">
-        <v>-0.01801511596394856</v>
+        <v>-0.01801511596394834</v>
       </c>
     </row>
     <row r="1758">
@@ -18010,7 +18010,7 @@
         </is>
       </c>
       <c r="B1760" t="n">
-        <v>0.007030570258815594</v>
+        <v>0.007030570258815372</v>
       </c>
     </row>
     <row r="1761">
@@ -18030,7 +18030,7 @@
         </is>
       </c>
       <c r="B1762" t="n">
-        <v>-0.01019241695084872</v>
+        <v>-0.01019241695084883</v>
       </c>
     </row>
     <row r="1763">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="B1763" t="n">
-        <v>-0.002632215142658989</v>
+        <v>-0.002632215142658767</v>
       </c>
     </row>
     <row r="1764">
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="B1764" t="n">
-        <v>0.007913013215078202</v>
+        <v>0.00791301321507798</v>
       </c>
     </row>
     <row r="1765">
@@ -18070,7 +18070,7 @@
         </is>
       </c>
       <c r="B1766" t="n">
-        <v>0.00510825933180814</v>
+        <v>0.005108259331807918</v>
       </c>
     </row>
     <row r="1767">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="B1767" t="n">
-        <v>0.00623866988578814</v>
+        <v>0.006238669885788362</v>
       </c>
     </row>
     <row r="1768">
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="B1769" t="n">
-        <v>-0.00136952689199199</v>
+        <v>-0.001369526891992101</v>
       </c>
     </row>
     <row r="1770">
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="B1772" t="n">
-        <v>-0.01285239433679874</v>
+        <v>-0.01285239433679863</v>
       </c>
     </row>
     <row r="1773">
@@ -18140,7 +18140,7 @@
         </is>
       </c>
       <c r="B1773" t="n">
-        <v>0.01022830575472367</v>
+        <v>0.01022830575472344</v>
       </c>
     </row>
     <row r="1774">
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="B1778" t="n">
-        <v>0.01203941098121564</v>
+        <v>0.01203941098121586</v>
       </c>
     </row>
     <row r="1779">
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="B1780" t="n">
-        <v>-0.007578513559468703</v>
+        <v>-0.007578513559468814</v>
       </c>
     </row>
     <row r="1781">
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="B1787" t="n">
-        <v>-0.0008347167303475178</v>
+        <v>-0.0008347167303476288</v>
       </c>
     </row>
     <row r="1788">
@@ -18310,7 +18310,7 @@
         </is>
       </c>
       <c r="B1790" t="n">
-        <v>0.00177609221830255</v>
+        <v>0.001776092218302328</v>
       </c>
     </row>
     <row r="1791">
@@ -18330,7 +18330,7 @@
         </is>
       </c>
       <c r="B1792" t="n">
-        <v>-0.004542398008232418</v>
+        <v>-0.004542398008232307</v>
       </c>
     </row>
     <row r="1793">
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="B1793" t="n">
-        <v>-0.01679475381898665</v>
+        <v>-0.01679475381898676</v>
       </c>
     </row>
     <row r="1794">
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="B1795" t="n">
-        <v>-0.02257105882950183</v>
+        <v>-0.02257105882950161</v>
       </c>
     </row>
     <row r="1796">
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="B1796" t="n">
-        <v>-0.004924532685003369</v>
+        <v>-0.004924532685003813</v>
       </c>
     </row>
     <row r="1797">
@@ -18380,7 +18380,7 @@
         </is>
       </c>
       <c r="B1797" t="n">
-        <v>-0.02776924095343258</v>
+        <v>-0.02776924095343247</v>
       </c>
     </row>
     <row r="1798">
@@ -18410,7 +18410,7 @@
         </is>
       </c>
       <c r="B1800" t="n">
-        <v>-0.005316159225170258</v>
+        <v>-0.005316159225170036</v>
       </c>
     </row>
     <row r="1801">
@@ -18440,7 +18440,7 @@
         </is>
       </c>
       <c r="B1803" t="n">
-        <v>0.01540519916397454</v>
+        <v>0.01540519916397476</v>
       </c>
     </row>
     <row r="1804">
@@ -18520,7 +18520,7 @@
         </is>
       </c>
       <c r="B1811" t="n">
-        <v>-0.01681599762152863</v>
+        <v>-0.01681599762152874</v>
       </c>
     </row>
     <row r="1812">
@@ -18530,7 +18530,7 @@
         </is>
       </c>
       <c r="B1812" t="n">
-        <v>0.01054855277206568</v>
+        <v>0.0105485527720659</v>
       </c>
     </row>
     <row r="1813">
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="B1813" t="n">
-        <v>0.000872738008447671</v>
+        <v>0.0008727380084478931</v>
       </c>
     </row>
     <row r="1814">
@@ -18550,7 +18550,7 @@
         </is>
       </c>
       <c r="B1814" t="n">
-        <v>-0.02768984295205601</v>
+        <v>-0.02768984295205645</v>
       </c>
     </row>
     <row r="1815">
@@ -18620,7 +18620,7 @@
         </is>
       </c>
       <c r="B1821" t="n">
-        <v>0.01325754781631727</v>
+        <v>0.01325754781631705</v>
       </c>
     </row>
     <row r="1822">
@@ -18630,7 +18630,7 @@
         </is>
       </c>
       <c r="B1822" t="n">
-        <v>-0.01300553898259593</v>
+        <v>-0.01300553898259582</v>
       </c>
     </row>
     <row r="1823">
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="B1824" t="n">
-        <v>-0.006180166072909055</v>
+        <v>-0.006180166072908944</v>
       </c>
     </row>
     <row r="1825">
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="B1825" t="n">
-        <v>0.009705632072783299</v>
+        <v>0.009705632072783077</v>
       </c>
     </row>
     <row r="1826">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="B1828" t="n">
-        <v>-0.002793239813542736</v>
+        <v>-0.002793239813542847</v>
       </c>
     </row>
     <row r="1829">
@@ -18710,7 +18710,7 @@
         </is>
       </c>
       <c r="B1830" t="n">
-        <v>0.01247259478627116</v>
+        <v>0.01247259478627138</v>
       </c>
     </row>
     <row r="1831">
@@ -18720,7 +18720,7 @@
         </is>
       </c>
       <c r="B1831" t="n">
-        <v>0.009753904303686722</v>
+        <v>0.0097539043036865</v>
       </c>
     </row>
     <row r="1832">
@@ -18730,7 +18730,7 @@
         </is>
       </c>
       <c r="B1832" t="n">
-        <v>-0.004730792791704297</v>
+        <v>-0.004730792791704186</v>
       </c>
     </row>
     <row r="1833">
@@ -18770,7 +18770,7 @@
         </is>
       </c>
       <c r="B1836" t="n">
-        <v>0.0184455381087536</v>
+        <v>0.01844553810875382</v>
       </c>
     </row>
     <row r="1837">
@@ -18780,7 +18780,7 @@
         </is>
       </c>
       <c r="B1837" t="n">
-        <v>0.0007819437882177205</v>
+        <v>0.0007819437882174984</v>
       </c>
     </row>
     <row r="1838">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="B1841" t="n">
-        <v>-0.01059668177726147</v>
+        <v>-0.01059668177726159</v>
       </c>
     </row>
     <row r="1842">
@@ -18830,7 +18830,7 @@
         </is>
       </c>
       <c r="B1842" t="n">
-        <v>-0.002428010956527449</v>
+        <v>-0.002428010956527227</v>
       </c>
     </row>
     <row r="1843">
@@ -18900,7 +18900,7 @@
         </is>
       </c>
       <c r="B1849" t="n">
-        <v>-0.006491605007139301</v>
+        <v>-0.00649160500713919</v>
       </c>
     </row>
     <row r="1850">
@@ -18910,7 +18910,7 @@
         </is>
       </c>
       <c r="B1850" t="n">
-        <v>0.006280139381210637</v>
+        <v>0.006280139381210414</v>
       </c>
     </row>
     <row r="1851">
@@ -18920,7 +18920,7 @@
         </is>
       </c>
       <c r="B1851" t="n">
-        <v>0.01473292237675849</v>
+        <v>0.01473292237675872</v>
       </c>
     </row>
     <row r="1852">
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="B1856" t="n">
-        <v>0.01795266813743779</v>
+        <v>0.01795266813743757</v>
       </c>
     </row>
     <row r="1857">
@@ -18980,7 +18980,7 @@
         </is>
       </c>
       <c r="B1857" t="n">
-        <v>0.006953416720693051</v>
+        <v>0.006953416720693495</v>
       </c>
     </row>
     <row r="1858">
@@ -18990,7 +18990,7 @@
         </is>
       </c>
       <c r="B1858" t="n">
-        <v>0.003704625100737546</v>
+        <v>0.003704625100737324</v>
       </c>
     </row>
     <row r="1859">
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="B1859" t="n">
-        <v>0.005866502432354315</v>
+        <v>0.005866502432354537</v>
       </c>
     </row>
     <row r="1860">
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="B1860" t="n">
-        <v>-0.01454786361454052</v>
+        <v>-0.01454786361454075</v>
       </c>
     </row>
     <row r="1861">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="B1862" t="n">
-        <v>-0.005775282679172045</v>
+        <v>-0.005775282679172267</v>
       </c>
     </row>
     <row r="1863">
@@ -19040,7 +19040,7 @@
         </is>
       </c>
       <c r="B1863" t="n">
-        <v>0.009025495303527808</v>
+        <v>0.009025495303528031</v>
       </c>
     </row>
     <row r="1864">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="B1865" t="n">
-        <v>-0.01401879907540626</v>
+        <v>-0.01401879907540649</v>
       </c>
     </row>
     <row r="1866">
@@ -19080,7 +19080,7 @@
         </is>
       </c>
       <c r="B1867" t="n">
-        <v>-0.003802018974499832</v>
+        <v>-0.00380201897449961</v>
       </c>
     </row>
     <row r="1868">
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="B1871" t="n">
-        <v>-0.02996559845642144</v>
+        <v>-0.02996559845642177</v>
       </c>
     </row>
     <row r="1872">
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="B1872" t="n">
-        <v>0.0237180121934677</v>
+        <v>0.02371801219346814</v>
       </c>
     </row>
     <row r="1873">
@@ -19150,7 +19150,7 @@
         </is>
       </c>
       <c r="B1874" t="n">
-        <v>-0.02261792481917058</v>
+        <v>-0.0226179248191708</v>
       </c>
     </row>
     <row r="1875">
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="B1875" t="n">
-        <v>-0.05345132744347281</v>
+        <v>-0.05345132744347258</v>
       </c>
     </row>
     <row r="1876">
@@ -19180,7 +19180,7 @@
         </is>
       </c>
       <c r="B1877" t="n">
-        <v>0.02023213237659482</v>
+        <v>0.0202321323765946</v>
       </c>
     </row>
     <row r="1878">
@@ -19191,6 +19191,16 @@
       </c>
       <c r="B1878" t="n">
         <v>0.004939958138370448</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B1879" t="n">
+        <v>0.02265479503360024</v>
       </c>
     </row>
   </sheetData>
